--- a/LLY Financial Model.xlsx
+++ b/LLY Financial Model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samuelh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB591D71-A2F2-44FB-B816-5F8076705673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A54BDA4-5D1F-48DD-B499-7A696369BCEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9EA498D1-7DC0-ED4B-AD68-4170B24C29C4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9EA498D1-7DC0-ED4B-AD68-4170B24C29C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -302,45 +302,8 @@
 </comments>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="179">
   <si>
     <t xml:space="preserve">Price </t>
   </si>
@@ -874,6 +837,9 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>LLY</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +966,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1125,6 +1091,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1132,7 +1120,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1227,6 +1215,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1245,425 +1242,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-  <types>
-    <type name="_linkedentity">
-      <keyFlags>
-        <key name="%cvi">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-          <flag name="ExcludeFromCalcComparison" value="1"/>
-        </key>
-      </keyFlags>
-    </type>
-    <type name="_linkedentitycore">
-      <keyFlags>
-        <key name="%EntityServiceId">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%EntitySubDomainId">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%EntityCulture">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%EntityId">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%IsRefreshable">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-          <flag name="ExcludeFromCalcComparison" value="1"/>
-        </key>
-        <key name="%ProviderInfo">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%DataProviderExternalLinkLogo">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%DataProviderExternalLink">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-        </key>
-        <key name="%OutdatedReason">
-          <flag name="ShowInCardView" value="0"/>
-          <flag name="ShowInDotNotation" value="0"/>
-          <flag name="ShowInAutoComplete" value="0"/>
-          <flag name="ExcludeFromCalcComparison" value="1"/>
-        </key>
-      </keyFlags>
-    </type>
-  </types>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
-  <rv s="0">
-    <v>https://www.bing.com/financeapi/forcetrigger?t=a1wyu2&amp;q=XNYS%3aLLY&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="1">
-    <v>en-US</v>
-    <v>a1wyu2</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>ELI LILLY AND COMPANY (XNYS:LLY)</v>
-    <v>2</v>
-    <v>3</v>
-    <v>Finance</v>
-    <v>4</v>
-    <v>1182.73</v>
-    <v>623.78</v>
-    <v>0.51890000000000003</v>
-    <v>-11.39</v>
-    <v>-1.0243E-2</v>
-    <v>USD</v>
-    <v>Eli Lilly and Company is a medicine company, which discovers, develops, manufactures, and market products in a single business segment called human pharmaceutical products. The Company manufacture and distribute its products through facilities in the United States, including Puerto Rico, and in Europe and Asia. The Company’s products are sold in approximately 90 countries. Its Cardiometabolic Health products Basaglar; Humalog, Humalog Mix 75/25, Humalog U-100, Humalog U-200, Humalog Mix 50/50, insulin lispro, and others; Humulin, Humulin 70/30, and others; Jardiance; Mounjaro; Trulicity; Zepbound, and others. Its oncology products include Cyramza, Erbitux, Tyvyt, Verzenio, Retevmo, Jaypirca, and others. Its immunology products include Ebglyss, Olumiant, Omvoh, and Taltz. Its neuroscience products include Emgality and Kisunla. Its LillyDirect, a direct-to-patient digital health care platform, provides delivery of select Lilly medicines dispensed by third-party pharmacies to patients.</v>
-    <v>50000</v>
-    <v>New York Stock Exchange</v>
-    <v>XNYS</v>
-    <v>XNYS</v>
-    <v>Lilly Corporate Ctr, Drop Code 1094, INDIANAPOLIS, IN, 46285 US</v>
-    <v>1122.33</v>
-    <v>Pharmaceuticals</v>
-    <v>Stock</v>
-    <v>46191.749275231246</v>
-    <v>0</v>
-    <v>1088.6600000000001</v>
-    <v>1036490002253</v>
-    <v>ELI LILLY AND COMPANY</v>
-    <v>ELI LILLY AND COMPANY</v>
-    <v>1121.18</v>
-    <v>39.100700000000003</v>
-    <v>1112</v>
-    <v>1100.6099999999999</v>
-    <v>941741400</v>
-    <v>LLY</v>
-    <v>ELI LILLY AND COMPANY (XNYS:LLY)</v>
-    <v>1925195</v>
-    <v>3111984</v>
-    <v>1901</v>
-  </rv>
-  <rv s="2">
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
-  <s t="_hyperlink">
-    <k n="Address" t="s"/>
-    <k n="Text" t="s"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change (%)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Employees"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="P/E"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-    <k n="Year incorporated"/>
-  </s>
-  <s t="_linkedentity">
-    <k n="%cvi" t="r"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
-<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="1">
-    <a count="42">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">P/E</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
-  </spbArrays>
-  <spbData count="5">
-    <spb s="0">
-      <v>0</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="1">
-      <v>0</v>
-      <v>0</v>
-      <v>0</v>
-    </spb>
-    <spb s="2">
-      <v>1</v>
-      <v>1</v>
-      <v>1</v>
-      <v>1</v>
-    </spb>
-    <spb s="3">
-      <v>1</v>
-      <v>2</v>
-      <v>2</v>
-      <v>1</v>
-      <v>3</v>
-      <v>1</v>
-      <v>1</v>
-      <v>1</v>
-      <v>4</v>
-      <v>4</v>
-      <v>5</v>
-      <v>6</v>
-      <v>1</v>
-      <v>1</v>
-      <v>1</v>
-      <v>4</v>
-      <v>7</v>
-      <v>8</v>
-      <v>9</v>
-      <v>4</v>
-    </spb>
-    <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from previous close</v>
-      <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
-      <v>GMT</v>
-    </spb>
-  </spbData>
-</supportingPropertyBags>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="5">
-  <s>
-    <k n="^Order" t="spba"/>
-    <k n="TitleProperty" t="s"/>
-    <k n="SubTitleProperty" t="s"/>
-  </s>
-  <s>
-    <k n="ShowInCardView" t="b"/>
-    <k n="ShowInDotNotation" t="b"/>
-    <k n="ShowInAutoComplete" t="b"/>
-  </s>
-  <s>
-    <k n="ExchangeID" t="spb"/>
-    <k n="UniqueName" t="spb"/>
-    <k n="`%ProviderInfo" t="spb"/>
-    <k n="LearnMoreOnLink" t="spb"/>
-  </s>
-  <s>
-    <k n="Low" t="i"/>
-    <k n="P/E" t="i"/>
-    <k n="Beta" t="i"/>
-    <k n="High" t="i"/>
-    <k n="Name" t="i"/>
-    <k n="Open" t="i"/>
-    <k n="Price" t="i"/>
-    <k n="Change" t="i"/>
-    <k n="Volume" t="i"/>
-    <k n="Employees" t="i"/>
-    <k n="Change (%)" t="i"/>
-    <k n="Market cap" t="i"/>
-    <k n="52 week low" t="i"/>
-    <k n="52 week high" t="i"/>
-    <k n="Previous close" t="i"/>
-    <k n="Volume average" t="i"/>
-    <k n="Last trade time" t="i"/>
-    <k n="Year incorporated" t="i"/>
-    <k n="`%EntityServiceId" t="i"/>
-    <k n="Shares outstanding" t="i"/>
-  </s>
-  <s>
-    <k n="Price" t="s"/>
-    <k n="Change" t="s"/>
-    <k n="Change (%)" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Last trade time" t="s"/>
-  </s>
-</spbStructures>
-</file>
-
-<file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
-<richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <dxfs count="7">
-    <x:dxf>
-      <x:numFmt numFmtId="2" formatCode="0.00"/>
-    </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="0" formatCode="General"/>
-    </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="14" formatCode="0.00%"/>
-    </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="3" formatCode="#,##0"/>
-    </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="1" formatCode="0"/>
-    </x:dxf>
-  </dxfs>
-  <richProperties>
-    <rPr n="NumberFormat" t="s"/>
-    <rPr n="IsTitleField" t="b"/>
-  </richProperties>
-  <richStyles>
-    <rSty dxfid="1">
-      <rpv i="0">_([$$-en-US]* #,##0.00_);_([$$-en-US]* (#,##0.00);_([$$-en-US]* "-"??_);_(@_)</rpv>
-    </rSty>
-    <rSty dxfid="5">
-      <rpv i="0">#,##0.00</rpv>
-    </rSty>
-    <rSty>
-      <rpv i="1">1</rpv>
-    </rSty>
-    <rSty dxfid="4">
-      <rpv i="0">#,##0</rpv>
-    </rSty>
-    <rSty dxfid="3"/>
-    <rSty dxfid="1">
-      <rpv i="0">_([$$-en-US]* #,##0_);_([$$-en-US]* (#,##0);_([$$-en-US]* "-"_);_(@_)</rpv>
-    </rSty>
-    <rSty dxfid="2"/>
-    <rSty dxfid="6">
-      <rpv i="0">0</rpv>
-    </rSty>
-    <rSty dxfid="0">
-      <rpv i="0">0.00</rpv>
-    </rSty>
-  </richStyles>
-</richStyleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1983,7 +1561,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="3">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2005,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{948DA03D-D60F-7048-8E8C-0EDC58CFE77F}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A2:H29"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.125" customWidth="1"/>
@@ -2018,19 +1596,11 @@
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-    </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_FV(A1,"Price")</f>
-        <v>1100.6099999999999</v>
-      </c>
+      <c r="A2" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="55"/>
       <c r="D2" s="50" t="s">
         <v>90</v>
       </c>
@@ -2049,11 +1619,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" cm="1">
-        <f t="array" aca="1" ref="B3" ca="1">_FV(A1,"Shares outstanding",TRUE)/1000000</f>
-        <v>941.7414</v>
+        <v>0</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1213.4000000000001</v>
       </c>
       <c r="D3" s="40" t="s">
         <v>80</v>
@@ -2075,11 +1644,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" cm="1">
-        <f t="array" aca="1" ref="B4" ca="1">_FV(A1,"Market cap",TRUE)/1000000</f>
-        <v>1036490.002253</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>895.9</v>
       </c>
       <c r="D4" s="40" t="s">
         <v>81</v>
@@ -2101,10 +1669,11 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>7268</v>
+        <f>B3*B4</f>
+        <v>1087085.06</v>
       </c>
       <c r="D5" s="40" t="s">
         <v>64</v>
@@ -2126,11 +1695,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="1">
-        <f>1635+40868</f>
-        <v>42503</v>
+        <v>7268</v>
       </c>
       <c r="D6" s="40" t="s">
         <v>100</v>
@@ -2152,11 +1720,11 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3">
-        <f ca="1">B4+B6-B5</f>
-        <v>1071725.0022530002</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <f>1635+40868</f>
+        <v>42503</v>
       </c>
       <c r="D7" s="40" t="s">
         <v>82</v>
@@ -2177,6 +1745,13 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <f>B5+B7-B6</f>
+        <v>1122320.06</v>
+      </c>
       <c r="D8" s="40" t="s">
         <v>129</v>
       </c>
@@ -8203,10 +7778,10 @@
         <f t="shared" si="89"/>
         <v>130601.74499090893</v>
       </c>
-      <c r="M91" t="s">
+      <c r="M91" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="N91" s="16">
+      <c r="N91" s="57">
         <v>0.01</v>
       </c>
     </row>
@@ -8250,10 +7825,10 @@
         <f t="shared" si="89"/>
         <v>32650.436247727233</v>
       </c>
-      <c r="M92" t="s">
+      <c r="M92" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="N92" s="16">
+      <c r="N92" s="59">
         <v>0.09</v>
       </c>
     </row>
@@ -8298,10 +7873,10 @@
         <v>97951.308743181711</v>
       </c>
       <c r="L93" s="3"/>
-      <c r="M93" t="s">
+      <c r="M93" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="N93" s="1">
+      <c r="N93" s="60">
         <f>K93*(1+N91)/(N92-N91)</f>
         <v>1236635.272882669</v>
       </c>
@@ -8346,12 +7921,12 @@
         <f t="shared" si="91"/>
         <v>108.53330608662793</v>
       </c>
-      <c r="M94" t="s">
+      <c r="M94" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="N94" s="2">
-        <f ca="1">Main!B3</f>
-        <v>941.7414</v>
+      <c r="N94" s="22">
+        <f>Main!B4</f>
+        <v>895.9</v>
       </c>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
@@ -8471,12 +8046,12 @@
         <f>AVERAGE(AI47:AL47)</f>
         <v>902.5</v>
       </c>
-      <c r="M95" t="s">
+      <c r="M95" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="N95" s="1">
-        <f ca="1">N93/N94</f>
-        <v>1313.1367834977511</v>
+      <c r="N95" s="62">
+        <f>N93/N94</f>
+        <v>1380.3273500197222</v>
       </c>
     </row>
     <row r="98" spans="3:5" x14ac:dyDescent="0.25">

--- a/LLY Financial Model.xlsx
+++ b/LLY Financial Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D69650-30B8-45B2-B0B1-9420F3CCFE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE6F0EB-236B-47AB-ADDF-5103C93B31A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="753" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="753" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="330">
   <si>
     <t>LLY</t>
   </si>
@@ -1133,9 +1133,6 @@
   </si>
   <si>
     <t>LT Debt</t>
-  </si>
-  <si>
-    <t>income statement</t>
   </si>
   <si>
     <t>Equity Value Per Share</t>
@@ -1198,12 +1195,12 @@
     <numFmt numFmtId="174" formatCode="&quot;$&quot;#,##0.0_);\(&quot;$&quot;#,##0.0\);@_)"/>
     <numFmt numFmtId="175" formatCode="0.0%_);\(0.0%\);@_)"/>
     <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="179" formatCode="#,##0.0_);\(#,##0.0\)"/>
-    <numFmt numFmtId="180" formatCode="0.000%"/>
-    <numFmt numFmtId="181" formatCode="_(&quot;$&quot;* #,##0.0_);_(&quot;$&quot;* \(#,##0.0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\);@_)"/>
-    <numFmt numFmtId="183" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="184" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0_);\(#,##0.0\)"/>
+    <numFmt numFmtId="178" formatCode="0.000%"/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0.0_);_(&quot;$&quot;* \(#,##0.0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\);@_)"/>
+    <numFmt numFmtId="181" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="182" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="36" x14ac:knownFonts="1">
     <font>
@@ -1508,7 +1505,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1791,12 +1788,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1987,38 +1997,34 @@
     <xf numFmtId="167" fontId="26" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="172" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="174" fontId="21" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="168" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="174" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2035,7 +2041,7 @@
     </xf>
     <xf numFmtId="174" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2044,13 +2050,13 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="183" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="174" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2071,9 +2077,6 @@
     <xf numFmtId="8" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="8" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2081,15 +2084,12 @@
     </xf>
     <xf numFmtId="167" fontId="30" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="31" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="30" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="31" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="8" fontId="21" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2104,11 +2104,6 @@
     </xf>
     <xf numFmtId="171" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="21" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
@@ -2136,7 +2131,7 @@
     <xf numFmtId="167" fontId="23" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2144,6 +2139,27 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2449,8 +2465,8 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="205" t="s">
-        <v>330</v>
+      <c r="C2" s="198" t="s">
+        <v>329</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>1</v>
@@ -2472,7 +2488,7 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="190">
+      <c r="C3" s="183">
         <v>1215.02</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2497,7 +2513,7 @@
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="189">
+      <c r="C4" s="182">
         <v>893.7</v>
       </c>
       <c r="E4" s="7" t="s">
@@ -2548,7 +2564,7 @@
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="190">
+      <c r="C6" s="183">
         <v>8950</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -2573,7 +2589,7 @@
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="190">
+      <c r="C7" s="183">
         <f>7050+47858</f>
         <v>54908</v>
       </c>
@@ -3451,7 +3467,7 @@
     </row>
     <row r="4" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>39</v>
@@ -3513,75 +3529,75 @@
         <v>57</v>
       </c>
       <c r="C5" s="24">
-        <f>SUM(C6:C14)</f>
+        <f t="shared" ref="C5:T5" si="0">SUM(C6:C14)</f>
         <v>3243.6</v>
       </c>
       <c r="D5" s="24">
-        <f>SUM(D6:D14)</f>
+        <f t="shared" si="0"/>
         <v>3268.2</v>
       </c>
       <c r="E5" s="24">
-        <f>SUM(E6:E14)</f>
+        <f t="shared" si="0"/>
         <v>3489.2</v>
       </c>
       <c r="F5" s="24">
-        <f>SUM(F6:F14)</f>
+        <f t="shared" si="0"/>
         <v>3811.7</v>
       </c>
       <c r="G5" s="24">
-        <f>SUM(G6:G14)</f>
+        <f t="shared" si="0"/>
         <v>4045.3</v>
       </c>
       <c r="H5" s="24">
-        <f>SUM(H6:H14)</f>
+        <f t="shared" si="0"/>
         <v>4260.3999999999996</v>
       </c>
       <c r="I5" s="24">
-        <f>SUM(I6:I14)</f>
+        <f t="shared" si="0"/>
         <v>4565.3999999999996</v>
       </c>
       <c r="J5" s="24">
-        <f>SUM(J6:J14)</f>
+        <f t="shared" si="0"/>
         <v>5588.7000000000007</v>
       </c>
       <c r="K5" s="24">
-        <f>SUM(K6:K14)</f>
+        <f t="shared" si="0"/>
         <v>5369.2</v>
       </c>
       <c r="L5" s="24">
-        <f>SUM(L6:L14)</f>
+        <f t="shared" si="0"/>
         <v>7858.8000000000011</v>
       </c>
       <c r="M5" s="24">
-        <f>SUM(M6:M14)</f>
+        <f t="shared" si="0"/>
         <v>7261.6</v>
       </c>
       <c r="N5" s="24">
-        <f>SUM(N6:N14)</f>
+        <f t="shared" si="0"/>
         <v>8962.6999999999989</v>
       </c>
       <c r="O5" s="24">
-        <f>SUM(O6:O14)</f>
+        <f t="shared" si="0"/>
         <v>9147</v>
       </c>
       <c r="P5" s="24">
-        <f>SUM(P6:P14)</f>
+        <f t="shared" si="0"/>
         <v>11185.800000000001</v>
       </c>
       <c r="Q5" s="24">
-        <f>SUM(Q6:Q14)</f>
+        <f t="shared" si="0"/>
         <v>13051.800000000001</v>
       </c>
       <c r="R5" s="24">
-        <f>SUM(R6:R14)</f>
+        <f t="shared" si="0"/>
         <v>14526.3</v>
       </c>
       <c r="S5" s="24">
-        <f>SUM(S6:S14)</f>
+        <f t="shared" si="0"/>
         <v>15790.900000000001</v>
       </c>
       <c r="T5" s="24">
-        <f>SUM(T6:T14)</f>
+        <f t="shared" si="0"/>
         <v>18126</v>
       </c>
     </row>
@@ -4043,75 +4059,75 @@
         <v>59</v>
       </c>
       <c r="C15" s="29">
-        <f t="shared" ref="C15:T15" si="0">SUM(C16:C22)</f>
+        <f t="shared" ref="C15:T15" si="1">SUM(C16:C22)</f>
         <v>907.90000000000009</v>
       </c>
       <c r="D15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1034.1999999999998</v>
       </c>
       <c r="E15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1071.5</v>
       </c>
       <c r="F15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1207.8999999999999</v>
       </c>
       <c r="G15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1230.0000000000002</v>
       </c>
       <c r="H15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1518.6</v>
       </c>
       <c r="I15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1596.7</v>
       </c>
       <c r="J15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1736.2</v>
       </c>
       <c r="K15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1660.7</v>
       </c>
       <c r="L15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2043.2000000000003</v>
       </c>
       <c r="M15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2102.6</v>
       </c>
       <c r="N15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2328.1999999999998</v>
       </c>
       <c r="O15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1853.3000000000002</v>
       </c>
       <c r="P15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2317.6000000000004</v>
       </c>
       <c r="Q15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2326</v>
       </c>
       <c r="R15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2468.5</v>
       </c>
       <c r="S15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2268.4</v>
       </c>
       <c r="T15" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2486</v>
       </c>
     </row>
@@ -4496,75 +4512,75 @@
         <v>60</v>
       </c>
       <c r="C23" s="29">
-        <f t="shared" ref="C23:T23" si="1">SUM(C24:C27)</f>
+        <f t="shared" ref="C23:T23" si="2">SUM(C24:C27)</f>
         <v>743.7</v>
       </c>
       <c r="D23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>792.40000000000009</v>
       </c>
       <c r="E23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>862.8</v>
       </c>
       <c r="F23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>913.59999999999991</v>
       </c>
       <c r="G23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>755.9</v>
       </c>
       <c r="H23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>922.8</v>
       </c>
       <c r="I23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>975.6</v>
       </c>
       <c r="J23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1028.0999999999999</v>
       </c>
       <c r="K23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>834</v>
       </c>
       <c r="L23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1082.3000000000002</v>
       </c>
       <c r="M23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1185.8</v>
       </c>
       <c r="N23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1290.9000000000001</v>
       </c>
       <c r="O23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1088.0999999999999</v>
       </c>
       <c r="P23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1255.5999999999999</v>
       </c>
       <c r="Q23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1362.4</v>
       </c>
       <c r="R23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1535.5</v>
       </c>
       <c r="S23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1202.7</v>
       </c>
       <c r="T23" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1417</v>
       </c>
     </row>
@@ -4782,75 +4798,75 @@
         <v>61</v>
       </c>
       <c r="C28" s="29">
-        <f t="shared" ref="C28:T28" si="2">SUM(C29:C30)</f>
+        <f t="shared" ref="C28:T28" si="3">SUM(C29:C30)</f>
         <v>149.30000000000001</v>
       </c>
       <c r="D28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>157.5</v>
       </c>
       <c r="E28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>168.5</v>
       </c>
       <c r="F28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>175.6</v>
       </c>
       <c r="G28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>154.30000000000001</v>
       </c>
       <c r="H28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>169.3</v>
       </c>
       <c r="I28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>168.5</v>
       </c>
       <c r="J28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>186.1</v>
       </c>
       <c r="K28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>225.7</v>
       </c>
       <c r="L28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>192</v>
       </c>
       <c r="M28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>204.3</v>
       </c>
       <c r="N28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>257.7</v>
       </c>
       <c r="O28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>146.1</v>
       </c>
       <c r="P28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>249.7</v>
       </c>
       <c r="Q28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>246.1</v>
       </c>
       <c r="R28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>370.18000000000006</v>
       </c>
       <c r="S28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>261.06</v>
       </c>
       <c r="T28" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>358</v>
       </c>
     </row>
@@ -4960,71 +4976,71 @@
         <v>62</v>
       </c>
       <c r="C31" s="29">
-        <f>C32-(C5+C15+C23+C28)</f>
+        <f t="shared" ref="C31:S31" si="4">C32-(C5+C15+C23+C28)</f>
         <v>2765.5</v>
       </c>
       <c r="D31" s="29">
-        <f>D32-(D5+D15+D23+D28)</f>
+        <f t="shared" si="4"/>
         <v>1235.7000000000007</v>
       </c>
       <c r="E31" s="29">
-        <f>E32-(E5+E15+E23+E28)</f>
+        <f t="shared" si="4"/>
         <v>1349.6000000000004</v>
       </c>
       <c r="F31" s="29">
-        <f>F32-(F5+F15+F23+F28)</f>
+        <f t="shared" si="4"/>
         <v>1193.0000000000009</v>
       </c>
       <c r="G31" s="29">
-        <f>G32-(G5+G15+G23+G28)</f>
+        <f t="shared" si="4"/>
         <v>774.5</v>
       </c>
       <c r="H31" s="29">
-        <f>H32-(H5+H15+H23+H28)</f>
+        <f t="shared" si="4"/>
         <v>1441</v>
       </c>
       <c r="I31" s="29">
-        <f>I32-(I5+I15+I23+I28)</f>
+        <f t="shared" si="4"/>
         <v>2192.4000000000005</v>
       </c>
       <c r="J31" s="29">
-        <f>J32-(J5+J15+J23+J28)</f>
+        <f t="shared" si="4"/>
         <v>814.29999999999927</v>
       </c>
       <c r="K31" s="29">
-        <f>K32-(K5+K15+K23+K28)</f>
+        <f t="shared" si="4"/>
         <v>678.40000000000055</v>
       </c>
       <c r="L31" s="29">
-        <f>L32-(L5+L15+L23+L28)</f>
+        <f t="shared" si="4"/>
         <v>126.49999999999636</v>
       </c>
       <c r="M31" s="29">
-        <f>M32-(M5+M15+M23+M28)</f>
+        <f t="shared" si="4"/>
         <v>684.80000000000109</v>
       </c>
       <c r="N31" s="29">
-        <f>N32-(N5+N15+N23+N28)</f>
+        <f t="shared" si="4"/>
         <v>693.30000000000109</v>
       </c>
       <c r="O31" s="29">
-        <f>O32-(O5+O15+O23+O28)</f>
+        <f t="shared" si="4"/>
         <v>494.5</v>
       </c>
       <c r="P31" s="29">
-        <f>P32-(P5+P15+P23+P28)</f>
+        <f t="shared" si="4"/>
         <v>548.99999999999818</v>
       </c>
       <c r="Q31" s="29">
-        <f>Q32-(Q5+Q15+Q23+Q28)</f>
+        <f t="shared" si="4"/>
         <v>614.5</v>
       </c>
       <c r="R31" s="29">
-        <f>R32-(R5+R15+R23+R28)</f>
+        <f t="shared" si="4"/>
         <v>391.52000000000044</v>
       </c>
       <c r="S31" s="29">
-        <f>S32-(S5+S15+S23+S28)</f>
+        <f t="shared" si="4"/>
         <v>275.93999999999505</v>
       </c>
       <c r="T31" s="29">
@@ -5155,75 +5171,75 @@
         <v>65</v>
       </c>
       <c r="C34" s="31">
-        <f t="shared" ref="C34:T34" si="3">C32-C33</f>
+        <f t="shared" ref="C34:T34" si="5">C32-C33</f>
         <v>5737.9</v>
       </c>
       <c r="D34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5057.5</v>
       </c>
       <c r="E34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5362.5</v>
       </c>
       <c r="F34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5753.7000000000007</v>
       </c>
       <c r="G34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5333.3</v>
       </c>
       <c r="H34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6504.7000000000007</v>
       </c>
       <c r="I34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7638.5</v>
       </c>
       <c r="J34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7565.4</v>
       </c>
       <c r="K34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7094.5</v>
       </c>
       <c r="L34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9132.5999999999985</v>
       </c>
       <c r="M34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9268.2999999999993</v>
       </c>
       <c r="N34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>11129</v>
       </c>
       <c r="O34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10504</v>
       </c>
       <c r="P34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13109.900000000001</v>
       </c>
       <c r="Q34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>14592.5</v>
       </c>
       <c r="R34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>15920.3</v>
       </c>
       <c r="S34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>16222</v>
       </c>
       <c r="T34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>19706</v>
       </c>
     </row>
@@ -5556,59 +5572,59 @@
         <v>2096.4</v>
       </c>
       <c r="G40" s="26">
-        <f t="shared" ref="G40:T40" si="4">G34-(SUM(G35:G39))</f>
+        <f t="shared" ref="G40:T40" si="6">G34-(SUM(G35:G39))</f>
         <v>1529.6999999999998</v>
       </c>
       <c r="H40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2088.9000000000005</v>
       </c>
       <c r="I40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>427.19999999999982</v>
       </c>
       <c r="J40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2266.8000000000002</v>
       </c>
       <c r="K40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2536.1000000000004</v>
       </c>
       <c r="L40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3517.199999999998</v>
       </c>
       <c r="M40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1588.3999999999996</v>
       </c>
       <c r="N40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5038.6000000000004</v>
       </c>
       <c r="O40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3456</v>
       </c>
       <c r="P40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6777.2000000000007</v>
       </c>
       <c r="Q40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7232.4000000000005</v>
       </c>
       <c r="R40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8266.1999999999989</v>
       </c>
       <c r="S40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8850</v>
       </c>
       <c r="T40" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9247</v>
       </c>
       <c r="U40" s="26"/>
@@ -5710,75 +5726,75 @@
         <v>73</v>
       </c>
       <c r="C42" s="33">
-        <f t="shared" ref="C42:T42" si="5">C40-C41</f>
+        <f t="shared" ref="C42:T42" si="7">C40-C41</f>
         <v>1902.8999999999999</v>
       </c>
       <c r="D42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>952.50000000000011</v>
       </c>
       <c r="E42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1451.7</v>
       </c>
       <c r="F42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1937.7</v>
       </c>
       <c r="G42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1344.8999999999999</v>
       </c>
       <c r="H42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1763.2000000000005</v>
       </c>
       <c r="I42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-57.400000000000205</v>
       </c>
       <c r="J42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1947.7000000000003</v>
       </c>
       <c r="K42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2242.9000000000005</v>
       </c>
       <c r="L42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2966.9999999999982</v>
       </c>
       <c r="M42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>970.29999999999961</v>
       </c>
       <c r="N42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4409.7000000000007</v>
       </c>
       <c r="O42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2759</v>
       </c>
       <c r="P42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5661.3000000000011</v>
       </c>
       <c r="Q42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5582.5</v>
       </c>
       <c r="R42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>6637.6999999999989</v>
       </c>
       <c r="S42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>7396</v>
       </c>
       <c r="T42" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>7095</v>
       </c>
       <c r="U42" s="31"/>
@@ -5816,59 +5832,59 @@
         <v>2.14</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" ref="G43:T43" si="6">G42/G44</f>
+        <f t="shared" ref="G43:T43" si="8">G42/G44</f>
         <v>1.4888741281966122</v>
       </c>
       <c r="H43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.9526024363233672</v>
       </c>
       <c r="I43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-6.3791953767504114E-2</v>
       </c>
       <c r="J43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.1617092119866816</v>
       </c>
       <c r="K43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.4816331046691755</v>
       </c>
       <c r="L43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3.2813536828135348</v>
       </c>
       <c r="M43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.0721546961325963</v>
       </c>
       <c r="N43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4.8779867256637175</v>
       </c>
       <c r="O43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3.0635132134132799</v>
       </c>
       <c r="P43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6.2917314958879764</v>
       </c>
       <c r="Q43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6.2110591900311531</v>
       </c>
       <c r="R43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>7.3916481069042304</v>
       </c>
       <c r="S43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8.2553856457193877</v>
       </c>
       <c r="T43" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>7.9391632938743673</v>
       </c>
       <c r="U43" s="6"/>
@@ -6008,59 +6024,59 @@
       <c r="E47" s="36"/>
       <c r="F47" s="36"/>
       <c r="G47" s="37">
-        <f>(G5-C5)/C5</f>
+        <f t="shared" ref="G47:T47" si="9">(G5-C5)/C5</f>
         <v>0.24716364533234686</v>
       </c>
       <c r="H47" s="37">
-        <f>(H5-D5)/D5</f>
+        <f t="shared" si="9"/>
         <v>0.30359219142035365</v>
       </c>
       <c r="I47" s="37">
-        <f>(I5-E5)/E5</f>
+        <f t="shared" si="9"/>
         <v>0.30843746417516904</v>
       </c>
       <c r="J47" s="37">
-        <f>(J5-F5)/F5</f>
+        <f t="shared" si="9"/>
         <v>0.46619618542907393</v>
       </c>
       <c r="K47" s="37">
-        <f>(K5-G5)/G5</f>
+        <f t="shared" si="9"/>
         <v>0.3272686821743751</v>
       </c>
       <c r="L47" s="37">
-        <f>(L5-H5)/H5</f>
+        <f t="shared" si="9"/>
         <v>0.84461552905830484</v>
       </c>
       <c r="M47" s="37">
-        <f>(M5-I5)/I5</f>
+        <f t="shared" si="9"/>
         <v>0.59057256757348775</v>
       </c>
       <c r="N47" s="37">
-        <f>(N5-J5)/J5</f>
+        <f t="shared" si="9"/>
         <v>0.6037182171166815</v>
       </c>
       <c r="O47" s="37">
-        <f>(O5-K5)/K5</f>
+        <f t="shared" si="9"/>
         <v>0.70360575132235725</v>
       </c>
       <c r="P47" s="37">
-        <f>(P5-L5)/L5</f>
+        <f t="shared" si="9"/>
         <v>0.4233470758894487</v>
       </c>
       <c r="Q47" s="37">
-        <f>(Q5-M5)/M5</f>
+        <f t="shared" si="9"/>
         <v>0.79737247989423821</v>
       </c>
       <c r="R47" s="37">
-        <f>(R5-N5)/N5</f>
+        <f t="shared" si="9"/>
         <v>0.62075044350474762</v>
       </c>
       <c r="S47" s="37">
-        <f>(S5-O5)/O5</f>
+        <f t="shared" si="9"/>
         <v>0.72634743631791865</v>
       </c>
       <c r="T47" s="37">
-        <f>(T5-P5)/P5</f>
+        <f t="shared" si="9"/>
         <v>0.62044735289384745</v>
       </c>
       <c r="V47" s="37"/>
@@ -6089,59 +6105,59 @@
       <c r="E48" s="36"/>
       <c r="F48" s="36"/>
       <c r="G48" s="37">
-        <f t="shared" ref="G48:T48" si="7">(G15-C15)/C15</f>
+        <f t="shared" ref="G48:T48" si="10">(G15-C15)/C15</f>
         <v>0.35477475492895705</v>
       </c>
       <c r="H48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.46838135757106958</v>
       </c>
       <c r="I48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.49015398973401775</v>
       </c>
       <c r="J48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.43737064326517117</v>
       </c>
       <c r="K48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.35016260162601603</v>
       </c>
       <c r="L48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.34544975635453734</v>
       </c>
       <c r="M48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.31684098453059428</v>
       </c>
       <c r="N48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.34097454210344419</v>
       </c>
       <c r="O48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.11597519118444037</v>
       </c>
       <c r="P48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.13429913860610809</v>
       </c>
       <c r="Q48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.10624940549795496</v>
       </c>
       <c r="R48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>6.0261145949660762E-2</v>
       </c>
       <c r="S48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.22397884854044131</v>
       </c>
       <c r="T48" s="37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>7.2661373835001555E-2</v>
       </c>
       <c r="V48" s="37"/>
@@ -6170,59 +6186,59 @@
       <c r="E49" s="36"/>
       <c r="F49" s="36"/>
       <c r="G49" s="37">
-        <f t="shared" ref="G49:T49" si="8">(G23-C23)/C23</f>
+        <f t="shared" ref="G49:T49" si="11">(G23-C23)/C23</f>
         <v>1.6404464165658102E-2</v>
       </c>
       <c r="H49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.16456335184250359</v>
       </c>
       <c r="I49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.13073713490959674</v>
       </c>
       <c r="J49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.12532837127845886</v>
       </c>
       <c r="K49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.10332054504564099</v>
       </c>
       <c r="L49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.17284351972258369</v>
       </c>
       <c r="M49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.21545715457154563</v>
       </c>
       <c r="N49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.25561715786402123</v>
       </c>
       <c r="O49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.30467625899280565</v>
       </c>
       <c r="P49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.16012196248729529</v>
       </c>
       <c r="Q49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.14892899308483737</v>
       </c>
       <c r="R49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.18948020760709575</v>
       </c>
       <c r="S49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.10532120209539578</v>
       </c>
       <c r="T49" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.12854412233195292</v>
       </c>
       <c r="V49" s="37"/>
@@ -6251,59 +6267,59 @@
       <c r="E50" s="36"/>
       <c r="F50" s="36"/>
       <c r="G50" s="37">
-        <f t="shared" ref="G50:T50" si="9">(G28-C28)/C28</f>
+        <f t="shared" ref="G50:T50" si="12">(G28-C28)/C28</f>
         <v>3.3489618218352307E-2</v>
       </c>
       <c r="H50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>7.4920634920634999E-2</v>
       </c>
       <c r="I50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>5.9794988610478363E-2</v>
       </c>
       <c r="K50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.46273493195074511</v>
       </c>
       <c r="L50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.13408151210868274</v>
       </c>
       <c r="M50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.21246290801186951</v>
       </c>
       <c r="N50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.38473938742611496</v>
       </c>
       <c r="O50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-0.35268054940186089</v>
       </c>
       <c r="P50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.30052083333333329</v>
       </c>
       <c r="Q50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.20460107684777279</v>
       </c>
       <c r="R50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.43647652308886331</v>
       </c>
       <c r="S50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.78685831622176605</v>
       </c>
       <c r="T50" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.43372046455746904</v>
       </c>
       <c r="V50" s="37"/>
@@ -6332,59 +6348,59 @@
       <c r="E51" s="36"/>
       <c r="F51" s="36"/>
       <c r="G51" s="37">
-        <f t="shared" ref="G51:T51" si="10">(G31-C31)/C31</f>
+        <f t="shared" ref="G51:T51" si="13">(G31-C31)/C31</f>
         <v>-0.71994214427770742</v>
       </c>
       <c r="H51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.16614064902484352</v>
       </c>
       <c r="I51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.62448132780082988</v>
       </c>
       <c r="J51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.31743503772003467</v>
       </c>
       <c r="K51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.12408005164622267</v>
       </c>
       <c r="L51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.91221374045801784</v>
       </c>
       <c r="M51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.68764823937237685</v>
       </c>
       <c r="N51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.14859388431781689</v>
       </c>
       <c r="O51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.27107900943396285</v>
       </c>
       <c r="P51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3.3399209486167112</v>
       </c>
       <c r="Q51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.10265771028037526</v>
       </c>
       <c r="R51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.43528054233376628</v>
       </c>
       <c r="S51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.44198179979778551</v>
       </c>
       <c r="T51" s="37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>6.9216757741351442E-2</v>
       </c>
       <c r="V51" s="37"/>
@@ -6409,75 +6425,75 @@
         <v>81</v>
       </c>
       <c r="C52" s="37">
-        <f t="shared" ref="C52:T52" si="11">C34/C32</f>
+        <f t="shared" ref="C52:T52" si="14">C34/C32</f>
         <v>0.73468629961587706</v>
       </c>
       <c r="D52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.77951602959309496</v>
       </c>
       <c r="E52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.77251642272674881</v>
       </c>
       <c r="F52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.78798378482018139</v>
       </c>
       <c r="G52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.76627873563218396</v>
       </c>
       <c r="H52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.78255795767615888</v>
       </c>
       <c r="I52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.80417114101025411</v>
       </c>
       <c r="J52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.80883956636089549</v>
       </c>
       <c r="K52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.80913549270072993</v>
       </c>
       <c r="L52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.80799447924408108</v>
       </c>
       <c r="M52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.81022982577300651</v>
       </c>
       <c r="N52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.82237231023882718</v>
       </c>
       <c r="O52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.82520229397438916</v>
       </c>
       <c r="P52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.8426631185843666</v>
       </c>
       <c r="Q52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.82908163265306123</v>
       </c>
       <c r="R52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.82522807381297947</v>
       </c>
       <c r="S52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.81933430981362698</v>
       </c>
       <c r="T52" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.85775224166449027</v>
       </c>
       <c r="V52" s="37"/>
@@ -6502,75 +6518,75 @@
         <v>82</v>
       </c>
       <c r="C53" s="37">
-        <f t="shared" ref="C53:T53" si="12">C35/C32</f>
+        <f t="shared" ref="C53:T53" si="15">C35/C32</f>
         <v>0.20615877080665812</v>
       </c>
       <c r="D53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.27464549938347721</v>
       </c>
       <c r="E53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.25972398294341364</v>
       </c>
       <c r="F53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.27334355912240815</v>
       </c>
       <c r="G53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.28521551724137928</v>
       </c>
       <c r="H53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.28350236402353196</v>
       </c>
       <c r="I53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.25362685027267173</v>
       </c>
       <c r="J53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.27398593024996259</v>
       </c>
       <c r="K53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.28772810218978107</v>
       </c>
       <c r="L53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.2398697667834519</v>
       </c>
       <c r="M53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.23901355875899327</v>
       </c>
       <c r="N53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.22334624024592103</v>
       </c>
       <c r="O53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.21478513630293031</v>
       </c>
       <c r="P53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.21443401016859817</v>
       </c>
       <c r="Q53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.19690582246261534</v>
       </c>
       <c r="R53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.19705059091851546</v>
       </c>
       <c r="S53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.17728168089297439</v>
       </c>
       <c r="T53" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.16623139200835726</v>
       </c>
       <c r="V53" s="37"/>
@@ -6595,75 +6611,75 @@
         <v>83</v>
       </c>
       <c r="C54" s="37">
-        <f t="shared" ref="C54:T54" si="13">C36/C32</f>
+        <f t="shared" ref="C54:T54" si="16">C36/C32</f>
         <v>0.1994750320102433</v>
       </c>
       <c r="D54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.25047780517879159</v>
       </c>
       <c r="E54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.23254004840382619</v>
       </c>
       <c r="F54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.22504040099701444</v>
       </c>
       <c r="G54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.2513218390804598</v>
       </c>
       <c r="H54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.2316382141697044</v>
       </c>
       <c r="I54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.18991219758701283</v>
       </c>
       <c r="J54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.20576474864755062</v>
       </c>
       <c r="K54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.22265054744525548</v>
       </c>
       <c r="L54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.18732526453622114</v>
       </c>
       <c r="M54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.1835633922249128</v>
       </c>
       <c r="N54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.17915730669188934</v>
       </c>
       <c r="O54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.19388797234661009</v>
       </c>
       <c r="P54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.17695417703130925</v>
       </c>
       <c r="Q54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.15571451297668287</v>
       </c>
       <c r="R54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.16231598590089158</v>
       </c>
       <c r="S54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.14818930249002474</v>
       </c>
       <c r="T54" s="37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.14929920780012187</v>
       </c>
       <c r="U54" s="37"/>
@@ -6689,75 +6705,75 @@
         <v>84</v>
       </c>
       <c r="C55" s="37">
-        <f t="shared" ref="C55:T55" si="14">C37/C32</f>
+        <f t="shared" ref="C55:T55" si="17">C37/C32</f>
         <v>2.1203585147247118E-2</v>
       </c>
       <c r="D55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>6.7879161528976564E-2</v>
       </c>
       <c r="E55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>8.9892820099112588E-3</v>
       </c>
       <c r="F55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3.288230299378235E-2</v>
       </c>
       <c r="G55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1.5086206896551725E-2</v>
       </c>
       <c r="H55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1.1681765137570528E-2</v>
       </c>
       <c r="I55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.31321457899058808</v>
       </c>
       <c r="J55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>6.6564030192229562E-2</v>
       </c>
       <c r="K55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1.2602645985401459E-2</v>
       </c>
       <c r="L55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1.3651484587889728E-2</v>
       </c>
       <c r="M55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.24708237536169803</v>
       </c>
       <c r="N55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1.3980846535824073E-2</v>
       </c>
       <c r="O55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.12349752533584728</v>
       </c>
       <c r="P55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>9.834358549142868E-3</v>
       </c>
       <c r="Q55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3.7253988455070226E-2</v>
       </c>
       <c r="R55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2.7410325523533067E-2</v>
       </c>
       <c r="S55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2.9496439214101722E-2</v>
       </c>
       <c r="T55" s="37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.12083224514668756</v>
       </c>
       <c r="U55" s="37"/>
@@ -6783,75 +6799,75 @@
         <v>85</v>
       </c>
       <c r="C56" s="37">
-        <f t="shared" ref="C56:T56" si="15">C41/C40</f>
+        <f t="shared" ref="C56:T56" si="18">C41/C40</f>
         <v>7.3383326840670046E-2</v>
       </c>
       <c r="D56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.12686772389769915</v>
       </c>
       <c r="E56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>7.2692430533375915E-2</v>
       </c>
       <c r="F56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>7.5701202060675432E-2</v>
       </c>
       <c r="G56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.12080800156893511</v>
       </c>
       <c r="H56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.15591938340753503</v>
       </c>
       <c r="I56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1.1343632958801504</v>
       </c>
       <c r="J56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.14077113110993472</v>
       </c>
       <c r="K56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.11561058317889671</v>
       </c>
       <c r="L56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.15643125213237813</v>
       </c>
       <c r="M56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.38913371946612957</v>
       </c>
       <c r="N56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.12481641725876234</v>
       </c>
       <c r="O56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.20167824074074073</v>
       </c>
       <c r="P56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.16465501977217731</v>
       </c>
       <c r="Q56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.22812620983352691</v>
       </c>
       <c r="R56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.19700708910986914</v>
       </c>
       <c r="S56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.16429378531073446</v>
       </c>
       <c r="T56" s="37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.2327241267438088</v>
       </c>
       <c r="U56" s="37"/>
@@ -7641,66 +7657,66 @@
     <row r="1" spans="2:17" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C2" s="22" t="str">
-        <f>C14</f>
+        <f t="shared" ref="C2:Q2" si="0">C14</f>
         <v>FY'22</v>
       </c>
       <c r="D2" s="22" t="str">
-        <f>D14</f>
+        <f t="shared" si="0"/>
         <v>FY'23</v>
       </c>
       <c r="E2" s="22" t="str">
-        <f>E14</f>
+        <f t="shared" si="0"/>
         <v>FY'24</v>
       </c>
       <c r="F2" s="39" t="str">
-        <f>F14</f>
+        <f t="shared" si="0"/>
         <v>FY'25</v>
       </c>
       <c r="G2" s="22" t="str">
-        <f>G14</f>
+        <f t="shared" si="0"/>
         <v>FY'26</v>
       </c>
       <c r="H2" s="22" t="str">
-        <f>H14</f>
+        <f t="shared" si="0"/>
         <v>FY'27</v>
       </c>
       <c r="I2" s="22" t="str">
-        <f>I14</f>
+        <f t="shared" si="0"/>
         <v>FY'28</v>
       </c>
       <c r="J2" s="22" t="str">
-        <f>J14</f>
+        <f t="shared" si="0"/>
         <v>FY'29</v>
       </c>
       <c r="K2" s="22" t="str">
-        <f>K14</f>
+        <f t="shared" si="0"/>
         <v>FY'30</v>
       </c>
       <c r="L2" s="22" t="str">
-        <f>L14</f>
+        <f t="shared" si="0"/>
         <v>FY'31</v>
       </c>
       <c r="M2" s="22" t="str">
-        <f>M14</f>
+        <f t="shared" si="0"/>
         <v>FY'32</v>
       </c>
       <c r="N2" s="22" t="str">
-        <f>N14</f>
+        <f t="shared" si="0"/>
         <v>FY'33</v>
       </c>
       <c r="O2" s="22" t="str">
-        <f>O14</f>
+        <f t="shared" si="0"/>
         <v>FY'34</v>
       </c>
       <c r="P2" s="22" t="str">
-        <f>P14</f>
+        <f t="shared" si="0"/>
         <v>FY'35</v>
       </c>
       <c r="Q2" s="22" t="str">
-        <f>Q14</f>
+        <f t="shared" si="0"/>
         <v>FY'36</v>
       </c>
     </row>
@@ -7722,22 +7738,22 @@
         <v>0.62672864258479022</v>
       </c>
       <c r="G3" s="42">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H3" s="42">
-        <v>0.3417</v>
+        <v>0.3</v>
       </c>
       <c r="I3" s="42">
-        <v>0.2833</v>
+        <v>0.2</v>
       </c>
       <c r="J3" s="42">
-        <v>0.22500000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="K3" s="42">
-        <v>0.16669999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="L3" s="42">
-        <v>0.10829999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="M3" s="42">
         <v>0.05</v>
@@ -7773,37 +7789,37 @@
         <v>0.10211808671493745</v>
       </c>
       <c r="G4" s="42">
-        <v>0.25</v>
+        <v>-0.05</v>
       </c>
       <c r="H4" s="42">
-        <v>0.2167</v>
+        <v>-0.05</v>
       </c>
       <c r="I4" s="42">
-        <v>0.18329999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="J4" s="42">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="K4" s="42">
-        <v>0.1167</v>
+        <v>-0.05</v>
       </c>
       <c r="L4" s="42">
-        <v>8.3299999999999999E-2</v>
+        <v>-0.05</v>
       </c>
       <c r="M4" s="42">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="N4" s="42">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="O4" s="42">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="P4" s="42">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="Q4" s="42">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
@@ -7875,13 +7891,13 @@
         <v>0.15048311924519722</v>
       </c>
       <c r="G6" s="42">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="42">
-        <v>0.26329999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="I6" s="42">
-        <v>0.22670000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J6" s="42">
         <v>0.19</v>
@@ -8240,37 +8256,47 @@
         <v>0.19786023519536136</v>
       </c>
       <c r="G12" s="43">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H12" s="43">
-        <v>0.2</v>
+        <f>G12</f>
+        <v>0.19</v>
       </c>
       <c r="I12" s="43">
-        <v>0.2</v>
+        <f t="shared" ref="I12:Q12" si="1">H12</f>
+        <v>0.19</v>
       </c>
       <c r="J12" s="43">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.19</v>
       </c>
       <c r="K12" s="43">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.19</v>
       </c>
       <c r="L12" s="43">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.19</v>
       </c>
       <c r="M12" s="43">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.19</v>
       </c>
       <c r="N12" s="43">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.19</v>
       </c>
       <c r="O12" s="43">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.19</v>
       </c>
       <c r="P12" s="43">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.19</v>
       </c>
       <c r="Q12" s="43">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.19</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
@@ -8278,7 +8304,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="206"/>
+      <c r="F13" s="199"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -8341,68 +8367,68 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="207" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="208">
         <f>SUM('10QIS'!C5:F5)</f>
         <v>13812.7</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="208">
         <f>SUM('10QIS'!G5:J5)</f>
         <v>18459.800000000003</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="208">
         <f>SUM('10QIS'!K5:N5)</f>
         <v>29452.299999999996</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="209">
         <f>SUM('10QIS'!O5:R5)</f>
         <v>47910.900000000009</v>
       </c>
-      <c r="G15" s="26">
-        <f>F15*(1+G3)</f>
-        <v>67075.260000000009</v>
-      </c>
-      <c r="H15" s="26">
-        <f>G15*(1+H3)</f>
-        <v>89994.876342000003</v>
-      </c>
-      <c r="I15" s="26">
-        <f>H15*(1+I3)</f>
-        <v>115490.42480968861</v>
-      </c>
-      <c r="J15" s="26">
-        <f>I15*(1+J3)</f>
-        <v>141475.77039186857</v>
-      </c>
-      <c r="K15" s="26">
-        <f>J15*(1+K3)</f>
-        <v>165059.78131619308</v>
-      </c>
-      <c r="L15" s="26">
-        <f>K15*(1+L3)</f>
-        <v>182935.75563273681</v>
-      </c>
-      <c r="M15" s="26">
-        <f>L15*(1+M3)</f>
-        <v>192082.54341437365</v>
-      </c>
-      <c r="N15" s="26">
-        <f>M15*(1+N3)</f>
-        <v>201686.67058509233</v>
-      </c>
-      <c r="O15" s="26">
-        <f>N15*(1+O3)</f>
-        <v>211771.00411434696</v>
-      </c>
-      <c r="P15" s="26">
-        <f>O15*(1+P3)</f>
-        <v>222359.55432006432</v>
-      </c>
-      <c r="Q15" s="26">
-        <f>P15*(1+Q3)</f>
-        <v>233477.53203606754</v>
+      <c r="G15" s="208">
+        <f t="shared" ref="G15:Q15" si="2">F15*(1+G3)</f>
+        <v>71866.350000000006</v>
+      </c>
+      <c r="H15" s="208">
+        <f t="shared" si="2"/>
+        <v>93426.255000000005</v>
+      </c>
+      <c r="I15" s="208">
+        <f t="shared" si="2"/>
+        <v>112111.50600000001</v>
+      </c>
+      <c r="J15" s="208">
+        <f t="shared" si="2"/>
+        <v>123322.65660000002</v>
+      </c>
+      <c r="K15" s="208">
+        <f t="shared" si="2"/>
+        <v>129488.78943000002</v>
+      </c>
+      <c r="L15" s="208">
+        <f t="shared" si="2"/>
+        <v>135963.22890150003</v>
+      </c>
+      <c r="M15" s="208">
+        <f t="shared" si="2"/>
+        <v>142761.39034657503</v>
+      </c>
+      <c r="N15" s="208">
+        <f t="shared" si="2"/>
+        <v>149899.45986390379</v>
+      </c>
+      <c r="O15" s="208">
+        <f t="shared" si="2"/>
+        <v>157394.43285709899</v>
+      </c>
+      <c r="P15" s="208">
+        <f t="shared" si="2"/>
+        <v>165264.15449995393</v>
+      </c>
+      <c r="Q15" s="208">
+        <f t="shared" si="2"/>
+        <v>173527.36222495165</v>
       </c>
     </row>
     <row r="16" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
@@ -8697,80 +8723,80 @@
       <c r="B25" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="211">
         <f>SUM('10QIS'!C15:F15)</f>
         <v>4221.5</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="211">
         <f>SUM('10QIS'!G15:J15)</f>
         <v>6081.5</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="211">
         <f>SUM('10QIS'!K15:N15)</f>
         <v>8134.7</v>
       </c>
-      <c r="F25" s="51">
+      <c r="F25" s="212">
         <f>SUM('10QIS'!O15:R15)</f>
         <v>8965.4000000000015</v>
       </c>
-      <c r="G25" s="26">
-        <f>F25*(1+G4)</f>
-        <v>11206.750000000002</v>
-      </c>
-      <c r="H25" s="26">
-        <f>G25*(1+H4)</f>
-        <v>13635.252725</v>
-      </c>
-      <c r="I25" s="26">
-        <f>H25*(1+I4)</f>
-        <v>16134.5945494925</v>
-      </c>
-      <c r="J25" s="26">
-        <f>I25*(1+J4)</f>
-        <v>18554.783731916374</v>
-      </c>
-      <c r="K25" s="26">
-        <f>J25*(1+K4)</f>
-        <v>20720.126993431015</v>
-      </c>
-      <c r="L25" s="26">
-        <f>K25*(1+L4)</f>
-        <v>22446.113571983817</v>
-      </c>
-      <c r="M25" s="26">
-        <f>L25*(1+M4)</f>
-        <v>23568.419250583007</v>
-      </c>
-      <c r="N25" s="26">
-        <f>M25*(1+N4)</f>
-        <v>24746.840213112158</v>
-      </c>
-      <c r="O25" s="26">
-        <f>N25*(1+O4)</f>
-        <v>25984.182223767766</v>
-      </c>
-      <c r="P25" s="26">
-        <f>O25*(1+P4)</f>
-        <v>27283.391334956155</v>
-      </c>
-      <c r="Q25" s="26">
-        <f>P25*(1+Q4)</f>
-        <v>28647.560901703964</v>
+      <c r="G25" s="211">
+        <f t="shared" ref="G25:Q25" si="3">F25*(1+G4)</f>
+        <v>8517.130000000001</v>
+      </c>
+      <c r="H25" s="211">
+        <f t="shared" si="3"/>
+        <v>8091.2735000000002</v>
+      </c>
+      <c r="I25" s="211">
+        <f t="shared" si="3"/>
+        <v>7686.7098249999999</v>
+      </c>
+      <c r="J25" s="211">
+        <f t="shared" si="3"/>
+        <v>7302.37433375</v>
+      </c>
+      <c r="K25" s="211">
+        <f t="shared" si="3"/>
+        <v>6937.2556170624994</v>
+      </c>
+      <c r="L25" s="211">
+        <f t="shared" si="3"/>
+        <v>6590.3928362093739</v>
+      </c>
+      <c r="M25" s="211">
+        <f t="shared" si="3"/>
+        <v>6260.8731943989051</v>
+      </c>
+      <c r="N25" s="211">
+        <f t="shared" si="3"/>
+        <v>5947.8295346789591</v>
+      </c>
+      <c r="O25" s="211">
+        <f t="shared" si="3"/>
+        <v>5650.4380579450108</v>
+      </c>
+      <c r="P25" s="211">
+        <f t="shared" si="3"/>
+        <v>5367.9161550477602</v>
+      </c>
+      <c r="Q25" s="211">
+        <f t="shared" si="3"/>
+        <v>5099.5203472953717</v>
       </c>
     </row>
     <row r="26" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="210">
         <f>SUM('10QIS'!C16:F16)</f>
         <v>2483.6000000000004</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="210">
         <f>SUM('10QIS'!G16:J16)</f>
         <v>3863.2999999999997</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="210">
         <f>SUM('10QIS'!K16:N16)</f>
         <v>5306.5</v>
       </c>
@@ -8778,31 +8804,31 @@
         <f>SUM('10QIS'!O16:R16)</f>
         <v>5722.4</v>
       </c>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
+      <c r="G26" s="210"/>
+      <c r="H26" s="210"/>
+      <c r="I26" s="210"/>
+      <c r="J26" s="210"/>
+      <c r="K26" s="210"/>
+      <c r="L26" s="210"/>
+      <c r="M26" s="210"/>
+      <c r="N26" s="210"/>
+      <c r="O26" s="210"/>
+      <c r="P26" s="210"/>
+      <c r="Q26" s="210"/>
     </row>
     <row r="27" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="210">
         <f>SUM('10QIS'!C17:F17)</f>
         <v>971.5</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="210">
         <f>SUM('10QIS'!G17:J17)</f>
         <v>974.80000000000007</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="210">
         <f>SUM('10QIS'!K17:N17)</f>
         <v>973.4</v>
       </c>
@@ -8810,31 +8836,31 @@
         <f>SUM('10QIS'!O17:R17)</f>
         <v>982.7</v>
       </c>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
+      <c r="G27" s="210"/>
+      <c r="H27" s="210"/>
+      <c r="I27" s="210"/>
+      <c r="J27" s="210"/>
+      <c r="K27" s="210"/>
+      <c r="L27" s="210"/>
+      <c r="M27" s="210"/>
+      <c r="N27" s="210"/>
+      <c r="O27" s="210"/>
+      <c r="P27" s="210"/>
+      <c r="Q27" s="210"/>
     </row>
     <row r="28" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="210">
         <f>SUM('10QIS'!C18:F18)</f>
         <v>408.4</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="210">
         <f>SUM('10QIS'!G18:J18)</f>
         <v>596.5</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="210">
         <f>SUM('10QIS'!K18:N18)</f>
         <v>627.4</v>
       </c>
@@ -8842,31 +8868,31 @@
         <f>SUM('10QIS'!O18:R18)</f>
         <v>706.3</v>
       </c>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="210"/>
+      <c r="M28" s="210"/>
+      <c r="N28" s="210"/>
+      <c r="O28" s="210"/>
+      <c r="P28" s="210"/>
+      <c r="Q28" s="210"/>
     </row>
     <row r="29" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="210">
         <f>SUM('10QIS'!C19:F19)</f>
         <v>64.599999999999994</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="210">
         <f>SUM('10QIS'!G19:J19)</f>
         <v>253.60000000000002</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="210">
         <f>SUM('10QIS'!K19:N19)</f>
         <v>364.4</v>
       </c>
@@ -8874,31 +8900,31 @@
         <f>SUM('10QIS'!O19:R19)</f>
         <v>445.3</v>
       </c>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
+      <c r="G29" s="210"/>
+      <c r="H29" s="210"/>
+      <c r="I29" s="210"/>
+      <c r="J29" s="210"/>
+      <c r="K29" s="210"/>
+      <c r="L29" s="210"/>
+      <c r="M29" s="210"/>
+      <c r="N29" s="210"/>
+      <c r="O29" s="210"/>
+      <c r="P29" s="210"/>
+      <c r="Q29" s="210"/>
     </row>
     <row r="30" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="210">
         <f>SUM('10QIS'!C20:F20)</f>
         <v>293.39999999999998</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="210">
         <f>SUM('10QIS'!G20:J20)</f>
         <v>393.29999999999995</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="210">
         <f>SUM('10QIS'!K20:N20)</f>
         <v>525.9</v>
       </c>
@@ -8906,31 +8932,31 @@
         <f>SUM('10QIS'!O20:R20)</f>
         <v>552.6</v>
       </c>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="26"/>
+      <c r="G30" s="210"/>
+      <c r="H30" s="210"/>
+      <c r="I30" s="210"/>
+      <c r="J30" s="210"/>
+      <c r="K30" s="210"/>
+      <c r="L30" s="210"/>
+      <c r="M30" s="210"/>
+      <c r="N30" s="210"/>
+      <c r="O30" s="210"/>
+      <c r="P30" s="210"/>
+      <c r="Q30" s="210"/>
     </row>
     <row r="31" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="210">
         <f>SUM('10QIS'!C21:F21)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="210">
         <f>SUM('10QIS'!G21:J21)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="210">
         <f>SUM('10QIS'!K21:N21)</f>
         <v>337.1</v>
       </c>
@@ -8938,31 +8964,31 @@
         <f>SUM('10QIS'!O21:R21)</f>
         <v>511.1</v>
       </c>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
+      <c r="G31" s="210"/>
+      <c r="H31" s="210"/>
+      <c r="I31" s="210"/>
+      <c r="J31" s="210"/>
+      <c r="K31" s="210"/>
+      <c r="L31" s="210"/>
+      <c r="M31" s="210"/>
+      <c r="N31" s="210"/>
+      <c r="O31" s="210"/>
+      <c r="P31" s="210"/>
+      <c r="Q31" s="210"/>
     </row>
     <row r="32" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="210">
         <f>SUM('10QIS'!C22:F22)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="210">
         <f>SUM('10QIS'!G22:J22)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="210">
         <f>SUM('10QIS'!K22:N22)</f>
         <v>0</v>
       </c>
@@ -8970,80 +8996,80 @@
         <f>SUM('10QIS'!O22:R22)</f>
         <v>45</v>
       </c>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
+      <c r="G32" s="210"/>
+      <c r="H32" s="210"/>
+      <c r="I32" s="210"/>
+      <c r="J32" s="210"/>
+      <c r="K32" s="210"/>
+      <c r="L32" s="210"/>
+      <c r="M32" s="210"/>
+      <c r="N32" s="210"/>
+      <c r="O32" s="210"/>
+      <c r="P32" s="210"/>
+      <c r="Q32" s="210"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="211">
         <f>SUM('10QIS'!C23:F23)</f>
         <v>3312.5</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="211">
         <f>SUM('10QIS'!G23:J23)</f>
         <v>3682.3999999999996</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="211">
         <f>SUM('10QIS'!K23:N23)</f>
         <v>4393</v>
       </c>
-      <c r="F33" s="51">
+      <c r="F33" s="212">
         <f>SUM('10QIS'!O23:R23)</f>
         <v>5241.6000000000004</v>
       </c>
-      <c r="G33" s="26">
-        <f>F33*(1+G5)</f>
+      <c r="G33" s="211">
+        <f t="shared" ref="G33:Q33" si="4">F33*(1+G5)</f>
         <v>6027.84</v>
       </c>
-      <c r="H33" s="26">
-        <f>G33*(1+H5)</f>
+      <c r="H33" s="211">
+        <f t="shared" si="4"/>
         <v>6831.3510720000004</v>
       </c>
-      <c r="I33" s="26">
-        <f>H33*(1+I5)</f>
+      <c r="I33" s="211">
+        <f t="shared" si="4"/>
         <v>7628.5697421024006</v>
       </c>
-      <c r="J33" s="26">
-        <f>I33*(1+J5)</f>
+      <c r="J33" s="211">
+        <f t="shared" si="4"/>
         <v>8391.4267163126406</v>
       </c>
-      <c r="K33" s="26">
-        <f>J33*(1+K5)</f>
+      <c r="K33" s="211">
+        <f t="shared" si="4"/>
         <v>9090.4325617814829</v>
       </c>
-      <c r="L33" s="26">
-        <f>K33*(1+L5)</f>
+      <c r="L33" s="211">
+        <f t="shared" si="4"/>
         <v>9696.7644136523086</v>
       </c>
-      <c r="M33" s="26">
-        <f>L33*(1+M5)</f>
+      <c r="M33" s="211">
+        <f t="shared" si="4"/>
         <v>10181.602634334924</v>
       </c>
-      <c r="N33" s="26">
-        <f>M33*(1+N5)</f>
+      <c r="N33" s="211">
+        <f t="shared" si="4"/>
         <v>10690.68276605167</v>
       </c>
-      <c r="O33" s="26">
-        <f>N33*(1+O5)</f>
+      <c r="O33" s="211">
+        <f t="shared" si="4"/>
         <v>11225.216904354254</v>
       </c>
-      <c r="P33" s="26">
-        <f>O33*(1+P5)</f>
+      <c r="P33" s="211">
+        <f t="shared" si="4"/>
         <v>11786.477749571968</v>
       </c>
-      <c r="Q33" s="26">
-        <f>P33*(1+Q5)</f>
+      <c r="Q33" s="211">
+        <f t="shared" si="4"/>
         <v>12375.801637050567</v>
       </c>
     </row>
@@ -9051,15 +9077,15 @@
       <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="210">
         <f>SUM('10QIS'!C24:F24)</f>
         <v>0</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="210">
         <f>SUM('10QIS'!G24:J24)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="210">
         <f>SUM('10QIS'!K24:N24)</f>
         <v>42.7</v>
       </c>
@@ -9067,31 +9093,31 @@
         <f>SUM('10QIS'!O24:R24)</f>
         <v>406.20000000000005</v>
       </c>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
+      <c r="G34" s="210"/>
+      <c r="H34" s="210"/>
+      <c r="I34" s="210"/>
+      <c r="J34" s="210"/>
+      <c r="K34" s="210"/>
+      <c r="L34" s="210"/>
+      <c r="M34" s="210"/>
+      <c r="N34" s="210"/>
+      <c r="O34" s="210"/>
+      <c r="P34" s="210"/>
+      <c r="Q34" s="210"/>
     </row>
     <row r="35" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="210">
         <f>SUM('10QIS'!C25:F25)</f>
         <v>830.5</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="210">
         <f>SUM('10QIS'!G25:J25)</f>
         <v>922.7</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="210">
         <f>SUM('10QIS'!K25:N25)</f>
         <v>957.50000000000011</v>
       </c>
@@ -9099,31 +9125,31 @@
         <f>SUM('10QIS'!O25:R25)</f>
         <v>1005.6</v>
       </c>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="26"/>
+      <c r="G35" s="210"/>
+      <c r="H35" s="210"/>
+      <c r="I35" s="210"/>
+      <c r="J35" s="210"/>
+      <c r="K35" s="210"/>
+      <c r="L35" s="210"/>
+      <c r="M35" s="210"/>
+      <c r="N35" s="210"/>
+      <c r="O35" s="210"/>
+      <c r="P35" s="210"/>
+      <c r="Q35" s="210"/>
     </row>
     <row r="36" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="210">
         <f>SUM('10QIS'!C26:F26)</f>
         <v>0</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="210">
         <f>SUM('10QIS'!G26:J26)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="210">
         <f>SUM('10QIS'!K26:N26)</f>
         <v>132.4</v>
       </c>
@@ -9131,31 +9157,31 @@
         <f>SUM('10QIS'!O26:R26)</f>
         <v>266.8</v>
       </c>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
+      <c r="G36" s="210"/>
+      <c r="H36" s="210"/>
+      <c r="I36" s="210"/>
+      <c r="J36" s="210"/>
+      <c r="K36" s="210"/>
+      <c r="L36" s="210"/>
+      <c r="M36" s="210"/>
+      <c r="N36" s="210"/>
+      <c r="O36" s="210"/>
+      <c r="P36" s="210"/>
+      <c r="Q36" s="210"/>
     </row>
     <row r="37" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="210">
         <f>SUM('10QIS'!C27:F27)</f>
         <v>2482</v>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="210">
         <f>SUM('10QIS'!G27:J27)</f>
         <v>2759.7000000000003</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="210">
         <f>SUM('10QIS'!K27:N27)</f>
         <v>3260.4</v>
       </c>
@@ -9163,81 +9189,81 @@
         <f>SUM('10QIS'!O27:R27)</f>
         <v>3563</v>
       </c>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
+      <c r="G37" s="210"/>
+      <c r="H37" s="210"/>
+      <c r="I37" s="210"/>
+      <c r="J37" s="210"/>
+      <c r="K37" s="210"/>
+      <c r="L37" s="210"/>
+      <c r="M37" s="210"/>
+      <c r="N37" s="210"/>
+      <c r="O37" s="210"/>
+      <c r="P37" s="210"/>
+      <c r="Q37" s="210"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B38" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="211">
         <f>SUM('10QIS'!C28:F28)</f>
         <v>650.9</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="211">
         <f>SUM('10QIS'!G28:J28)</f>
         <v>678.2</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="211">
         <f>SUM('10QIS'!K28:N28)</f>
         <v>879.7</v>
       </c>
-      <c r="F38" s="51">
+      <c r="F38" s="212">
         <f>SUM('10QIS'!O28:R28)</f>
         <v>1012.08</v>
       </c>
-      <c r="G38" s="26">
-        <f>F38*(1+G6)</f>
-        <v>1315.7040000000002</v>
-      </c>
-      <c r="H38" s="26">
-        <f>G38*(1+H6)</f>
-        <v>1662.1288632000003</v>
-      </c>
-      <c r="I38" s="26">
-        <f>H38*(1+I6)</f>
-        <v>2038.9334764874407</v>
-      </c>
-      <c r="J38" s="26">
-        <f>I38*(1+J6)</f>
-        <v>2426.3308370200543</v>
-      </c>
-      <c r="K38" s="26">
-        <f>J38*(1+K6)</f>
-        <v>2798.2873543352284</v>
-      </c>
-      <c r="L38" s="26">
-        <f>K38*(1+L6)</f>
-        <v>3124.8474885861497</v>
-      </c>
-      <c r="M38" s="26">
-        <f>L38*(1+M6)</f>
-        <v>3374.8352876730419</v>
-      </c>
-      <c r="N38" s="26">
-        <f>M38*(1+N6)</f>
-        <v>3644.8221106868855</v>
-      </c>
-      <c r="O38" s="26">
-        <f>N38*(1+O6)</f>
-        <v>3936.4078795418368</v>
-      </c>
-      <c r="P38" s="26">
-        <f>O38*(1+P6)</f>
-        <v>4251.3205099051838</v>
-      </c>
-      <c r="Q38" s="26">
-        <f>P38*(1+Q6)</f>
-        <v>4591.426150697599</v>
+      <c r="G38" s="211">
+        <f t="shared" ref="G38:Q38" si="5">F38*(1+G6)</f>
+        <v>1518.1200000000001</v>
+      </c>
+      <c r="H38" s="211">
+        <f t="shared" si="5"/>
+        <v>1897.65</v>
+      </c>
+      <c r="I38" s="211">
+        <f t="shared" si="5"/>
+        <v>2277.1799999999998</v>
+      </c>
+      <c r="J38" s="211">
+        <f t="shared" si="5"/>
+        <v>2709.8441999999995</v>
+      </c>
+      <c r="K38" s="211">
+        <f t="shared" si="5"/>
+        <v>3125.2633158599992</v>
+      </c>
+      <c r="L38" s="211">
+        <f t="shared" si="5"/>
+        <v>3489.981544820861</v>
+      </c>
+      <c r="M38" s="211">
+        <f t="shared" si="5"/>
+        <v>3769.1800684065302</v>
+      </c>
+      <c r="N38" s="211">
+        <f t="shared" si="5"/>
+        <v>4070.714473879053</v>
+      </c>
+      <c r="O38" s="211">
+        <f t="shared" si="5"/>
+        <v>4396.3716317893777</v>
+      </c>
+      <c r="P38" s="211">
+        <f t="shared" si="5"/>
+        <v>4748.0813623325284</v>
+      </c>
+      <c r="Q38" s="211">
+        <f t="shared" si="5"/>
+        <v>5127.9278713191306</v>
       </c>
     </row>
     <row r="39" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
@@ -9325,47 +9351,47 @@
         <v>2049.5199999999986</v>
       </c>
       <c r="G41" s="26">
-        <f>F41*(1+G7)</f>
+        <f t="shared" ref="G41:Q41" si="6">F41*(1+G7)</f>
         <v>2008.5295999999987</v>
       </c>
       <c r="H41" s="26">
-        <f>G41*(1+H7)</f>
+        <f t="shared" si="6"/>
         <v>1968.3590079999988</v>
       </c>
       <c r="I41" s="26">
-        <f>H41*(1+I7)</f>
+        <f t="shared" si="6"/>
         <v>1928.9918278399987</v>
       </c>
       <c r="J41" s="26">
-        <f>I41*(1+J7)</f>
+        <f t="shared" si="6"/>
         <v>1890.4119912831986</v>
       </c>
       <c r="K41" s="26">
-        <f>J41*(1+K7)</f>
+        <f t="shared" si="6"/>
         <v>1852.6037514575346</v>
       </c>
       <c r="L41" s="26">
-        <f>K41*(1+L7)</f>
+        <f t="shared" si="6"/>
         <v>1815.5516764283839</v>
       </c>
       <c r="M41" s="26">
-        <f>L41*(1+M7)</f>
+        <f t="shared" si="6"/>
         <v>1779.2406428998161</v>
       </c>
       <c r="N41" s="26">
-        <f>M41*(1+N7)</f>
+        <f t="shared" si="6"/>
         <v>1743.6558300418196</v>
       </c>
       <c r="O41" s="26">
-        <f>N41*(1+O7)</f>
+        <f t="shared" si="6"/>
         <v>1708.7827134409831</v>
       </c>
       <c r="P41" s="26">
-        <f>O41*(1+P7)</f>
+        <f t="shared" si="6"/>
         <v>1674.6070591721634</v>
       </c>
       <c r="Q41" s="26">
-        <f>P41*(1+Q7)</f>
+        <f t="shared" si="6"/>
         <v>1641.1149179887202</v>
       </c>
     </row>
@@ -9374,64 +9400,64 @@
         <v>63</v>
       </c>
       <c r="C42" s="31">
-        <f>C15+C25+C33+C38+C41</f>
+        <f t="shared" ref="C42:Q42" si="7">C15+C25+C33+C38+C41</f>
         <v>28541.400000000005</v>
       </c>
       <c r="D42" s="31">
-        <f>D15+D25+D33+D38+D41</f>
+        <f t="shared" si="7"/>
         <v>34124.100000000006</v>
       </c>
       <c r="E42" s="31">
-        <f>E15+E25+E33+E38+E41</f>
+        <f t="shared" si="7"/>
         <v>45042.69999999999</v>
       </c>
       <c r="F42" s="52">
-        <f>F15+F25+F33+F38+F41</f>
+        <f t="shared" si="7"/>
         <v>65179.500000000007</v>
       </c>
       <c r="G42" s="31">
-        <f>G15+G25+G33+G38+G41</f>
-        <v>87634.083599999998</v>
+        <f t="shared" si="7"/>
+        <v>89937.969599999997</v>
       </c>
       <c r="H42" s="31">
-        <f>H15+H25+H33+H38+H41</f>
-        <v>114091.96801020001</v>
+        <f t="shared" si="7"/>
+        <v>112214.88858</v>
       </c>
       <c r="I42" s="31">
-        <f>I15+I25+I33+I38+I41</f>
-        <v>143221.51440561094</v>
+        <f t="shared" si="7"/>
+        <v>131632.95739494238</v>
       </c>
       <c r="J42" s="31">
-        <f>J15+J25+J33+J38+J41</f>
-        <v>172738.72366840087</v>
+        <f t="shared" si="7"/>
+        <v>143616.71384134586</v>
       </c>
       <c r="K42" s="31">
-        <f>K15+K25+K33+K38+K41</f>
-        <v>199521.23197719833</v>
+        <f t="shared" si="7"/>
+        <v>150494.34467616153</v>
       </c>
       <c r="L42" s="31">
-        <f>L15+L25+L33+L38+L41</f>
-        <v>220019.03278338746</v>
+        <f t="shared" si="7"/>
+        <v>157555.91937261095</v>
       </c>
       <c r="M42" s="31">
-        <f>M15+M25+M33+M38+M41</f>
-        <v>230986.64122986447</v>
+        <f t="shared" si="7"/>
+        <v>164752.28688661524</v>
       </c>
       <c r="N42" s="31">
-        <f>N15+N25+N33+N38+N41</f>
-        <v>242512.67150498487</v>
+        <f t="shared" si="7"/>
+        <v>172352.34246855529</v>
       </c>
       <c r="O42" s="31">
-        <f>O15+O25+O33+O38+O41</f>
-        <v>254625.59383545179</v>
+        <f t="shared" si="7"/>
+        <v>180375.24216462861</v>
       </c>
       <c r="P42" s="31">
-        <f>P15+P25+P33+P38+P41</f>
-        <v>267355.35097366979</v>
+        <f t="shared" si="7"/>
+        <v>188841.23682607836</v>
       </c>
       <c r="Q42" s="31">
-        <f>Q15+Q25+Q33+Q38+Q41</f>
-        <v>280733.43564350833</v>
+        <f t="shared" si="7"/>
+        <v>197771.72699860542</v>
       </c>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
@@ -9455,48 +9481,48 @@
         <v>11052.8</v>
       </c>
       <c r="G43" s="26">
-        <f>G42*(1-$G$8)</f>
-        <v>17110.341989433731</v>
+        <f t="shared" ref="G43:Q43" si="8">G42*(1-$G$8)</f>
+        <v>17560.170135576045</v>
       </c>
       <c r="H43" s="26">
-        <f>H42*(1-$G$8)</f>
-        <v>22276.179663297757</v>
+        <f t="shared" si="8"/>
+        <v>21909.684463340491</v>
       </c>
       <c r="I43" s="26">
-        <f>I42*(1-$G$8)</f>
-        <v>27963.652851213395</v>
+        <f t="shared" si="8"/>
+        <v>25701.015239554854</v>
       </c>
       <c r="J43" s="26">
-        <f>J42*(1-$G$8)</f>
-        <v>33726.816272483164</v>
+        <f t="shared" si="8"/>
+        <v>28040.814581235249</v>
       </c>
       <c r="K43" s="26">
-        <f>K42*(1-$G$8)</f>
-        <v>38956.035974146995</v>
+        <f t="shared" si="8"/>
+        <v>29383.655298300393</v>
       </c>
       <c r="L43" s="26">
-        <f>L42*(1-$G$8)</f>
-        <v>42958.181799349484</v>
+        <f t="shared" si="8"/>
+        <v>30762.410607612273</v>
       </c>
       <c r="M43" s="26">
-        <f>M42*(1-$G$8)</f>
-        <v>45099.580711923081</v>
+        <f t="shared" si="8"/>
+        <v>32167.483887185706</v>
       </c>
       <c r="N43" s="26">
-        <f>N42*(1-$G$8)</f>
-        <v>47350.01013032208</v>
+        <f t="shared" si="8"/>
+        <v>33651.376281602199</v>
       </c>
       <c r="O43" s="26">
-        <f>O42*(1-$G$8)</f>
-        <v>49715.028797165738</v>
+        <f t="shared" si="8"/>
+        <v>35217.827962358278</v>
       </c>
       <c r="P43" s="26">
-        <f>P42*(1-$G$8)</f>
-        <v>52200.482962140253</v>
+        <f t="shared" si="8"/>
+        <v>36870.792858976711</v>
       </c>
       <c r="Q43" s="26">
-        <f>Q42*(1-$G$8)</f>
-        <v>54812.521503096003</v>
+        <f t="shared" si="8"/>
+        <v>38614.449376030941</v>
       </c>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
@@ -9520,48 +9546,48 @@
         <v>54126.7</v>
       </c>
       <c r="G44" s="31">
-        <f>G42*($G$8)</f>
-        <v>70523.741610566271</v>
+        <f t="shared" ref="G44:Q44" si="9">G42*($G$8)</f>
+        <v>72377.799464423952</v>
       </c>
       <c r="H44" s="31">
-        <f>H42*($G$8)</f>
-        <v>91815.788346902264</v>
+        <f t="shared" si="9"/>
+        <v>90305.204116659501</v>
       </c>
       <c r="I44" s="31">
-        <f>I42*($G$8)</f>
-        <v>115257.86155439755</v>
+        <f t="shared" si="9"/>
+        <v>105931.94215538753</v>
       </c>
       <c r="J44" s="31">
-        <f>J42*($G$8)</f>
-        <v>139011.90739591772</v>
+        <f t="shared" si="9"/>
+        <v>115575.89926011061</v>
       </c>
       <c r="K44" s="31">
-        <f>K42*($G$8)</f>
-        <v>160565.19600305133</v>
+        <f t="shared" si="9"/>
+        <v>121110.68937786114</v>
       </c>
       <c r="L44" s="31">
-        <f>L42*($G$8)</f>
-        <v>177060.85098403797</v>
+        <f t="shared" si="9"/>
+        <v>126793.50876499868</v>
       </c>
       <c r="M44" s="31">
-        <f>M42*($G$8)</f>
-        <v>185887.0605179414</v>
+        <f t="shared" si="9"/>
+        <v>132584.80299942952</v>
       </c>
       <c r="N44" s="31">
-        <f>N42*($G$8)</f>
-        <v>195162.6613746628</v>
+        <f t="shared" si="9"/>
+        <v>138700.9661869531</v>
       </c>
       <c r="O44" s="31">
-        <f>O42*($G$8)</f>
-        <v>204910.56503828606</v>
+        <f t="shared" si="9"/>
+        <v>145157.41420227033</v>
       </c>
       <c r="P44" s="31">
-        <f>P42*($G$8)</f>
-        <v>215154.86801152953</v>
+        <f t="shared" si="9"/>
+        <v>151970.44396710163</v>
       </c>
       <c r="Q44" s="31">
-        <f>Q42*($G$8)</f>
-        <v>225920.91414041232</v>
+        <f t="shared" si="9"/>
+        <v>159157.27762257447</v>
       </c>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
@@ -9585,48 +9611,48 @@
         <v>13337.3</v>
       </c>
       <c r="G45" s="26">
-        <f>G$42*G9</f>
-        <v>20773.410124291451</v>
+        <f t="shared" ref="G45:Q45" si="10">G$42*G9</f>
+        <v>21319.53974408716</v>
       </c>
       <c r="H45" s="26">
-        <f>H$42*H9</f>
-        <v>27045.176328670201</v>
+        <f t="shared" si="10"/>
+        <v>26600.219991619895</v>
       </c>
       <c r="I45" s="26">
-        <f>I$42*I9</f>
-        <v>33950.252403505161</v>
+        <f t="shared" si="10"/>
+        <v>31203.217943372449</v>
       </c>
       <c r="J45" s="26">
-        <f>J$42*J9</f>
-        <v>40947.222857823574</v>
+        <f t="shared" si="10"/>
+        <v>34043.933305069469</v>
       </c>
       <c r="K45" s="26">
-        <f>K$42*K9</f>
-        <v>47295.940233535293</v>
+        <f t="shared" si="10"/>
+        <v>35674.256121785715</v>
       </c>
       <c r="L45" s="26">
-        <f>L$42*L9</f>
-        <v>52154.885581062139</v>
+        <f t="shared" si="10"/>
+        <v>37348.182307426374</v>
       </c>
       <c r="M45" s="26">
-        <f>M$42*M9</f>
-        <v>54754.725951177104</v>
+        <f t="shared" si="10"/>
+        <v>39054.060746868847</v>
       </c>
       <c r="N45" s="26">
-        <f>N$42*N9</f>
-        <v>57486.938626589574</v>
+        <f t="shared" si="10"/>
+        <v>40855.632293981493</v>
       </c>
       <c r="O45" s="26">
-        <f>O$42*O9</f>
-        <v>60358.27239351764</v>
+        <f t="shared" si="10"/>
+        <v>42757.437835000288</v>
       </c>
       <c r="P45" s="26">
-        <f>P$42*P9</f>
-        <v>63375.825096206361</v>
+        <f t="shared" si="10"/>
+        <v>44764.277776581621</v>
       </c>
       <c r="Q45" s="26">
-        <f>Q$42*Q9</f>
-        <v>66547.061995225551</v>
+        <f t="shared" si="10"/>
+        <v>46881.225057181233</v>
       </c>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.25">
@@ -9650,48 +9676,48 @@
         <v>11093.1</v>
       </c>
       <c r="G46" s="26">
-        <f>G$42*G10</f>
-        <v>17260.155724164855</v>
+        <f t="shared" ref="G46:Q46" si="11">G$42*G10</f>
+        <v>17713.922449360838</v>
       </c>
       <c r="H46" s="26">
-        <f>H$42*H10</f>
-        <v>22471.224138327008</v>
+        <f t="shared" si="11"/>
+        <v>22101.520001067351</v>
       </c>
       <c r="I46" s="26">
-        <f>I$42*I10</f>
-        <v>28208.495372359492</v>
+        <f t="shared" si="11"/>
+        <v>25926.046690229359</v>
       </c>
       <c r="J46" s="26">
-        <f>J$42*J10</f>
-        <v>34022.119563877997</v>
+        <f t="shared" si="11"/>
+        <v>28286.332710557966</v>
       </c>
       <c r="K46" s="26">
-        <f>K$42*K10</f>
-        <v>39297.124962503331</v>
+        <f t="shared" si="11"/>
+        <v>29640.930994076007</v>
       </c>
       <c r="L46" s="26">
-        <f>L$42*L10</f>
-        <v>43334.312542767315</v>
+        <f t="shared" si="11"/>
+        <v>31031.758328733493</v>
       </c>
       <c r="M46" s="26">
-        <f>M$42*M10</f>
-        <v>45494.460991080174</v>
+        <f t="shared" si="11"/>
+        <v>32449.134067002011</v>
       </c>
       <c r="N46" s="26">
-        <f>N$42*N10</f>
-        <v>47764.594588164044</v>
+        <f t="shared" si="11"/>
+        <v>33946.019039923594</v>
       </c>
       <c r="O46" s="26">
-        <f>O$42*O10</f>
-        <v>50150.320747552702</v>
+        <f t="shared" si="11"/>
+        <v>35526.18616697027</v>
       </c>
       <c r="P46" s="26">
-        <f>P$42*P10</f>
-        <v>52657.536907184476</v>
+        <f t="shared" si="11"/>
+        <v>37193.62399725039</v>
       </c>
       <c r="Q46" s="26">
-        <f>Q$42*Q10</f>
-        <v>55292.445782895891</v>
+        <f t="shared" si="11"/>
+        <v>38952.547520368527</v>
       </c>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.25">
@@ -9715,48 +9741,48 @@
         <v>2909.5</v>
       </c>
       <c r="G47" s="26">
-        <f>G$42*G11</f>
-        <v>5711.5180372693967</v>
+        <f t="shared" ref="G47:Q47" si="12">G$42*G11</f>
+        <v>5861.6729302545782</v>
       </c>
       <c r="H47" s="26">
-        <f>H$42*H11</f>
-        <v>7435.9005814698839</v>
+        <f t="shared" si="12"/>
+        <v>7313.5626441907089</v>
       </c>
       <c r="I47" s="26">
-        <f>I$42*I11</f>
-        <v>9334.4076784832796</v>
+        <f t="shared" si="12"/>
+        <v>8579.1278869529651</v>
       </c>
       <c r="J47" s="26">
-        <f>J$42*J11</f>
-        <v>11258.180555298984</v>
+        <f t="shared" si="12"/>
+        <v>9360.1646512590942</v>
       </c>
       <c r="K47" s="26">
-        <f>K$42*K11</f>
-        <v>13003.720338509705</v>
+        <f t="shared" si="12"/>
+        <v>9808.4116226775295</v>
       </c>
       <c r="L47" s="26">
-        <f>L$42*L11</f>
-        <v>14339.656702759019</v>
+        <f t="shared" si="12"/>
+        <v>10268.647065252477</v>
       </c>
       <c r="M47" s="26">
-        <f>M$42*M11</f>
-        <v>15054.466408006643</v>
+        <f t="shared" si="12"/>
+        <v>10737.667578397377</v>
       </c>
       <c r="N47" s="26">
-        <f>N$42*N11</f>
-        <v>15805.671043350869</v>
+        <f t="shared" si="12"/>
+        <v>11232.99830769025</v>
       </c>
       <c r="O47" s="26">
-        <f>O$42*O11</f>
-        <v>16595.12614497876</v>
+        <f t="shared" si="12"/>
+        <v>11755.887741149514</v>
       </c>
       <c r="P47" s="26">
-        <f>P$42*P11</f>
-        <v>17424.783220379395</v>
+        <f t="shared" si="12"/>
+        <v>12307.655720295663</v>
       </c>
       <c r="Q47" s="26">
-        <f>Q$42*Q11</f>
-        <v>18296.694795842028</v>
+        <f t="shared" si="12"/>
+        <v>12889.697017547791</v>
       </c>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
@@ -9780,43 +9806,43 @@
         <v>484</v>
       </c>
       <c r="G48" s="26">
-        <f>AVERAGE(C48:F48)</f>
+        <f t="shared" ref="G48:Q48" si="13">AVERAGE(C48:F48)</f>
         <v>414.22500000000002</v>
       </c>
       <c r="H48" s="26">
-        <f>AVERAGE(D48:G48)</f>
+        <f t="shared" si="13"/>
         <v>456.63125000000002</v>
       </c>
       <c r="I48" s="26">
-        <f>AVERAGE(E48:H48)</f>
+        <f t="shared" si="13"/>
         <v>553.86406249999993</v>
       </c>
       <c r="J48" s="26">
-        <f>AVERAGE(F48:I48)</f>
+        <f t="shared" si="13"/>
         <v>477.18007812500002</v>
       </c>
       <c r="K48" s="26">
-        <f>AVERAGE(G48:J48)</f>
+        <f t="shared" si="13"/>
         <v>475.47509765625</v>
       </c>
       <c r="L48" s="26">
-        <f>AVERAGE(H48:K48)</f>
+        <f t="shared" si="13"/>
         <v>490.78762207031252</v>
       </c>
       <c r="M48" s="26">
-        <f>AVERAGE(I48:L48)</f>
+        <f t="shared" si="13"/>
         <v>499.32671508789065</v>
       </c>
       <c r="N48" s="26">
-        <f>AVERAGE(J48:M48)</f>
+        <f t="shared" si="13"/>
         <v>485.69237823486333</v>
       </c>
       <c r="O48" s="26">
-        <f>AVERAGE(K48:N48)</f>
+        <f t="shared" si="13"/>
         <v>487.82045326232912</v>
       </c>
       <c r="P48" s="26">
-        <f>AVERAGE(L48:O48)</f>
+        <f t="shared" si="13"/>
         <v>490.90679216384888</v>
       </c>
       <c r="Q48" s="26">
@@ -9850,43 +9876,43 @@
       </c>
       <c r="H49" s="26">
         <f>(BS!G29+BS!G35)*CFS!H11</f>
-        <v>766.17627898379146</v>
+        <v>771.27782793175697</v>
       </c>
       <c r="I49" s="26">
         <f>(BS!H29+BS!H35)*CFS!I11</f>
-        <v>975.59270347918562</v>
+        <v>977.79788870296375</v>
       </c>
       <c r="J49" s="26">
         <f>(BS!I29+BS!I35)*CFS!J11</f>
-        <v>1173.8169754080386</v>
+        <v>1159.9747329602515</v>
       </c>
       <c r="K49" s="26">
         <f>(BS!J29+BS!J35)*CFS!K11</f>
-        <v>1334.9128491612373</v>
+        <v>1293.5779996167216</v>
       </c>
       <c r="L49" s="26">
         <f>(BS!K29+BS!K35)*CFS!L11</f>
-        <v>1430.6822835433795</v>
+        <v>1364.5984274672969</v>
       </c>
       <c r="M49" s="26">
         <f>(BS!L29+BS!L35)*CFS!M11</f>
-        <v>1367.5544877656507</v>
+        <v>1301.208751792537</v>
       </c>
       <c r="N49" s="26">
         <f>(BS!M29+BS!M35)*CFS!N11</f>
-        <v>1303.7994445524605</v>
+        <v>1238.4462429534265</v>
       </c>
       <c r="O49" s="26">
         <f>(BS!N29+BS!N35)*CFS!O11</f>
-        <v>1241.9501218794317</v>
+        <v>1178.8402110136324</v>
       </c>
       <c r="P49" s="26">
         <f>(BS!O29+BS!O35)*CFS!P11</f>
-        <v>1183.3246092179304</v>
+        <v>1122.3231404731869</v>
       </c>
       <c r="Q49" s="26">
         <f>(BS!P29+BS!P35)*CFS!Q11</f>
-        <v>1127.797981901758</v>
+        <v>1068.7479693248067</v>
       </c>
     </row>
     <row r="50" spans="2:17" x14ac:dyDescent="0.25">
@@ -9910,48 +9936,48 @@
         <v>25731.800000000003</v>
       </c>
       <c r="G50" s="26">
-        <f>G44-SUM(G45:G49)</f>
-        <v>25793.432724840575</v>
+        <f t="shared" ref="G50:Q50" si="14">G44-SUM(G45:G49)</f>
+        <v>26497.439340721379</v>
       </c>
       <c r="H50" s="26">
-        <f>H44-SUM(H45:H49)</f>
-        <v>33640.679769451388</v>
+        <f t="shared" si="14"/>
+        <v>33061.992401849791</v>
       </c>
       <c r="I50" s="26">
-        <f>I44-SUM(I45:I49)</f>
-        <v>42235.249334070439</v>
+        <f t="shared" si="14"/>
+        <v>38691.8876836298</v>
       </c>
       <c r="J50" s="26">
-        <f>J44-SUM(J45:J49)</f>
-        <v>51133.387365384115</v>
+        <f t="shared" si="14"/>
+        <v>42248.313782138823</v>
       </c>
       <c r="K50" s="26">
-        <f>K44-SUM(K45:K49)</f>
-        <v>59158.022521685503</v>
+        <f t="shared" si="14"/>
+        <v>44218.037542048914</v>
       </c>
       <c r="L50" s="26">
-        <f>L44-SUM(L45:L49)</f>
-        <v>65310.526251835792</v>
+        <f t="shared" si="14"/>
+        <v>46289.535014048728</v>
       </c>
       <c r="M50" s="26">
-        <f>M44-SUM(M45:M49)</f>
-        <v>68716.52596482393</v>
+        <f t="shared" si="14"/>
+        <v>48543.405140280855</v>
       </c>
       <c r="N50" s="26">
-        <f>N44-SUM(N45:N49)</f>
-        <v>72315.965293770991</v>
+        <f t="shared" si="14"/>
+        <v>50942.17792416946</v>
       </c>
       <c r="O50" s="26">
-        <f>O44-SUM(O45:O49)</f>
-        <v>76077.075177095205</v>
+        <f t="shared" si="14"/>
+        <v>53451.24179487428</v>
       </c>
       <c r="P50" s="26">
-        <f>P44-SUM(P45:P49)</f>
-        <v>80022.491386377515</v>
+        <f t="shared" si="14"/>
+        <v>56091.656540336917</v>
       </c>
       <c r="Q50" s="26">
-        <f>Q44-SUM(Q45:Q49)</f>
-        <v>84165.976999859849</v>
+        <f t="shared" si="14"/>
+        <v>58874.123473464875</v>
       </c>
     </row>
     <row r="51" spans="2:17" x14ac:dyDescent="0.25">
@@ -9975,48 +10001,48 @@
         <v>5091.3</v>
       </c>
       <c r="G51" s="26">
-        <f>G50*G12</f>
-        <v>5158.6865449681154</v>
+        <f t="shared" ref="G51:Q51" si="15">G50*G12</f>
+        <v>5034.5134747370621</v>
       </c>
       <c r="H51" s="26">
-        <f>H50*H12</f>
-        <v>6728.135953890278</v>
+        <f t="shared" si="15"/>
+        <v>6281.7785563514608</v>
       </c>
       <c r="I51" s="26">
-        <f>I50*I12</f>
-        <v>8447.0498668140881</v>
+        <f t="shared" si="15"/>
+        <v>7351.4586598896622</v>
       </c>
       <c r="J51" s="26">
-        <f>J50*J12</f>
-        <v>10226.677473076823</v>
+        <f t="shared" si="15"/>
+        <v>8027.1796186063766</v>
       </c>
       <c r="K51" s="26">
-        <f>K50*K12</f>
-        <v>11831.604504337101</v>
+        <f t="shared" si="15"/>
+        <v>8401.4271329892945</v>
       </c>
       <c r="L51" s="26">
-        <f>L50*L12</f>
-        <v>13062.10525036716</v>
+        <f t="shared" si="15"/>
+        <v>8795.0116526692582</v>
       </c>
       <c r="M51" s="26">
-        <f>M50*M12</f>
-        <v>13743.305192964786</v>
+        <f t="shared" si="15"/>
+        <v>9223.2469766533632</v>
       </c>
       <c r="N51" s="26">
-        <f>N50*N12</f>
-        <v>14463.193058754199</v>
+        <f t="shared" si="15"/>
+        <v>9679.013805592198</v>
       </c>
       <c r="O51" s="26">
-        <f>O50*O12</f>
-        <v>15215.415035419042</v>
+        <f t="shared" si="15"/>
+        <v>10155.735941026114</v>
       </c>
       <c r="P51" s="26">
-        <f>P50*P12</f>
-        <v>16004.498277275503</v>
+        <f t="shared" si="15"/>
+        <v>10657.414742664014</v>
       </c>
       <c r="Q51" s="26">
-        <f>Q50*Q12</f>
-        <v>16833.19539997197</v>
+        <f t="shared" si="15"/>
+        <v>11186.083459958327</v>
       </c>
     </row>
     <row r="52" spans="2:17" x14ac:dyDescent="0.25">
@@ -10040,48 +10066,48 @@
         <v>20640.5</v>
       </c>
       <c r="G52" s="31">
-        <f>G50-G51</f>
-        <v>20634.746179872462</v>
+        <f t="shared" ref="G52:Q52" si="16">G50-G51</f>
+        <v>21462.925865984318</v>
       </c>
       <c r="H52" s="31">
-        <f>H50-H51</f>
-        <v>26912.543815561112</v>
+        <f t="shared" si="16"/>
+        <v>26780.213845498329</v>
       </c>
       <c r="I52" s="31">
-        <f>I50-I51</f>
-        <v>33788.199467256352</v>
+        <f t="shared" si="16"/>
+        <v>31340.429023740136</v>
       </c>
       <c r="J52" s="31">
-        <f>J50-J51</f>
-        <v>40906.709892307292</v>
+        <f t="shared" si="16"/>
+        <v>34221.13416353245</v>
       </c>
       <c r="K52" s="31">
-        <f>K50-K51</f>
-        <v>47326.418017348406</v>
+        <f t="shared" si="16"/>
+        <v>35816.61040905962</v>
       </c>
       <c r="L52" s="31">
-        <f>L50-L51</f>
-        <v>52248.421001468632</v>
+        <f t="shared" si="16"/>
+        <v>37494.52336137947</v>
       </c>
       <c r="M52" s="31">
-        <f>M50-M51</f>
-        <v>54973.220771859145</v>
+        <f t="shared" si="16"/>
+        <v>39320.158163627493</v>
       </c>
       <c r="N52" s="31">
-        <f>N50-N51</f>
-        <v>57852.77223501679</v>
+        <f t="shared" si="16"/>
+        <v>41263.164118577261</v>
       </c>
       <c r="O52" s="31">
-        <f>O50-O51</f>
-        <v>60861.660141676162</v>
+        <f t="shared" si="16"/>
+        <v>43295.505853848168</v>
       </c>
       <c r="P52" s="31">
-        <f>P50-P51</f>
-        <v>64017.993109102012</v>
+        <f t="shared" si="16"/>
+        <v>45434.241797672905</v>
       </c>
       <c r="Q52" s="31">
-        <f>Q50-Q51</f>
-        <v>67332.78159988788</v>
+        <f t="shared" si="16"/>
+        <v>47688.04001350655</v>
       </c>
     </row>
     <row r="53" spans="2:17" x14ac:dyDescent="0.25">
@@ -10089,64 +10115,64 @@
         <v>74</v>
       </c>
       <c r="C53" s="6">
-        <f>C52/C54</f>
+        <f t="shared" ref="C53:Q53" si="17">C52/C54</f>
         <v>6.9178516197928897</v>
       </c>
       <c r="D53" s="6">
-        <f>D52/D54</f>
+        <f t="shared" si="17"/>
         <v>5.5428460536164792</v>
       </c>
       <c r="E53" s="6">
-        <f>E52/E54</f>
+        <f t="shared" si="17"/>
         <v>11.711252419131874</v>
       </c>
       <c r="F53" s="53">
-        <f>F52/F54</f>
+        <f t="shared" si="17"/>
         <v>22.951740242410764</v>
       </c>
       <c r="G53" s="6">
-        <f>G52/G54</f>
-        <v>23.061109260121519</v>
+        <f t="shared" si="17"/>
+        <v>23.986671516228547</v>
       </c>
       <c r="H53" s="6">
-        <f>H52/H54</f>
-        <v>29.971093953517581</v>
+        <f t="shared" si="17"/>
+        <v>29.823724979674065</v>
       </c>
       <c r="I53" s="6">
-        <f>I52/I54</f>
-        <v>37.628152421912525</v>
+        <f t="shared" si="17"/>
+        <v>34.902198367102997</v>
       </c>
       <c r="J53" s="6">
-        <f>J52/J54</f>
-        <v>45.555665563012738</v>
+        <f t="shared" si="17"/>
+        <v>38.110289173709504</v>
       </c>
       <c r="K53" s="6">
-        <f>K52/K54</f>
-        <v>52.70495909276508</v>
+        <f t="shared" si="17"/>
+        <v>39.887087709849787</v>
       </c>
       <c r="L53" s="6">
-        <f>L52/L54</f>
-        <v>58.186336657351333</v>
+        <f t="shared" si="17"/>
+        <v>41.755691699292242</v>
       </c>
       <c r="M53" s="6">
-        <f>M52/M54</f>
-        <v>61.152701231279984</v>
+        <f t="shared" si="17"/>
+        <v>43.740094736779007</v>
       </c>
       <c r="N53" s="6">
-        <f>N52/N54</f>
-        <v>64.284429396096215</v>
+        <f t="shared" si="17"/>
+        <v>45.850507382162633</v>
       </c>
       <c r="O53" s="6">
-        <f>O52/O54</f>
-        <v>67.552761131778851</v>
+        <f t="shared" si="17"/>
+        <v>48.055392478881366</v>
       </c>
       <c r="P53" s="6">
-        <f>P52/P54</f>
-        <v>70.97731926282168</v>
+        <f t="shared" si="17"/>
+        <v>50.373348630936199</v>
       </c>
       <c r="Q53" s="6">
-        <f>Q52/Q54</f>
-        <v>74.569778614417046</v>
+        <f t="shared" si="17"/>
+        <v>52.813599882060522</v>
       </c>
     </row>
     <row r="54" spans="2:17" x14ac:dyDescent="0.25">
@@ -10222,7 +10248,7 @@
     <row r="1" spans="2:17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>115</v>
@@ -10233,7 +10259,7 @@
       <c r="E2" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="F2" s="181" t="s">
+      <c r="F2" s="177" t="s">
         <v>118</v>
       </c>
       <c r="G2" s="22" t="s">
@@ -10856,7 +10882,7 @@
       </c>
     </row>
     <row r="12" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F12" s="206"/>
+      <c r="F12" s="199"/>
     </row>
     <row r="13" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="55" t="s">
@@ -10926,47 +10952,47 @@
       </c>
       <c r="G14" s="59">
         <f>CFS!G47</f>
-        <v>14581.700693774201</v>
+        <v>14579.427354502326</v>
       </c>
       <c r="H14" s="59">
         <f>CFS!H47</f>
-        <v>23809.272608289852</v>
+        <v>24729.365744129191</v>
       </c>
       <c r="I14" s="59">
         <f>CFS!I47</f>
-        <v>32159.311997256089</v>
+        <v>34167.978594879372</v>
       </c>
       <c r="J14" s="59">
         <f>CFS!J47</f>
-        <v>38343.788875923754</v>
+        <v>42096.906735780751</v>
       </c>
       <c r="K14" s="59">
         <f>CFS!K47</f>
-        <v>40948.786105848587</v>
+        <v>46754.857167099966</v>
       </c>
       <c r="L14" s="59">
         <f>CFS!L47</f>
-        <v>33743.519886339433</v>
+        <v>41516.48092142729</v>
       </c>
       <c r="M14" s="59">
         <f>CFS!M47</f>
-        <v>29131.952665518431</v>
+        <v>36503.896458904564</v>
       </c>
       <c r="N14" s="59">
         <f>CFS!N47</f>
-        <v>24843.532019142491</v>
+        <v>31858.303291926528</v>
       </c>
       <c r="O14" s="59">
         <f>CFS!O47</f>
-        <v>20977.309058564162</v>
+        <v>27573.840663875697</v>
       </c>
       <c r="P14" s="59">
         <f>CFS!P47</f>
-        <v>17530.481556622894</v>
+        <v>23644.767731937089</v>
       </c>
       <c r="Q14" s="59">
         <f>CFS!Q47</f>
-        <v>14500.688145699576</v>
+        <v>20067.68988143891</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
@@ -10987,47 +11013,47 @@
       </c>
       <c r="G15" s="59">
         <f>IS!G$42*BS!G3</f>
-        <v>23878.386988792485</v>
+        <v>24506.145952270264</v>
       </c>
       <c r="H15" s="59">
         <f>IS!H$42*BS!H3</f>
-        <v>31087.586616361768</v>
+        <v>30576.123185676472</v>
       </c>
       <c r="I15" s="59">
         <f>IS!I$42*BS!I3</f>
-        <v>39024.756186280196</v>
+        <v>35867.125757856018</v>
       </c>
       <c r="J15" s="59">
         <f>IS!J$42*BS!J3</f>
-        <v>47067.555479112278</v>
+        <v>39132.439460601905</v>
       </c>
       <c r="K15" s="59">
         <f>IS!K$42*BS!K3</f>
-        <v>54365.208077923911</v>
+        <v>41006.444686575203</v>
       </c>
       <c r="L15" s="59">
         <f>IS!L$42*BS!L3</f>
-        <v>59950.414198221231</v>
+        <v>42930.570625082582</v>
       </c>
       <c r="M15" s="59">
         <f>IS!M$42*BS!M3</f>
-        <v>62938.849611340869</v>
+        <v>44891.424682703706</v>
       </c>
       <c r="N15" s="59">
         <f>IS!N$42*BS!N3</f>
-        <v>66079.442860539435</v>
+        <v>46962.274982801973</v>
       </c>
       <c r="O15" s="59">
         <f>IS!O$42*BS!O3</f>
-        <v>69379.951465071426</v>
+        <v>49148.341132469621</v>
       </c>
       <c r="P15" s="59">
         <f>IS!P$42*BS!P3</f>
-        <v>72848.534175505716</v>
+        <v>51455.141049427366</v>
       </c>
       <c r="Q15" s="59">
         <f>IS!Q$42*BS!Q3</f>
-        <v>76493.772076016336</v>
+        <v>53888.505918198694</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
@@ -11048,47 +11074,47 @@
       </c>
       <c r="G16" s="59">
         <f>IS!G$42*BS!G4</f>
-        <v>3220.0865336800675</v>
+        <v>3304.7420920995091</v>
       </c>
       <c r="H16" s="59">
         <f>IS!H$42*BS!H4</f>
-        <v>4192.2730825555427</v>
+        <v>4123.3003958161689</v>
       </c>
       <c r="I16" s="59">
         <f>IS!I$42*BS!I4</f>
-        <v>5262.629001471907</v>
+        <v>4836.8111593505164</v>
       </c>
       <c r="J16" s="59">
         <f>IS!J$42*BS!J4</f>
-        <v>6347.2294691708285</v>
+        <v>5277.1504790620256</v>
       </c>
       <c r="K16" s="59">
         <f>IS!K$42*BS!K4</f>
-        <v>7331.3442199677802</v>
+        <v>5529.8668369565103</v>
       </c>
       <c r="L16" s="59">
         <f>IS!L$42*BS!L4</f>
-        <v>8084.5293921587754</v>
+        <v>5789.3421535513953</v>
       </c>
       <c r="M16" s="59">
         <f>IS!M$42*BS!M4</f>
-        <v>8487.5306767545826</v>
+        <v>6053.7703893623529</v>
       </c>
       <c r="N16" s="59">
         <f>IS!N$42*BS!N4</f>
-        <v>8911.0509938621599</v>
+        <v>6333.0320148542087</v>
       </c>
       <c r="O16" s="59">
         <f>IS!O$42*BS!O4</f>
-        <v>9356.1364729079996</v>
+        <v>6627.8309128527444</v>
       </c>
       <c r="P16" s="59">
         <f>IS!P$42*BS!P4</f>
-        <v>9823.8873508072174</v>
+        <v>6938.9111944469905</v>
       </c>
       <c r="Q16" s="59">
         <f>IS!Q$42*BS!Q4</f>
-        <v>10315.46081768351</v>
+        <v>7267.0592158832133</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -11109,47 +11135,47 @@
       </c>
       <c r="G17" s="59">
         <f>IS!G$43*BS!G5</f>
-        <v>21276.467528841309</v>
+        <v>21835.822447104551</v>
       </c>
       <c r="H17" s="59">
         <f>IS!H$43*BS!H5</f>
-        <v>27700.113391390816</v>
+        <v>27244.381809509963</v>
       </c>
       <c r="I17" s="59">
         <f>IS!I$43*BS!I5</f>
-        <v>34772.405615507108</v>
+        <v>31958.847844206168</v>
       </c>
       <c r="J17" s="59">
         <f>IS!J$43*BS!J5</f>
-        <v>41938.817571023508</v>
+        <v>34868.355132138218</v>
       </c>
       <c r="K17" s="59">
         <f>IS!K$43*BS!K5</f>
-        <v>48441.278085976075</v>
+        <v>36538.158513665374</v>
       </c>
       <c r="L17" s="59">
         <f>IS!L$43*BS!L5</f>
-        <v>53417.88964337176</v>
+        <v>38252.62118115076</v>
       </c>
       <c r="M17" s="59">
         <f>IS!M$43*BS!M5</f>
-        <v>56080.688812307366</v>
+        <v>39999.809871297803</v>
       </c>
       <c r="N17" s="59">
         <f>IS!N$43*BS!N5</f>
-        <v>58879.065868480997</v>
+        <v>41845.009012588729</v>
       </c>
       <c r="O17" s="59">
         <f>IS!O$43*BS!O5</f>
-        <v>61819.933029480853</v>
+        <v>43792.86945521969</v>
       </c>
       <c r="P17" s="59">
         <f>IS!P$43*BS!P5</f>
-        <v>64910.560023854203</v>
+        <v>45848.307854460043</v>
       </c>
       <c r="Q17" s="59">
         <f>IS!Q$43*BS!Q5</f>
-        <v>68158.592893977228</v>
+        <v>48016.519997120122</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
@@ -11170,47 +11196,47 @@
       </c>
       <c r="G18" s="59">
         <f>IS!G$42*BS!G6</f>
-        <v>19246.571494626376</v>
+        <v>19752.5607717764</v>
       </c>
       <c r="H18" s="59">
         <f>IS!H$42*BS!H6</f>
-        <v>25057.365000744299</v>
+        <v>24645.112804220651</v>
       </c>
       <c r="I18" s="59">
         <f>IS!I$42*BS!I6</f>
-        <v>31454.920315686995</v>
+        <v>28909.79196079442</v>
       </c>
       <c r="J18" s="59">
         <f>IS!J$42*BS!J6</f>
-        <v>37937.615804250694</v>
+        <v>31541.715702619163</v>
       </c>
       <c r="K18" s="59">
         <f>IS!K$42*BS!K6</f>
-        <v>43819.70459659239</v>
+        <v>33052.210342811042</v>
       </c>
       <c r="L18" s="59">
         <f>IS!L$42*BS!L6</f>
-        <v>48321.519101775732</v>
+        <v>34603.103519034754</v>
       </c>
       <c r="M18" s="59">
         <f>IS!M$42*BS!M6</f>
-        <v>50730.27208256445</v>
+        <v>36183.600469195022</v>
       </c>
       <c r="N18" s="59">
         <f>IS!N$42*BS!N6</f>
-        <v>53261.668048908905</v>
+        <v>37852.757115924003</v>
       </c>
       <c r="O18" s="59">
         <f>IS!O$42*BS!O6</f>
-        <v>55921.959753519004</v>
+        <v>39614.780591852628</v>
       </c>
       <c r="P18" s="59">
         <f>IS!P$42*BS!P6</f>
-        <v>58717.723351484477</v>
+        <v>41474.118475368967</v>
       </c>
       <c r="Q18" s="59">
         <f>IS!Q$42*BS!Q6</f>
-        <v>61655.875409244029</v>
+        <v>43435.470845665222</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
@@ -11231,47 +11257,47 @@
       </c>
       <c r="G19" s="59">
         <f>IS!G$42*BS!G7</f>
-        <v>197.6420544680459</v>
+        <v>202.83803237520996</v>
       </c>
       <c r="H19" s="59">
         <f>IS!H$42*BS!H7</f>
-        <v>257.31279462867002</v>
+        <v>253.07939798955186</v>
       </c>
       <c r="I19" s="59">
         <f>IS!I$42*BS!I7</f>
-        <v>323.0089616769813</v>
+        <v>296.87316927955146</v>
       </c>
       <c r="J19" s="59">
         <f>IS!J$42*BS!J7</f>
-        <v>389.57942879670634</v>
+        <v>323.90025904890092</v>
       </c>
       <c r="K19" s="59">
         <f>IS!K$42*BS!K7</f>
-        <v>449.98229659092425</v>
+        <v>339.41145095307178</v>
       </c>
       <c r="L19" s="59">
         <f>IS!L$42*BS!L7</f>
-        <v>496.21119860014193</v>
+        <v>355.33749334950107</v>
       </c>
       <c r="M19" s="59">
         <f>IS!M$42*BS!M7</f>
-        <v>520.94655928305792</v>
+        <v>371.56753538048673</v>
       </c>
       <c r="N19" s="59">
         <f>IS!N$42*BS!N7</f>
-        <v>546.94133448757304</v>
+        <v>388.70801928332713</v>
       </c>
       <c r="O19" s="59">
         <f>IS!O$42*BS!O7</f>
-        <v>574.2597334102195</v>
+        <v>406.80214788699516</v>
       </c>
       <c r="P19" s="59">
         <f>IS!P$42*BS!P7</f>
-        <v>602.96928624996281</v>
+        <v>425.89559314559813</v>
       </c>
       <c r="Q19" s="59">
         <f>IS!Q$42*BS!Q7</f>
-        <v>633.14101887243248</v>
+        <v>446.03661993103646</v>
       </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
@@ -11291,48 +11317,48 @@
         <v>55629</v>
       </c>
       <c r="G20" s="62">
-        <f>SUM(G14:G19)</f>
-        <v>82400.855294182489</v>
+        <f t="shared" ref="G20:Q20" si="0">SUM(G14:G19)</f>
+        <v>84181.536650128255</v>
       </c>
       <c r="H20" s="62">
-        <f>SUM(H14:H19)</f>
-        <v>112103.92349397094</v>
+        <f t="shared" si="0"/>
+        <v>111571.363337342</v>
       </c>
       <c r="I20" s="62">
-        <f>SUM(I14:I19)</f>
-        <v>142997.03207787927</v>
+        <f t="shared" si="0"/>
+        <v>136037.42848636603</v>
       </c>
       <c r="J20" s="62">
-        <f>SUM(J14:J19)</f>
-        <v>172024.58662827779</v>
+        <f t="shared" si="0"/>
+        <v>153240.46776925097</v>
       </c>
       <c r="K20" s="62">
-        <f>SUM(K14:K19)</f>
-        <v>195356.30338289967</v>
+        <f t="shared" si="0"/>
+        <v>163220.94899806115</v>
       </c>
       <c r="L20" s="62">
-        <f>SUM(L14:L19)</f>
-        <v>204014.08342046707</v>
+        <f t="shared" si="0"/>
+        <v>163447.45589359629</v>
       </c>
       <c r="M20" s="62">
-        <f>SUM(M14:M19)</f>
-        <v>207890.24040776875</v>
+        <f t="shared" si="0"/>
+        <v>164004.06940684392</v>
       </c>
       <c r="N20" s="62">
-        <f>SUM(N14:N19)</f>
-        <v>212521.70112542156</v>
+        <f t="shared" si="0"/>
+        <v>165240.08443737877</v>
       </c>
       <c r="O20" s="62">
-        <f>SUM(O14:O19)</f>
-        <v>218029.54951295367</v>
+        <f t="shared" si="0"/>
+        <v>167164.46490415739</v>
       </c>
       <c r="P20" s="62">
-        <f>SUM(P14:P19)</f>
-        <v>224434.15574452447</v>
+        <f t="shared" si="0"/>
+        <v>169787.14189878607</v>
       </c>
       <c r="Q20" s="62">
-        <f>SUM(Q14:Q19)</f>
-        <v>231757.53036149312</v>
+        <f t="shared" si="0"/>
+        <v>173121.28247823718</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
@@ -11352,47 +11378,47 @@
         <v>2802</v>
       </c>
       <c r="G21" s="59">
-        <f>F21</f>
+        <f t="shared" ref="G21:Q21" si="1">F21</f>
         <v>2802</v>
       </c>
       <c r="H21" s="59">
-        <f>G21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
       <c r="I21" s="59">
-        <f>H21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
       <c r="J21" s="59">
-        <f>I21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
       <c r="K21" s="59">
-        <f>J21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
       <c r="L21" s="59">
-        <f>K21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
       <c r="M21" s="59">
-        <f>L21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
       <c r="N21" s="59">
-        <f>M21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
       <c r="O21" s="59">
-        <f>N21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
       <c r="P21" s="59">
-        <f>O21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
       <c r="Q21" s="59">
-        <f>P21</f>
+        <f t="shared" si="1"/>
         <v>2802</v>
       </c>
     </row>
@@ -11413,47 +11439,47 @@
         <v>5898</v>
       </c>
       <c r="G22" s="59">
-        <f>F22</f>
+        <f t="shared" ref="G22:Q22" si="2">F22</f>
         <v>5898</v>
       </c>
       <c r="H22" s="59">
-        <f>G22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
       <c r="I22" s="59">
-        <f>H22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
       <c r="J22" s="59">
-        <f>I22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
       <c r="K22" s="59">
-        <f>J22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
       <c r="L22" s="59">
-        <f>K22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
       <c r="M22" s="59">
-        <f>L22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
       <c r="N22" s="59">
-        <f>M22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
       <c r="O22" s="59">
-        <f>N22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
       <c r="P22" s="59">
-        <f>O22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
       <c r="Q22" s="59">
-        <f>P22</f>
+        <f t="shared" si="2"/>
         <v>5898</v>
       </c>
     </row>
@@ -11474,47 +11500,47 @@
         <v>6521</v>
       </c>
       <c r="G23" s="59">
-        <f>F23</f>
+        <f t="shared" ref="G23:Q23" si="3">F23</f>
         <v>6521</v>
       </c>
       <c r="H23" s="59">
-        <f>G23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
       <c r="I23" s="59">
-        <f>H23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
       <c r="J23" s="59">
-        <f>I23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
       <c r="K23" s="59">
-        <f>J23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
       <c r="L23" s="59">
-        <f>K23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
       <c r="M23" s="59">
-        <f>L23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
       <c r="N23" s="59">
-        <f>M23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
       <c r="O23" s="59">
-        <f>N23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
       <c r="P23" s="59">
-        <f>O23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
       <c r="Q23" s="59">
-        <f>P23</f>
+        <f t="shared" si="3"/>
         <v>6521</v>
       </c>
     </row>
@@ -11597,47 +11623,47 @@
       </c>
       <c r="G25" s="59">
         <f>F25-CFS!G27-CFS!G15</f>
-        <v>29728.065374063073</v>
+        <v>29860.909652158414</v>
       </c>
       <c r="H25" s="59">
         <f>G25-CFS!H27-CFS!H15</f>
-        <v>36306.717758248597</v>
+        <v>36331.327834724361</v>
       </c>
       <c r="I25" s="59">
         <f>H25-CFS!I27-CFS!I15</f>
-        <v>44565.007746961033</v>
+        <v>43921.410503174877</v>
       </c>
       <c r="J25" s="59">
         <f>I25-CFS!J27-CFS!J15</f>
-        <v>54525.28835322331</v>
+        <v>52202.488070675448</v>
       </c>
       <c r="K25" s="59">
         <f>J25-CFS!K27-CFS!K15</f>
-        <v>66029.874095184423</v>
+        <v>60880.136433457272</v>
       </c>
       <c r="L25" s="59">
         <f>K25-CFS!L27-CFS!L15</f>
-        <v>78716.382706002871</v>
+        <v>69964.961971136712</v>
       </c>
       <c r="M25" s="59">
         <f>L25-CFS!M27-CFS!M15</f>
-        <v>92035.294146867862</v>
+        <v>79464.736966951954</v>
       </c>
       <c r="N25" s="59">
         <f>M25-CFS!N27-CFS!N15</f>
-        <v>106018.80755640814</v>
+        <v>89402.738462371461</v>
       </c>
       <c r="O25" s="59">
         <f>N25-CFS!O27-CFS!O15</f>
-        <v>120700.76369385065</v>
+        <v>99803.348054873975</v>
       </c>
       <c r="P25" s="59">
         <f>O25-CFS!P27-CFS!P15</f>
-        <v>136116.72984626595</v>
+        <v>110692.11502545826</v>
       </c>
       <c r="Q25" s="59">
         <f>P25-CFS!Q27-CFS!Q15</f>
-        <v>152304.08920141048</v>
+        <v>122095.82263112903</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -11657,47 +11683,47 @@
         <v>6992</v>
       </c>
       <c r="G26" s="59">
-        <f>F26</f>
+        <f t="shared" ref="G26:Q26" si="4">F26</f>
         <v>6992</v>
       </c>
       <c r="H26" s="59">
-        <f>G26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
       <c r="I26" s="59">
-        <f>H26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
       <c r="J26" s="59">
-        <f>I26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
       <c r="K26" s="59">
-        <f>J26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
       <c r="L26" s="59">
-        <f>K26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
       <c r="M26" s="59">
-        <f>L26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
       <c r="N26" s="59">
-        <f>M26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
       <c r="O26" s="59">
-        <f>N26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
       <c r="P26" s="59">
-        <f>O26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
       <c r="Q26" s="59">
-        <f>P26</f>
+        <f t="shared" si="4"/>
         <v>6992</v>
       </c>
     </row>
@@ -11718,48 +11744,48 @@
         <v>112476</v>
       </c>
       <c r="G27" s="62">
-        <f>G20+SUM(G21:G26)</f>
-        <v>146544.58733491221</v>
+        <f t="shared" ref="G27:Q27" si="5">G20+SUM(G21:G26)</f>
+        <v>148458.11296895333</v>
       </c>
       <c r="H27" s="62">
-        <f>H20+SUM(H21:H26)</f>
-        <v>185069.97458555287</v>
+        <f t="shared" si="5"/>
+        <v>184562.02450539969</v>
       </c>
       <c r="I27" s="62">
-        <f>I20+SUM(I21:I26)</f>
-        <v>226465.03982484029</v>
+        <f t="shared" si="5"/>
+        <v>218861.83898954091</v>
       </c>
       <c r="J27" s="62">
-        <f>J20+SUM(J21:J26)</f>
-        <v>267696.54164816777</v>
+        <f t="shared" si="5"/>
+        <v>246589.62250659309</v>
       </c>
       <c r="K27" s="62">
-        <f>K20+SUM(K21:K26)</f>
-        <v>304776.51081141742</v>
+        <f t="shared" si="5"/>
+        <v>267491.41876485175</v>
       </c>
       <c r="L27" s="62">
-        <f>L20+SUM(L21:L26)</f>
-        <v>328364.46612646995</v>
+        <f t="shared" si="5"/>
+        <v>279046.41786473303</v>
       </c>
       <c r="M27" s="62">
-        <f>M20+SUM(M21:M26)</f>
-        <v>347803.20122130332</v>
+        <f t="shared" si="5"/>
+        <v>291346.47304046253</v>
       </c>
       <c r="N27" s="62">
-        <f>N20+SUM(N21:N26)</f>
-        <v>368661.84201516304</v>
+        <f t="shared" si="5"/>
+        <v>304764.15623308357</v>
       </c>
       <c r="O27" s="62">
-        <f>O20+SUM(O21:O26)</f>
-        <v>391095.31320680433</v>
+        <f t="shared" si="5"/>
+        <v>319332.81295903138</v>
       </c>
       <c r="P27" s="62">
-        <f>P20+SUM(P21:P26)</f>
-        <v>415159.55225745705</v>
+        <f t="shared" si="5"/>
+        <v>335087.92359091097</v>
       </c>
       <c r="Q27" s="62">
-        <f>Q20+SUM(Q21:Q26)</f>
-        <v>440913.95289623691</v>
+        <f t="shared" si="5"/>
+        <v>352069.43844269955</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -11802,43 +11828,43 @@
       </c>
       <c r="H29" s="59">
         <f>G29+CFS!H37</f>
-        <v>2262.7394730869742</v>
+        <v>2294.6580481177739</v>
       </c>
       <c r="I29" s="59">
         <f>H29+CFS!I37</f>
-        <v>2853.8372186718184</v>
+        <v>2837.3024415525852</v>
       </c>
       <c r="J29" s="59">
         <f>I29+CFS!J37</f>
-        <v>3456.4796316770676</v>
+        <v>3313.5236172729628</v>
       </c>
       <c r="K29" s="59">
         <f>J29+CFS!K37</f>
-        <v>4007.9410355337141</v>
+        <v>3638.9428542093551</v>
       </c>
       <c r="L29" s="59">
         <f>K29+CFS!L37</f>
-        <v>4433.2773479101061</v>
+        <v>3817.2846132988943</v>
       </c>
       <c r="M29" s="59">
         <f>L29+CFS!M37</f>
-        <v>4555.7077326773715</v>
+        <v>3797.4691841806853</v>
       </c>
       <c r="N29" s="59">
         <f>M29+CFS!N37</f>
-        <v>4576.5871937123729</v>
+        <v>3780.0105370126498</v>
       </c>
       <c r="O29" s="59">
         <f>N29+CFS!O37</f>
-        <v>4606.1994047102526</v>
+        <v>3771.5130316244858</v>
       </c>
       <c r="P29" s="59">
         <f>O29+CFS!P37</f>
-        <v>4646.807214615209</v>
+        <v>3772.0784004583043</v>
       </c>
       <c r="Q29" s="59">
         <f>P29+CFS!Q37</f>
-        <v>4698.5407726584954</v>
+        <v>3781.7015120051874</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
@@ -11859,47 +11885,47 @@
       </c>
       <c r="G30" s="59">
         <f>IS!G$43*BS!G8</f>
-        <v>8326.9876919119179</v>
+        <v>8545.9028625564151</v>
       </c>
       <c r="H30" s="59">
         <f>IS!H$43*BS!H8</f>
-        <v>10841.014983432129</v>
+        <v>10662.654958771398</v>
       </c>
       <c r="I30" s="59">
         <f>IS!I$43*BS!I8</f>
-        <v>13608.903507407793</v>
+        <v>12507.759207944191</v>
       </c>
       <c r="J30" s="59">
         <f>IS!J$43*BS!J8</f>
-        <v>16413.627744072717</v>
+        <v>13646.4553445701</v>
       </c>
       <c r="K30" s="59">
         <f>IS!K$43*BS!K8</f>
-        <v>18958.500787577508</v>
+        <v>14299.967596406143</v>
       </c>
       <c r="L30" s="59">
         <f>IS!L$43*BS!L8</f>
-        <v>20906.201134436604</v>
+        <v>14970.958187820861</v>
       </c>
       <c r="M30" s="59">
         <f>IS!M$43*BS!M8</f>
-        <v>21948.342922104286</v>
+        <v>15654.75678825021</v>
       </c>
       <c r="N30" s="59">
         <f>IS!N$43*BS!N8</f>
-        <v>23043.545933247908</v>
+        <v>16376.913815389606</v>
       </c>
       <c r="O30" s="59">
         <f>IS!O$43*BS!O8</f>
-        <v>24194.515407856336</v>
+        <v>17139.249476107881</v>
       </c>
       <c r="P30" s="59">
         <f>IS!P$43*BS!P8</f>
-        <v>25404.096505261328</v>
+        <v>17943.688005612672</v>
       </c>
       <c r="Q30" s="59">
         <f>IS!Q$43*BS!Q8</f>
-        <v>26675.281663031394</v>
+        <v>18792.262883040537</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
@@ -11920,47 +11946,47 @@
       </c>
       <c r="G31" s="59">
         <f>IS!G$42*BS!G9</f>
-        <v>3193.1964582422379</v>
+        <v>3277.1450808919976</v>
       </c>
       <c r="H31" s="59">
         <f>IS!H$42*BS!H9</f>
-        <v>4157.2645390686484</v>
+        <v>4088.8678246611271</v>
       </c>
       <c r="I31" s="59">
         <f>IS!I$42*BS!I9</f>
-        <v>5218.6822039648341</v>
+        <v>4796.4202519655428</v>
       </c>
       <c r="J31" s="59">
         <f>IS!J$42*BS!J9</f>
-        <v>6294.2254652529091</v>
+        <v>5233.0824166063921</v>
       </c>
       <c r="K31" s="59">
         <f>IS!K$42*BS!K9</f>
-        <v>7270.1221387989463</v>
+        <v>5483.6884082554116</v>
       </c>
       <c r="L31" s="59">
         <f>IS!L$42*BS!L9</f>
-        <v>8017.0176644580752</v>
+        <v>5740.9969163609867</v>
       </c>
       <c r="M31" s="59">
         <f>IS!M$42*BS!M9</f>
-        <v>8416.6535938589277</v>
+        <v>6003.2169831881365</v>
       </c>
       <c r="N31" s="59">
         <f>IS!N$42*BS!N9</f>
-        <v>8836.6372068570472</v>
+        <v>6280.1465700537547</v>
       </c>
       <c r="O31" s="59">
         <f>IS!O$42*BS!O9</f>
-        <v>9278.0058969338188</v>
+        <v>6572.4836818477106</v>
       </c>
       <c r="P31" s="59">
         <f>IS!P$42*BS!P9</f>
-        <v>9741.8507132221876</v>
+        <v>6880.9662157877246</v>
       </c>
       <c r="Q31" s="59">
         <f>IS!Q$42*BS!Q9</f>
-        <v>10229.31918246277</v>
+        <v>7206.3739614708275</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
@@ -11981,47 +12007,47 @@
       </c>
       <c r="G32" s="59">
         <f>IS!G$42*BS!G10</f>
-        <v>23370.164563017512</v>
+        <v>23984.562440448299</v>
       </c>
       <c r="H32" s="59">
         <f>IS!H$42*BS!H10</f>
-        <v>30425.925144459477</v>
+        <v>29925.347590846202</v>
       </c>
       <c r="I32" s="59">
         <f>IS!I$42*BS!I10</f>
-        <v>38194.161713396534</v>
+        <v>35103.737608280033</v>
       </c>
       <c r="J32" s="59">
         <f>IS!J$42*BS!J10</f>
-        <v>46065.779805063612</v>
+        <v>38299.553080190453</v>
       </c>
       <c r="K32" s="59">
         <f>IS!K$42*BS!K10</f>
-        <v>53208.110743832971</v>
+        <v>40133.672384124453</v>
       </c>
       <c r="L32" s="59">
         <f>IS!L$42*BS!L10</f>
-        <v>58674.442544678015</v>
+        <v>42016.845642183871</v>
       </c>
       <c r="M32" s="59">
         <f>IS!M$42*BS!M10</f>
-        <v>61599.272744613016</v>
+        <v>43935.965306011036</v>
       </c>
       <c r="N32" s="59">
         <f>IS!N$42*BS!N10</f>
-        <v>64673.022286142834</v>
+        <v>45962.740076073431</v>
       </c>
       <c r="O32" s="59">
         <f>IS!O$42*BS!O10</f>
-        <v>67903.283579159441</v>
+        <v>48102.278466474498</v>
       </c>
       <c r="P32" s="59">
         <f>IS!P$42*BS!P10</f>
-        <v>71298.04172514868</v>
+        <v>50359.980952767262</v>
       </c>
       <c r="Q32" s="59">
         <f>IS!Q$42*BS!Q10</f>
-        <v>74865.695170344377</v>
+        <v>52741.554609804603</v>
       </c>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
@@ -12042,47 +12068,47 @@
       </c>
       <c r="G33" s="59">
         <f>IS!G$42*BS!G11</f>
-        <v>11370.468398886152</v>
+        <v>11669.396189096264</v>
       </c>
       <c r="H33" s="59">
         <f>IS!H$42*BS!H11</f>
-        <v>14803.362613433081</v>
+        <v>14559.812712909119</v>
       </c>
       <c r="I33" s="59">
         <f>IS!I$42*BS!I11</f>
-        <v>18582.903325865522</v>
+        <v>17079.295187735832</v>
       </c>
       <c r="J33" s="59">
         <f>IS!J$42*BS!J11</f>
-        <v>22412.74305669215</v>
+        <v>18634.180209364324</v>
       </c>
       <c r="K33" s="59">
         <f>IS!K$42*BS!K11</f>
-        <v>25887.757022241138</v>
+        <v>19526.548576259378</v>
       </c>
       <c r="L33" s="59">
         <f>IS!L$42*BS!L11</f>
-        <v>28547.334058240824</v>
+        <v>20442.783545964157</v>
       </c>
       <c r="M33" s="59">
         <f>IS!M$42*BS!M11</f>
-        <v>29970.374502427356</v>
+        <v>21376.507800767191</v>
       </c>
       <c r="N33" s="59">
         <f>IS!N$42*BS!N11</f>
-        <v>31465.869835111607</v>
+        <v>22362.610333871417</v>
       </c>
       <c r="O33" s="59">
         <f>IS!O$42*BS!O11</f>
-        <v>33037.514050681821</v>
+        <v>23403.576630478357</v>
       </c>
       <c r="P33" s="59">
         <f>IS!P$42*BS!P11</f>
-        <v>34689.192202829501</v>
+        <v>24502.034226070231</v>
       </c>
       <c r="Q33" s="59">
         <f>IS!Q$42*BS!Q11</f>
-        <v>36424.990453089544</v>
+        <v>25660.759828277387</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
@@ -12102,48 +12128,48 @@
         <v>35228</v>
       </c>
       <c r="G34" s="62">
-        <f>SUM(G29:G33)</f>
-        <v>47979.637112057819</v>
+        <f t="shared" ref="G34:Q34" si="6">SUM(G29:G33)</f>
+        <v>49195.82657299297</v>
       </c>
       <c r="H34" s="62">
-        <f>SUM(H29:H33)</f>
-        <v>62490.306753480312</v>
+        <f t="shared" si="6"/>
+        <v>61531.341135305614</v>
       </c>
       <c r="I34" s="62">
-        <f>SUM(I29:I33)</f>
-        <v>78458.487969306501</v>
+        <f t="shared" si="6"/>
+        <v>72324.514697478182</v>
       </c>
       <c r="J34" s="62">
-        <f>SUM(J29:J33)</f>
-        <v>94642.855702758461</v>
+        <f t="shared" si="6"/>
+        <v>79126.794668004237</v>
       </c>
       <c r="K34" s="62">
-        <f>SUM(K29:K33)</f>
-        <v>109332.43172798428</v>
+        <f t="shared" si="6"/>
+        <v>83082.819819254742</v>
       </c>
       <c r="L34" s="62">
-        <f>SUM(L29:L33)</f>
-        <v>120578.27274972362</v>
+        <f t="shared" si="6"/>
+        <v>86988.868905628769</v>
       </c>
       <c r="M34" s="62">
-        <f>SUM(M29:M33)</f>
-        <v>126490.35149568095</v>
+        <f t="shared" si="6"/>
+        <v>90767.916062397271</v>
       </c>
       <c r="N34" s="62">
-        <f>SUM(N29:N33)</f>
-        <v>132595.66245507178</v>
+        <f t="shared" si="6"/>
+        <v>94762.42133240086</v>
       </c>
       <c r="O34" s="62">
-        <f>SUM(O29:O33)</f>
-        <v>139019.51833934165</v>
+        <f t="shared" si="6"/>
+        <v>98989.101286532939</v>
       </c>
       <c r="P34" s="62">
-        <f>SUM(P29:P33)</f>
-        <v>145779.98836107689</v>
+        <f t="shared" si="6"/>
+        <v>103458.74780069619</v>
       </c>
       <c r="Q34" s="62">
-        <f>SUM(Q29:Q33)</f>
-        <v>152893.82724158658</v>
+        <f t="shared" si="6"/>
+        <v>108182.65279459854</v>
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
@@ -12164,47 +12190,47 @@
       </c>
       <c r="G35" s="59">
         <f>F35+CFS!G38+CFS!G39</f>
-        <v>55312.336542290868</v>
+        <v>55692.075832895738</v>
       </c>
       <c r="H35" s="59">
         <f>G35+CFS!H38+CFS!H39</f>
-        <v>70356.554180110616</v>
+        <v>70488.780942323661</v>
       </c>
       <c r="I35" s="59">
         <f>H35+CFS!I38+CFS!I39</f>
-        <v>84520.493614546853</v>
+        <v>83506.666166169947</v>
       </c>
       <c r="J35" s="59">
         <f>I35+CFS!J38+CFS!J39</f>
-        <v>95909.196073927247</v>
+        <v>92975.348042463491</v>
       </c>
       <c r="K35" s="59">
         <f>J35+CFS!K38+CFS!K39</f>
-        <v>102486.43566752103</v>
+        <v>97936.41084568997</v>
       </c>
       <c r="L35" s="59">
         <f>K35+CFS!L38+CFS!L39</f>
-        <v>97362.113884144972</v>
+        <v>93039.590303405479</v>
       </c>
       <c r="M35" s="59">
         <f>L35+CFS!M38+CFS!M39</f>
-        <v>92494.008189937726</v>
+        <v>88387.610788235208</v>
       </c>
       <c r="N35" s="59">
         <f>M35+CFS!N38+CFS!N39</f>
-        <v>87869.307780440839</v>
+        <v>83968.230248823442</v>
       </c>
       <c r="O35" s="59">
         <f>N35+CFS!O38+CFS!O39</f>
-        <v>83475.842391418802</v>
+        <v>79769.818736382265</v>
       </c>
       <c r="P35" s="59">
         <f>O35+CFS!P38+CFS!P39</f>
-        <v>79302.050271847867</v>
+        <v>75781.327799563151</v>
       </c>
       <c r="Q35" s="59">
         <f>P35+CFS!Q38+CFS!Q39</f>
-        <v>75336.947758255468</v>
+        <v>71992.261409584986</v>
       </c>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.25">
@@ -12224,47 +12250,47 @@
         <v>5875</v>
       </c>
       <c r="G36" s="59">
-        <f>F36</f>
+        <f t="shared" ref="G36:Q36" si="7">F36</f>
         <v>5875</v>
       </c>
       <c r="H36" s="59">
-        <f>G36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
       <c r="I36" s="59">
-        <f>H36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
       <c r="J36" s="59">
-        <f>I36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
       <c r="K36" s="59">
-        <f>J36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
       <c r="L36" s="59">
-        <f>K36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
       <c r="M36" s="59">
-        <f>L36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
       <c r="N36" s="59">
-        <f>M36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
       <c r="O36" s="59">
-        <f>N36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
       <c r="P36" s="59">
-        <f>O36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
       <c r="Q36" s="59">
-        <f>P36</f>
+        <f t="shared" si="7"/>
         <v>5875</v>
       </c>
     </row>
@@ -12285,47 +12311,47 @@
         <v>3970</v>
       </c>
       <c r="G37" s="59">
-        <f>F37</f>
+        <f t="shared" ref="G37:Q37" si="8">F37</f>
         <v>3970</v>
       </c>
       <c r="H37" s="59">
-        <f>G37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
       <c r="I37" s="59">
-        <f>H37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
       <c r="J37" s="59">
-        <f>I37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
       <c r="K37" s="59">
-        <f>J37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
       <c r="L37" s="59">
-        <f>K37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
       <c r="M37" s="59">
-        <f>L37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
       <c r="N37" s="59">
-        <f>M37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
       <c r="O37" s="59">
-        <f>N37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
       <c r="P37" s="59">
-        <f>O37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
       <c r="Q37" s="59">
-        <f>P37</f>
+        <f t="shared" si="8"/>
         <v>3970</v>
       </c>
     </row>
@@ -12346,48 +12372,48 @@
         <v>50713</v>
       </c>
       <c r="G38" s="62">
-        <f>SUM(G35:G37)</f>
-        <v>65157.336542290868</v>
+        <f t="shared" ref="G38:Q38" si="9">SUM(G35:G37)</f>
+        <v>65537.075832895731</v>
       </c>
       <c r="H38" s="62">
-        <f>SUM(H35:H37)</f>
-        <v>80201.554180110616</v>
+        <f t="shared" si="9"/>
+        <v>80333.780942323661</v>
       </c>
       <c r="I38" s="62">
-        <f>SUM(I35:I37)</f>
-        <v>94365.493614546853</v>
+        <f t="shared" si="9"/>
+        <v>93351.666166169947</v>
       </c>
       <c r="J38" s="62">
-        <f>SUM(J35:J37)</f>
-        <v>105754.19607392725</v>
+        <f t="shared" si="9"/>
+        <v>102820.34804246349</v>
       </c>
       <c r="K38" s="62">
-        <f>SUM(K35:K37)</f>
-        <v>112331.43566752103</v>
+        <f t="shared" si="9"/>
+        <v>107781.41084568997</v>
       </c>
       <c r="L38" s="62">
-        <f>SUM(L35:L37)</f>
-        <v>107207.11388414497</v>
+        <f t="shared" si="9"/>
+        <v>102884.59030340548</v>
       </c>
       <c r="M38" s="62">
-        <f>SUM(M35:M37)</f>
-        <v>102339.00818993773</v>
+        <f t="shared" si="9"/>
+        <v>98232.610788235208</v>
       </c>
       <c r="N38" s="62">
-        <f>SUM(N35:N37)</f>
-        <v>97714.307780440839</v>
+        <f t="shared" si="9"/>
+        <v>93813.230248823442</v>
       </c>
       <c r="O38" s="62">
-        <f>SUM(O35:O37)</f>
-        <v>93320.842391418802</v>
+        <f t="shared" si="9"/>
+        <v>89614.818736382265</v>
       </c>
       <c r="P38" s="62">
-        <f>SUM(P35:P37)</f>
-        <v>89147.050271847867</v>
+        <f t="shared" si="9"/>
+        <v>85626.327799563151</v>
       </c>
       <c r="Q38" s="62">
-        <f>SUM(Q35:Q37)</f>
-        <v>85181.947758255468</v>
+        <f t="shared" si="9"/>
+        <v>81837.261409584986</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
@@ -12408,47 +12434,47 @@
       </c>
       <c r="G39" s="62">
         <f>F39+IS!G52+CFS!G17+CFS!G36+CFS!G40</f>
-        <v>33407.613680563547</v>
+        <v>33725.210563064626</v>
       </c>
       <c r="H39" s="62">
         <f>G39+IS!H52+CFS!H17+CFS!H36+CFS!H40</f>
-        <v>42378.113651961961</v>
+        <v>42696.902427770416</v>
       </c>
       <c r="I39" s="62">
         <f>H39+IS!I52+CFS!I17+CFS!I36+CFS!I40</f>
-        <v>53641.058240986968</v>
+        <v>53185.658125892798</v>
       </c>
       <c r="J39" s="62">
         <f>I39+IS!J52+CFS!J17+CFS!J36+CFS!J40</f>
-        <v>67299.489871482045</v>
+        <v>64642.479796125357</v>
       </c>
       <c r="K39" s="62">
         <f>J39+IS!K52+CFS!K17+CFS!K36+CFS!K40</f>
-        <v>83112.643415912142</v>
+        <v>76627.188099907071</v>
       </c>
       <c r="L39" s="62">
         <f>K39+IS!L52+CFS!L17+CFS!L36+CFS!L40</f>
-        <v>100579.07949260139</v>
+        <v>89172.958655698763</v>
       </c>
       <c r="M39" s="62">
         <f>L39+IS!M52+CFS!M17+CFS!M36+CFS!M40</f>
-        <v>118973.84153568464</v>
+        <v>102345.94618983009</v>
       </c>
       <c r="N39" s="62">
         <f>M39+IS!N52+CFS!N17+CFS!N36+CFS!N40</f>
-        <v>138351.87177965045</v>
+        <v>116188.50465185926</v>
       </c>
       <c r="O39" s="62">
         <f>N39+IS!O52+CFS!O17+CFS!O36+CFS!O40</f>
-        <v>158754.95247604392</v>
+        <v>130728.89293611613</v>
       </c>
       <c r="P39" s="62">
         <f>O39+IS!P52+CFS!P17+CFS!P36+CFS!P40</f>
-        <v>180232.51362453241</v>
+        <v>146002.84799065156</v>
       </c>
       <c r="Q39" s="62">
         <f>P39+IS!Q52+CFS!Q17+CFS!Q36+CFS!Q40</f>
-        <v>202838.17789639495</v>
+        <v>162049.52423851594</v>
       </c>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
@@ -12468,48 +12494,48 @@
         <v>112476</v>
       </c>
       <c r="G40" s="62">
-        <f>G34+G38+G39</f>
-        <v>146544.58733491224</v>
+        <f t="shared" ref="G40:Q40" si="10">G34+G38+G39</f>
+        <v>148458.11296895333</v>
       </c>
       <c r="H40" s="62">
-        <f>H34+H38+H39</f>
-        <v>185069.97458555287</v>
+        <f t="shared" si="10"/>
+        <v>184562.02450539969</v>
       </c>
       <c r="I40" s="62">
-        <f>I34+I38+I39</f>
-        <v>226465.03982484032</v>
+        <f t="shared" si="10"/>
+        <v>218861.83898954093</v>
       </c>
       <c r="J40" s="62">
-        <f>J34+J38+J39</f>
-        <v>267696.54164816777</v>
+        <f t="shared" si="10"/>
+        <v>246589.62250659309</v>
       </c>
       <c r="K40" s="62">
-        <f>K34+K38+K39</f>
-        <v>304776.51081141748</v>
+        <f t="shared" si="10"/>
+        <v>267491.41876485175</v>
       </c>
       <c r="L40" s="62">
-        <f>L34+L38+L39</f>
-        <v>328364.46612647001</v>
+        <f t="shared" si="10"/>
+        <v>279046.41786473303</v>
       </c>
       <c r="M40" s="62">
-        <f>M34+M38+M39</f>
-        <v>347803.20122130332</v>
+        <f t="shared" si="10"/>
+        <v>291346.47304046259</v>
       </c>
       <c r="N40" s="62">
-        <f>N34+N38+N39</f>
-        <v>368661.84201516304</v>
+        <f t="shared" si="10"/>
+        <v>304764.15623308357</v>
       </c>
       <c r="O40" s="62">
-        <f>O34+O38+O39</f>
-        <v>391095.31320680433</v>
+        <f t="shared" si="10"/>
+        <v>319332.81295903132</v>
       </c>
       <c r="P40" s="62">
-        <f>P34+P38+P39</f>
-        <v>415159.55225745717</v>
+        <f t="shared" si="10"/>
+        <v>335087.92359091091</v>
       </c>
       <c r="Q40" s="62">
-        <f>Q34+Q38+Q39</f>
-        <v>440913.95289623702</v>
+        <f t="shared" si="10"/>
+        <v>352069.43844269949</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
@@ -12529,47 +12555,47 @@
         <v>0</v>
       </c>
       <c r="G41" s="65">
-        <f>G27-G40</f>
+        <f t="shared" ref="G41:Q41" si="11">G27-G40</f>
         <v>0</v>
       </c>
       <c r="H41" s="65">
-        <f>H27-H40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I41" s="65">
-        <f>I27-I40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J41" s="65">
-        <f>J27-J40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K41" s="65">
-        <f>K27-K40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L41" s="65">
-        <f>L27-L40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M41" s="65">
-        <f>M27-M40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="N41" s="65">
-        <f>N27-N40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O41" s="65">
-        <f>O27-O40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P41" s="65">
-        <f>P27-P40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q41" s="65">
-        <f>Q27-Q40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12591,7 +12617,7 @@
     <row r="1" spans="2:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>115</v>
@@ -12602,7 +12628,7 @@
       <c r="E2" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="F2" s="181" t="s">
+      <c r="F2" s="177" t="s">
         <v>118</v>
       </c>
       <c r="G2" s="22" t="s">
@@ -13115,7 +13141,7 @@
       </c>
     </row>
     <row r="12" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F12" s="206"/>
+      <c r="F12" s="199"/>
     </row>
     <row r="13" spans="2:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="55" t="s">
@@ -13185,47 +13211,47 @@
       </c>
       <c r="G14" s="59">
         <f>IS!G52</f>
-        <v>20634.746179872462</v>
+        <v>21462.925865984318</v>
       </c>
       <c r="H14" s="59">
         <f>IS!H52</f>
-        <v>26912.543815561112</v>
+        <v>26780.213845498329</v>
       </c>
       <c r="I14" s="59">
         <f>IS!I52</f>
-        <v>33788.199467256352</v>
+        <v>31340.429023740136</v>
       </c>
       <c r="J14" s="59">
         <f>IS!J52</f>
-        <v>40906.709892307292</v>
+        <v>34221.13416353245</v>
       </c>
       <c r="K14" s="59">
         <f>IS!K52</f>
-        <v>47326.418017348406</v>
+        <v>35816.61040905962</v>
       </c>
       <c r="L14" s="59">
         <f>IS!L52</f>
-        <v>52248.421001468632</v>
+        <v>37494.52336137947</v>
       </c>
       <c r="M14" s="59">
         <f>IS!M52</f>
-        <v>54973.220771859145</v>
+        <v>39320.158163627493</v>
       </c>
       <c r="N14" s="59">
         <f>IS!N52</f>
-        <v>57852.77223501679</v>
+        <v>41263.164118577261</v>
       </c>
       <c r="O14" s="59">
         <f>IS!O52</f>
-        <v>60861.660141676162</v>
+        <v>43295.505853848168</v>
       </c>
       <c r="P14" s="59">
         <f>IS!P52</f>
-        <v>64017.993109102012</v>
+        <v>45434.241797672905</v>
       </c>
       <c r="Q14" s="59">
         <f>IS!Q52</f>
-        <v>67332.78159988788</v>
+        <v>47688.04001350655</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
@@ -13246,47 +13272,47 @@
       </c>
       <c r="G15" s="59">
         <f>IS!G$42*CFS!G3</f>
-        <v>3679.7531309583919</v>
+        <v>3776.4932504827457</v>
       </c>
       <c r="H15" s="59">
         <f>IS!H$42*CFS!H3</f>
-        <v>4790.719081619266</v>
+        <v>4711.9005600282435</v>
       </c>
       <c r="I15" s="59">
         <f>IS!I$42*CFS!I3</f>
-        <v>6013.8680568646814</v>
+        <v>5527.264817673652</v>
       </c>
       <c r="J15" s="59">
         <f>IS!J$42*CFS!J3</f>
-        <v>7253.2949868897158</v>
+        <v>6030.462471974176</v>
       </c>
       <c r="K15" s="59">
         <f>IS!K$42*CFS!K3</f>
-        <v>8377.8918874981064</v>
+        <v>6319.2540306730216</v>
       </c>
       <c r="L15" s="59">
         <f>IS!L$42*CFS!L3</f>
-        <v>9238.5940663286256</v>
+        <v>6615.7693878411574</v>
       </c>
       <c r="M15" s="59">
         <f>IS!M$42*CFS!M3</f>
-        <v>9699.123689759861</v>
+        <v>6917.9446922815468</v>
       </c>
       <c r="N15" s="59">
         <f>IS!N$42*CFS!N3</f>
-        <v>10183.101432780335</v>
+        <v>7237.0708492999984</v>
       </c>
       <c r="O15" s="59">
         <f>IS!O$42*CFS!O3</f>
-        <v>10691.722759546756</v>
+        <v>7573.9522208305489</v>
       </c>
       <c r="P15" s="59">
         <f>IS!P$42*CFS!P3</f>
-        <v>11226.244965535769</v>
+        <v>7929.439139645624</v>
       </c>
       <c r="Q15" s="59">
         <f>IS!Q$42*CFS!Q3</f>
-        <v>11787.990429489759</v>
+        <v>8304.4302141611734</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
@@ -13306,47 +13332,47 @@
         <v>-1707</v>
       </c>
       <c r="G16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" ref="G16:Q16" si="0">AVERAGE($D$16:$F$16)</f>
         <v>-2243.6666666666665</v>
       </c>
       <c r="H16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
       <c r="I16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
       <c r="J16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
       <c r="K16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
       <c r="L16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
       <c r="M16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
       <c r="N16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
       <c r="O16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
       <c r="P16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
       <c r="Q16" s="59">
-        <f>AVERAGE($D$16:$F$16)</f>
+        <f t="shared" si="0"/>
         <v>-2243.6666666666665</v>
       </c>
     </row>
@@ -13368,47 +13394,47 @@
       </c>
       <c r="G17" s="59">
         <f>IS!G$42*CFS!G4</f>
-        <v>1213.3175315862877</v>
+        <v>1245.2154548570481</v>
       </c>
       <c r="H17" s="59">
         <f>IS!H$42*CFS!H4</f>
-        <v>1579.634079724181</v>
+        <v>1553.6454085669957</v>
       </c>
       <c r="I17" s="59">
         <f>IS!I$42*CFS!I4</f>
-        <v>1982.9405088760038</v>
+        <v>1822.493810408658</v>
       </c>
       <c r="J17" s="59">
         <f>IS!J$42*CFS!J4</f>
-        <v>2391.6142350202035</v>
+        <v>1988.4121516906746</v>
       </c>
       <c r="K17" s="59">
         <f>IS!K$42*CFS!K4</f>
-        <v>2762.4252886194386</v>
+        <v>2083.6348062202683</v>
       </c>
       <c r="L17" s="59">
         <f>IS!L$42*CFS!L4</f>
-        <v>3046.2228711973762</v>
+        <v>2181.4042131432179</v>
       </c>
       <c r="M17" s="59">
         <f>IS!M$42*CFS!M4</f>
-        <v>3198.0723692582474</v>
+        <v>2281.0398629930382</v>
       </c>
       <c r="N17" s="59">
         <f>IS!N$42*CFS!N4</f>
-        <v>3357.6533682018817</v>
+        <v>2386.2646830606277</v>
       </c>
       <c r="O17" s="59">
         <f>IS!O$42*CFS!O4</f>
-        <v>3525.3600459984027</v>
+        <v>2497.3438939739954</v>
       </c>
       <c r="P17" s="59">
         <f>IS!P$42*CFS!P4</f>
-        <v>3701.6069681335662</v>
+        <v>2614.5578742323901</v>
       </c>
       <c r="Q17" s="59">
         <f>IS!Q$42*CFS!Q4</f>
-        <v>3886.8301598662506</v>
+        <v>2738.2029201650225</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
@@ -13479,47 +13505,47 @@
       </c>
       <c r="G19" s="59">
         <f>IS!G47</f>
-        <v>5711.5180372693967</v>
+        <v>5861.6729302545782</v>
       </c>
       <c r="H19" s="59">
         <f>IS!H47</f>
-        <v>7435.9005814698839</v>
+        <v>7313.5626441907089</v>
       </c>
       <c r="I19" s="59">
         <f>IS!I47</f>
-        <v>9334.4076784832796</v>
+        <v>8579.1278869529651</v>
       </c>
       <c r="J19" s="59">
         <f>IS!J47</f>
-        <v>11258.180555298984</v>
+        <v>9360.1646512590942</v>
       </c>
       <c r="K19" s="59">
         <f>IS!K47</f>
-        <v>13003.720338509705</v>
+        <v>9808.4116226775295</v>
       </c>
       <c r="L19" s="59">
         <f>IS!L47</f>
-        <v>14339.656702759019</v>
+        <v>10268.647065252477</v>
       </c>
       <c r="M19" s="59">
         <f>IS!M47</f>
-        <v>15054.466408006643</v>
+        <v>10737.667578397377</v>
       </c>
       <c r="N19" s="59">
         <f>IS!N47</f>
-        <v>15805.671043350869</v>
+        <v>11232.99830769025</v>
       </c>
       <c r="O19" s="59">
         <f>IS!O47</f>
-        <v>16595.12614497876</v>
+        <v>11755.887741149514</v>
       </c>
       <c r="P19" s="59">
         <f>IS!P47</f>
-        <v>17424.783220379395</v>
+        <v>12307.655720295663</v>
       </c>
       <c r="Q19" s="59">
         <f>IS!Q47</f>
-        <v>18296.694795842028</v>
+        <v>12889.697017547791</v>
       </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
@@ -13590,47 +13616,47 @@
       </c>
       <c r="G21" s="59">
         <f>-(BS!G15+BS!G16-BS!F15-BS!F16)</f>
-        <v>-6943.4735224725518</v>
+        <v>-7655.8880443697744</v>
       </c>
       <c r="H21" s="59">
         <f>-(BS!H15+BS!H16-BS!G15-BS!G16)</f>
-        <v>-8181.3861764447574</v>
+        <v>-6888.5355371228698</v>
       </c>
       <c r="I21" s="59">
         <f>-(BS!I15+BS!I16-BS!H15-BS!H16)</f>
-        <v>-9007.5254888347899</v>
+        <v>-6004.5133357138939</v>
       </c>
       <c r="J21" s="59">
         <f>-(BS!J15+BS!J16-BS!I15-BS!I16)</f>
-        <v>-9127.3997605310051</v>
+        <v>-3705.6530224573944</v>
       </c>
       <c r="K21" s="59">
         <f>-(BS!K15+BS!K16-BS!J15-BS!J16)</f>
-        <v>-8281.7673496085863</v>
+        <v>-2126.7215838677857</v>
       </c>
       <c r="L21" s="59">
         <f>-(BS!L15+BS!L16-BS!K15-BS!K16)</f>
-        <v>-6338.3912924883125</v>
+        <v>-2183.6012551022677</v>
       </c>
       <c r="M21" s="59">
         <f>-(BS!M15+BS!M16-BS!L15-BS!L16)</f>
-        <v>-3391.4366977154395</v>
+        <v>-2225.282293432083</v>
       </c>
       <c r="N21" s="59">
         <f>-(BS!N15+BS!N16-BS!M15-BS!M16)</f>
-        <v>-3564.1135663061377</v>
+        <v>-2350.1119255901231</v>
       </c>
       <c r="O21" s="59">
         <f>-(BS!O15+BS!O16-BS!N15-BS!N16)</f>
-        <v>-3745.5940835778256</v>
+        <v>-2480.865047666186</v>
       </c>
       <c r="P21" s="59">
         <f>-(BS!P15+BS!P16-BS!O15-BS!O16)</f>
-        <v>-3936.3335883335039</v>
+        <v>-2617.8801985519922</v>
       </c>
       <c r="Q21" s="59">
         <f>-(BS!Q15+BS!Q16-BS!P15-BS!P16)</f>
-        <v>-4136.8113673869047</v>
+        <v>-2761.512890207553</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
@@ -13651,47 +13677,47 @@
       </c>
       <c r="G22" s="59">
         <f>-(BS!G17-BS!F17)</f>
-        <v>-7532.4675288413091</v>
+        <v>-8091.8224471045505</v>
       </c>
       <c r="H22" s="59">
         <f>-(BS!H17-BS!G17)</f>
-        <v>-6423.645862549507</v>
+        <v>-5408.5593624054127</v>
       </c>
       <c r="I22" s="59">
         <f>-(BS!I17-BS!H17)</f>
-        <v>-7072.2922241162923</v>
+        <v>-4714.4660346962046</v>
       </c>
       <c r="J22" s="59">
         <f>-(BS!J17-BS!I17)</f>
-        <v>-7166.4119555163998</v>
+        <v>-2909.5072879320505</v>
       </c>
       <c r="K22" s="59">
         <f>-(BS!K17-BS!J17)</f>
-        <v>-6502.4605149525669</v>
+        <v>-1669.8033815271556</v>
       </c>
       <c r="L22" s="59">
         <f>-(BS!L17-BS!K17)</f>
-        <v>-4976.6115573956849</v>
+        <v>-1714.4626674853862</v>
       </c>
       <c r="M22" s="59">
         <f>-(BS!M17-BS!L17)</f>
-        <v>-2662.7991689356058</v>
+        <v>-1747.1886901470425</v>
       </c>
       <c r="N22" s="59">
         <f>-(BS!N17-BS!M17)</f>
-        <v>-2798.377056173631</v>
+        <v>-1845.1991412909265</v>
       </c>
       <c r="O22" s="59">
         <f>-(BS!O17-BS!N17)</f>
-        <v>-2940.8671609998564</v>
+        <v>-1947.8604426309612</v>
       </c>
       <c r="P22" s="59">
         <f>-(BS!P17-BS!O17)</f>
-        <v>-3090.6269943733496</v>
+        <v>-2055.4383992403527</v>
       </c>
       <c r="Q22" s="59">
         <f>-(BS!Q17-BS!P17)</f>
-        <v>-3248.0328701230246</v>
+        <v>-2168.2121426600788</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
@@ -13712,47 +13738,47 @@
       </c>
       <c r="G23" s="59">
         <f>-(BS!G18+BS!G19-BS!F18-BS!F19)</f>
-        <v>-4982.2135490944202</v>
+        <v>-5493.3988041516095</v>
       </c>
       <c r="H23" s="59">
         <f>-(BS!H18+BS!H19-BS!G18-BS!G19)</f>
-        <v>-5870.4642462785469</v>
+        <v>-4942.7933980585949</v>
       </c>
       <c r="I23" s="59">
         <f>-(BS!I18+BS!I19-BS!H18-BS!H19)</f>
-        <v>-6463.2514819910057</v>
+        <v>-4308.4729278637697</v>
       </c>
       <c r="J23" s="59">
         <f>-(BS!J18+BS!J19-BS!I18-BS!I19)</f>
-        <v>-6549.2659556834251</v>
+        <v>-2658.9508315940916</v>
       </c>
       <c r="K23" s="59">
         <f>-(BS!K18+BS!K19-BS!J18-BS!J19)</f>
-        <v>-5942.4916601359155</v>
+        <v>-1526.0058320960479</v>
       </c>
       <c r="L23" s="59">
         <f>-(BS!L18+BS!L19-BS!K18-BS!K19)</f>
-        <v>-4548.0434071925574</v>
+        <v>-1566.8192186201395</v>
       </c>
       <c r="M23" s="59">
         <f>-(BS!M18+BS!M19-BS!L18-BS!L19)</f>
-        <v>-2433.4883414716369</v>
+        <v>-1596.7269921912507</v>
       </c>
       <c r="N23" s="59">
         <f>-(BS!N18+BS!N19-BS!M18-BS!M19)</f>
-        <v>-2557.3907415489689</v>
+        <v>-1686.2971306318182</v>
       </c>
       <c r="O23" s="59">
         <f>-(BS!O18+BS!O19-BS!N18-BS!N19)</f>
-        <v>-2687.6101035327438</v>
+        <v>-1780.1176045322902</v>
       </c>
       <c r="P23" s="59">
         <f>-(BS!P18+BS!P19-BS!O18-BS!O19)</f>
-        <v>-2824.4731508052191</v>
+        <v>-1878.4313287749437</v>
       </c>
       <c r="Q23" s="59">
         <f>-(BS!Q18+BS!Q19-BS!P18-BS!P19)</f>
-        <v>-2968.3237903820213</v>
+        <v>-1981.4933970816951</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
@@ -13773,47 +13799,47 @@
       </c>
       <c r="G24" s="59">
         <f>(BS!G30+BS!G31+BS!G32+BS!G33+BS!G36+BS!G37)-(BS!F30+BS!F31+BS!F32+BS!F33+BS!F36+BS!F37)</f>
-        <v>12667.817112057819</v>
+        <v>13884.006572992977</v>
       </c>
       <c r="H24" s="59">
         <f>(BS!H30+BS!H31+BS!H32+BS!H33+BS!H36+BS!H37)-(BS!G30+BS!G31+BS!G32+BS!G33+BS!G36+BS!G37)</f>
-        <v>13966.750168335522</v>
+        <v>11759.676514194871</v>
       </c>
       <c r="I24" s="59">
         <f>(BS!I30+BS!I31+BS!I32+BS!I33+BS!I36+BS!I37)-(BS!H30+BS!H31+BS!H32+BS!H33+BS!H36+BS!H37)</f>
-        <v>15377.083470241341</v>
+        <v>10250.529168737747</v>
       </c>
       <c r="J24" s="59">
         <f>(BS!J30+BS!J31+BS!J32+BS!J33+BS!J36+BS!J37)-(BS!I30+BS!I31+BS!I32+BS!I33+BS!I36+BS!I37)</f>
-        <v>15581.725320446712</v>
+        <v>6326.0587948056782</v>
       </c>
       <c r="K24" s="59">
         <f>(BS!K30+BS!K31+BS!K32+BS!K33+BS!K36+BS!K37)-(BS!J30+BS!J31+BS!J32+BS!J33+BS!J36+BS!J37)</f>
-        <v>14138.114621369154</v>
+        <v>3630.6059143141174</v>
       </c>
       <c r="L24" s="59">
         <f>(BS!L30+BS!L31+BS!L32+BS!L33+BS!L36+BS!L37)-(BS!K30+BS!K31+BS!K32+BS!K33+BS!K36+BS!K37)</f>
-        <v>10820.504709362969</v>
+        <v>3727.7073272844864</v>
       </c>
       <c r="M24" s="59">
         <f>(BS!M30+BS!M31+BS!M32+BS!M33+BS!M36+BS!M37)-(BS!L30+BS!L31+BS!L32+BS!L33+BS!L36+BS!L37)</f>
-        <v>5789.6483611900621</v>
+        <v>3798.8625858867017</v>
       </c>
       <c r="N24" s="59">
         <f>(BS!N30+BS!N31+BS!N32+BS!N33+BS!N36+BS!N37)-(BS!M30+BS!M31+BS!M32+BS!M33+BS!M36+BS!M37)</f>
-        <v>6084.4314983558143</v>
+        <v>4011.9639171716262</v>
       </c>
       <c r="O24" s="59">
         <f>(BS!O30+BS!O31+BS!O32+BS!O33+BS!O36+BS!O37)-(BS!N30+BS!N31+BS!N32+BS!N33+BS!N36+BS!N37)</f>
-        <v>6394.2436732720234</v>
+        <v>4235.1774595202442</v>
       </c>
       <c r="P24" s="59">
         <f>(BS!P30+BS!P31+BS!P32+BS!P33+BS!P36+BS!P37)-(BS!O30+BS!O31+BS!O32+BS!O33+BS!O36+BS!O37)</f>
-        <v>6719.8622118302737</v>
+        <v>4469.0811453294446</v>
       </c>
       <c r="Q24" s="59">
         <f>(BS!Q30+BS!Q31+BS!Q32+BS!Q33+BS!Q36+BS!Q37)-(BS!P30+BS!P31+BS!P32+BS!P33+BS!P36+BS!P37)</f>
-        <v>7062.1053224664065</v>
+        <v>4714.2818823554553</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
@@ -13833,48 +13859,48 @@
         <v>16813</v>
       </c>
       <c r="G25" s="62">
-        <f>SUM(G14:G24)</f>
-        <v>22205.330724669409</v>
+        <f t="shared" ref="G25:Q25" si="1">SUM(G14:G24)</f>
+        <v>22745.538112279064</v>
       </c>
       <c r="H25" s="62">
-        <f>SUM(H14:H24)</f>
-        <v>31966.384774770486</v>
+        <f t="shared" si="1"/>
+        <v>32635.444008225604</v>
       </c>
       <c r="I25" s="62">
-        <f>SUM(I14:I24)</f>
-        <v>41709.763320112899</v>
+        <f t="shared" si="1"/>
+        <v>40248.725742572635</v>
       </c>
       <c r="J25" s="62">
-        <f>SUM(J14:J24)</f>
-        <v>52304.780651565408</v>
+        <f t="shared" si="1"/>
+        <v>46408.454424611875</v>
       </c>
       <c r="K25" s="62">
-        <f>SUM(K14:K24)</f>
-        <v>62638.183961981078</v>
+        <f t="shared" si="1"/>
+        <v>50092.319318786904</v>
       </c>
       <c r="L25" s="62">
-        <f>SUM(L14:L24)</f>
-        <v>71586.686427373381</v>
+        <f t="shared" si="1"/>
+        <v>52579.501547026353</v>
       </c>
       <c r="M25" s="62">
-        <f>SUM(M14:M24)</f>
-        <v>77983.140725284611</v>
+        <f t="shared" si="1"/>
+        <v>55242.808240749117</v>
       </c>
       <c r="N25" s="62">
-        <f>SUM(N14:N24)</f>
-        <v>82120.081547010283</v>
+        <f t="shared" si="1"/>
+        <v>58006.187011620226</v>
       </c>
       <c r="O25" s="62">
-        <f>SUM(O14:O24)</f>
-        <v>86450.374750694988</v>
+        <f t="shared" si="1"/>
+        <v>60905.357407826363</v>
       </c>
       <c r="P25" s="62">
-        <f>SUM(P14:P24)</f>
-        <v>90995.390074802257</v>
+        <f t="shared" si="1"/>
+        <v>63959.559083942084</v>
       </c>
       <c r="Q25" s="62">
-        <f>SUM(Q14:Q24)</f>
-        <v>95769.567612993691</v>
+        <f t="shared" si="1"/>
+        <v>67179.766951120007</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -13913,47 +13939,47 @@
       </c>
       <c r="G27" s="59">
         <f>IS!G$42*CFS!G5</f>
-        <v>-8732.818505021467</v>
+        <v>-8962.4029026411608</v>
       </c>
       <c r="H27" s="59">
         <f>IS!H$42*CFS!H5</f>
-        <v>-11369.371465804794</v>
+        <v>-11182.318742594189</v>
       </c>
       <c r="I27" s="59">
         <f>IS!I$42*CFS!I5</f>
-        <v>-14272.158045577118</v>
+        <v>-13117.347486124167</v>
       </c>
       <c r="J27" s="59">
         <f>IS!J$42*CFS!J5</f>
-        <v>-17213.575593151985</v>
+        <v>-14311.54003947475</v>
       </c>
       <c r="K27" s="59">
         <f>IS!K$42*CFS!K5</f>
-        <v>-19882.477629459212</v>
+        <v>-14996.902393454848</v>
       </c>
       <c r="L27" s="59">
         <f>IS!L$42*CFS!L5</f>
-        <v>-21925.102677147075</v>
+        <v>-15700.594925520589</v>
       </c>
       <c r="M27" s="59">
         <f>IS!M$42*CFS!M5</f>
-        <v>-23018.035130624849</v>
+        <v>-16417.719688096779</v>
       </c>
       <c r="N27" s="59">
         <f>IS!N$42*CFS!N5</f>
-        <v>-24166.614842320596</v>
+        <v>-17175.072344719501</v>
       </c>
       <c r="O27" s="59">
         <f>IS!O$42*CFS!O5</f>
-        <v>-25373.678896989266</v>
+        <v>-17974.561813333061</v>
       </c>
       <c r="P27" s="59">
         <f>IS!P$42*CFS!P5</f>
-        <v>-26642.211117951058</v>
+        <v>-18818.206110229905</v>
       </c>
       <c r="Q27" s="59">
         <f>IS!Q$42*CFS!Q5</f>
-        <v>-27975.34978463428</v>
+        <v>-19708.137819831951</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -14123,48 +14149,48 @@
         <v>-3008</v>
       </c>
       <c r="G31" s="59">
-        <f>-G19</f>
-        <v>-5711.5180372693967</v>
+        <f t="shared" ref="G31:Q31" si="2">-G19</f>
+        <v>-5861.6729302545782</v>
       </c>
       <c r="H31" s="59">
-        <f>-H19</f>
-        <v>-7435.9005814698839</v>
+        <f t="shared" si="2"/>
+        <v>-7313.5626441907089</v>
       </c>
       <c r="I31" s="59">
-        <f>-I19</f>
-        <v>-9334.4076784832796</v>
+        <f t="shared" si="2"/>
+        <v>-8579.1278869529651</v>
       </c>
       <c r="J31" s="59">
-        <f>-J19</f>
-        <v>-11258.180555298984</v>
+        <f t="shared" si="2"/>
+        <v>-9360.1646512590942</v>
       </c>
       <c r="K31" s="59">
-        <f>-K19</f>
-        <v>-13003.720338509705</v>
+        <f t="shared" si="2"/>
+        <v>-9808.4116226775295</v>
       </c>
       <c r="L31" s="59">
-        <f>-L19</f>
-        <v>-14339.656702759019</v>
+        <f t="shared" si="2"/>
+        <v>-10268.647065252477</v>
       </c>
       <c r="M31" s="59">
-        <f>-M19</f>
-        <v>-15054.466408006643</v>
+        <f t="shared" si="2"/>
+        <v>-10737.667578397377</v>
       </c>
       <c r="N31" s="59">
-        <f>-N19</f>
-        <v>-15805.671043350869</v>
+        <f t="shared" si="2"/>
+        <v>-11232.99830769025</v>
       </c>
       <c r="O31" s="59">
-        <f>-O19</f>
-        <v>-16595.12614497876</v>
+        <f t="shared" si="2"/>
+        <v>-11755.887741149514</v>
       </c>
       <c r="P31" s="59">
-        <f>-P19</f>
-        <v>-17424.783220379395</v>
+        <f t="shared" si="2"/>
+        <v>-12307.655720295663</v>
       </c>
       <c r="Q31" s="59">
-        <f>-Q19</f>
-        <v>-18296.694795842028</v>
+        <f t="shared" si="2"/>
+        <v>-12889.697017547791</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
@@ -14284,48 +14310,48 @@
         <v>-10972</v>
       </c>
       <c r="G34" s="62">
-        <f>SUM(G27:G33)</f>
-        <v>-14444.336542290865</v>
+        <f t="shared" ref="G34:Q34" si="3">SUM(G27:G33)</f>
+        <v>-14824.075832895738</v>
       </c>
       <c r="H34" s="62">
-        <f>SUM(H27:H33)</f>
-        <v>-18805.272047274677</v>
+        <f t="shared" si="3"/>
+        <v>-18495.881386784898</v>
       </c>
       <c r="I34" s="62">
-        <f>SUM(I27:I33)</f>
-        <v>-23606.565724060398</v>
+        <f t="shared" si="3"/>
+        <v>-21696.475373077134</v>
       </c>
       <c r="J34" s="62">
-        <f>SUM(J27:J33)</f>
-        <v>-28471.756148450972</v>
+        <f t="shared" si="3"/>
+        <v>-23671.704690733844</v>
       </c>
       <c r="K34" s="62">
-        <f>SUM(K27:K33)</f>
-        <v>-32886.197967968918</v>
+        <f t="shared" si="3"/>
+        <v>-24805.314016132375</v>
       </c>
       <c r="L34" s="62">
-        <f>SUM(L27:L33)</f>
-        <v>-36264.759379906092</v>
+        <f t="shared" si="3"/>
+        <v>-25969.241990773065</v>
       </c>
       <c r="M34" s="62">
-        <f>SUM(M27:M33)</f>
-        <v>-38072.501538631492</v>
+        <f t="shared" si="3"/>
+        <v>-27155.387266494155</v>
       </c>
       <c r="N34" s="62">
-        <f>SUM(N27:N33)</f>
-        <v>-39972.285885671467</v>
+        <f t="shared" si="3"/>
+        <v>-28408.070652409751</v>
       </c>
       <c r="O34" s="62">
-        <f>SUM(O27:O33)</f>
-        <v>-41968.805041968022</v>
+        <f t="shared" si="3"/>
+        <v>-29730.449554482577</v>
       </c>
       <c r="P34" s="62">
-        <f>SUM(P27:P33)</f>
-        <v>-44066.994338330449</v>
+        <f t="shared" si="3"/>
+        <v>-31125.861830525566</v>
       </c>
       <c r="Q34" s="62">
-        <f>SUM(Q27:Q33)</f>
-        <v>-46272.044580476308</v>
+        <f t="shared" si="3"/>
+        <v>-32597.834837379742</v>
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
@@ -14364,47 +14390,47 @@
       </c>
       <c r="G36" s="59">
         <f>IS!G$52*CFS!G6</f>
-        <v>-10745.732313223343</v>
+        <v>-11177.014439818531</v>
       </c>
       <c r="H36" s="59">
         <f>IS!H$52*CFS!H6</f>
-        <v>-14014.95270109018</v>
+        <v>-13946.04066200251</v>
       </c>
       <c r="I36" s="59">
         <f>IS!I$52*CFS!I6</f>
-        <v>-17595.513104740119</v>
+        <v>-16320.814316542677</v>
       </c>
       <c r="J36" s="59">
         <f>IS!J$52*CFS!J6</f>
-        <v>-21302.542347052797</v>
+        <v>-17820.967797263907</v>
       </c>
       <c r="K36" s="59">
         <f>IS!K$52*CFS!K6</f>
-        <v>-24645.66391682551</v>
+        <v>-18651.826606821967</v>
       </c>
       <c r="L36" s="59">
         <f>IS!L$52*CFS!L6</f>
-        <v>-27208.841871678807</v>
+        <v>-19525.615083469507</v>
       </c>
       <c r="M36" s="59">
         <f>IS!M$52*CFS!M6</f>
-        <v>-28627.806209040471</v>
+        <v>-20476.331061056731</v>
       </c>
       <c r="N36" s="59">
         <f>IS!N$52*CFS!N6</f>
-        <v>-30127.358902129807</v>
+        <v>-21488.169137129356</v>
       </c>
       <c r="O36" s="59">
         <f>IS!O$52*CFS!O6</f>
-        <v>-31694.264728041759</v>
+        <v>-22546.52963576806</v>
       </c>
       <c r="P36" s="59">
         <f>IS!P$52*CFS!P6</f>
-        <v>-33337.953914412436</v>
+        <v>-23660.29588909019</v>
       </c>
       <c r="Q36" s="59">
         <f>IS!Q$52*CFS!Q6</f>
-        <v>-35064.160260080149</v>
+        <v>-24833.981870214211</v>
       </c>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
@@ -14429,43 +14455,43 @@
       </c>
       <c r="H37" s="59">
         <f>(BS!G34+BS!G38)*CFS!H7-BS!G29</f>
-        <v>543.91947308697422</v>
+        <v>575.83804811777395</v>
       </c>
       <c r="I37" s="59">
         <f>(BS!H34+BS!H38)*CFS!I7-BS!H29</f>
-        <v>591.09774558484423</v>
+        <v>542.64439343481126</v>
       </c>
       <c r="J37" s="59">
         <f>(BS!I34+BS!I38)*CFS!J7-BS!I29</f>
-        <v>602.64241300524918</v>
+        <v>476.22117572037769</v>
       </c>
       <c r="K37" s="59">
         <f>(BS!J34+BS!J38)*CFS!K7-BS!J29</f>
-        <v>551.46140385664648</v>
+        <v>325.41923693639228</v>
       </c>
       <c r="L37" s="59">
         <f>(BS!K34+BS!K38)*CFS!L7-BS!K29</f>
-        <v>425.33631237639202</v>
+        <v>178.34175908953921</v>
       </c>
       <c r="M37" s="59">
         <f>(BS!L34+BS!L38)*CFS!M7-BS!L29</f>
-        <v>122.43038476726542</v>
+        <v>-19.815429118209067</v>
       </c>
       <c r="N37" s="59">
         <f>(BS!M34+BS!M38)*CFS!N7-BS!M29</f>
-        <v>20.879461035001441</v>
+        <v>-17.458647168035441</v>
       </c>
       <c r="O37" s="59">
         <f>(BS!N34+BS!N38)*CFS!O7-BS!N29</f>
-        <v>29.612210997879629</v>
+        <v>-8.4975053881639724</v>
       </c>
       <c r="P37" s="59">
         <f>(BS!O34+BS!O38)*CFS!P7-BS!O29</f>
-        <v>40.607809904956412</v>
+        <v>0.56536883381841108</v>
       </c>
       <c r="Q37" s="59">
         <f>(BS!P34+BS!P38)*CFS!Q7-BS!P29</f>
-        <v>51.733558043286394</v>
+        <v>9.6231115468831376</v>
       </c>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
@@ -14486,23 +14512,23 @@
       </c>
       <c r="G38" s="69">
         <f>(-G27+IS!G47)*CFS!G8</f>
-        <v>14444.336542290865</v>
+        <v>14824.075832895738</v>
       </c>
       <c r="H38" s="59">
         <f>(-H27+IS!H47)*CFS!H8</f>
-        <v>15044.217637819742</v>
+        <v>14796.70510942792</v>
       </c>
       <c r="I38" s="59">
         <f>(-I27+IS!I47)*CFS!I8</f>
-        <v>14163.939434436239</v>
+        <v>13017.88522384628</v>
       </c>
       <c r="J38" s="59">
         <f>(-J27+IS!J47)*CFS!J8</f>
-        <v>11388.702459380389</v>
+        <v>9468.6818762935382</v>
       </c>
       <c r="K38" s="59">
         <f>(-K27+IS!K47)*CFS!K8</f>
-        <v>6577.2395935937839</v>
+        <v>4961.0628032264758</v>
       </c>
       <c r="L38" s="59">
         <f>(-L27+IS!L47)*CFS!L8</f>
@@ -14567,27 +14593,27 @@
       </c>
       <c r="L39" s="59">
         <f>-BS!K35*CFS!L10</f>
-        <v>-5124.3217833760518</v>
+        <v>-4896.8205422844985</v>
       </c>
       <c r="M39" s="59">
         <f>-BS!L35*CFS!M10</f>
-        <v>-4868.1056942072491</v>
+        <v>-4651.9795151702738</v>
       </c>
       <c r="N39" s="59">
         <f>-BS!M35*CFS!N10</f>
-        <v>-4624.7004094968861</v>
+        <v>-4419.3805394117608</v>
       </c>
       <c r="O39" s="59">
         <f>-BS!N35*CFS!O10</f>
-        <v>-4393.4653890220425</v>
+        <v>-4198.4115124411719</v>
       </c>
       <c r="P39" s="59">
         <f>-BS!O35*CFS!P10</f>
-        <v>-4173.7921195709405</v>
+        <v>-3988.4909368191134</v>
       </c>
       <c r="Q39" s="59">
         <f>-BS!P35*CFS!Q10</f>
-        <v>-3965.1025135923937</v>
+        <v>-3789.0663899781575</v>
       </c>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
@@ -14608,47 +14634,47 @@
       </c>
       <c r="G40" s="69">
         <f>IS!G42*CFS!G9</f>
-        <v>-4229.7177176718651</v>
+        <v>-4340.9163179582065</v>
       </c>
       <c r="H40" s="59">
         <f>IS!H42*CFS!H9</f>
-        <v>-5506.7252227966956</v>
+        <v>-5416.1267273570247</v>
       </c>
       <c r="I40" s="59">
         <f>IS!I42*CFS!I9</f>
-        <v>-6912.6822823672273</v>
+        <v>-6353.3528194837327</v>
       </c>
       <c r="J40" s="59">
         <f>IS!J42*CFS!J9</f>
-        <v>-8337.3501497796115</v>
+        <v>-6931.7568477266568</v>
       </c>
       <c r="K40" s="59">
         <f>IS!K42*CFS!K9</f>
-        <v>-9630.0258447122451</v>
+        <v>-7263.7103046762104</v>
       </c>
       <c r="L40" s="59">
         <f>IS!L42*CFS!L9</f>
-        <v>-10619.365924297977</v>
+        <v>-7604.5419352614981</v>
       </c>
       <c r="M40" s="59">
         <f>IS!M42*CFS!M9</f>
-        <v>-11148.724888993665</v>
+        <v>-7951.8794314324759</v>
       </c>
       <c r="N40" s="59">
         <f>IS!N42*CFS!N9</f>
-        <v>-11705.036457123066</v>
+        <v>-8318.7012024793603</v>
       </c>
       <c r="O40" s="59">
         <f>IS!O42*CFS!O9</f>
-        <v>-12289.674763239376</v>
+        <v>-8705.9318277972197</v>
       </c>
       <c r="P40" s="59">
         <f>IS!P42*CFS!P9</f>
-        <v>-12904.085014334652</v>
+        <v>-9114.5487282796403</v>
       </c>
       <c r="Q40" s="59">
         <f>IS!Q42*CFS!Q9</f>
-        <v>-13549.787227811446</v>
+        <v>-9545.584815592958</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
@@ -14718,48 +14744,48 @@
         <v>-2213</v>
       </c>
       <c r="G42" s="62">
-        <f>SUM(G36:G41)</f>
-        <v>-447.29348860434402</v>
+        <f t="shared" ref="G42:Q42" si="4">SUM(G36:G41)</f>
+        <v>-610.03492488099982</v>
       </c>
       <c r="H42" s="62">
-        <f>SUM(H36:H41)</f>
-        <v>-3933.540812980159</v>
+        <f t="shared" si="4"/>
+        <v>-3989.6242318138411</v>
       </c>
       <c r="I42" s="62">
-        <f>SUM(I36:I41)</f>
-        <v>-9753.1582070862642</v>
+        <f t="shared" si="4"/>
+        <v>-9113.6375187453177</v>
       </c>
       <c r="J42" s="62">
-        <f>SUM(J36:J41)</f>
-        <v>-17648.547624446772</v>
+        <f t="shared" si="4"/>
+        <v>-14807.821592976648</v>
       </c>
       <c r="K42" s="62">
-        <f>SUM(K36:K41)</f>
-        <v>-27146.988764087328</v>
+        <f t="shared" si="4"/>
+        <v>-20629.054871335309</v>
       </c>
       <c r="L42" s="62">
-        <f>SUM(L36:L41)</f>
-        <v>-42527.193266976443</v>
+        <f t="shared" si="4"/>
+        <v>-31848.635801925964</v>
       </c>
       <c r="M42" s="62">
-        <f>SUM(M36:M41)</f>
-        <v>-44522.206407474121</v>
+        <f t="shared" si="4"/>
+        <v>-33100.00543677769</v>
       </c>
       <c r="N42" s="62">
-        <f>SUM(N36:N41)</f>
-        <v>-46436.216307714756</v>
+        <f t="shared" si="4"/>
+        <v>-34243.709526188512</v>
       </c>
       <c r="O42" s="62">
-        <f>SUM(O36:O41)</f>
-        <v>-48347.792669305294</v>
+        <f t="shared" si="4"/>
+        <v>-35459.370481394617</v>
       </c>
       <c r="P42" s="62">
-        <f>SUM(P36:P41)</f>
-        <v>-50375.223238413077</v>
+        <f t="shared" si="4"/>
+        <v>-36762.770185355126</v>
       </c>
       <c r="Q42" s="62">
-        <f>SUM(Q36:Q41)</f>
-        <v>-52527.316443440701</v>
+        <f t="shared" si="4"/>
+        <v>-38159.009964238445</v>
       </c>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
@@ -14847,48 +14873,48 @@
         <v>4000</v>
       </c>
       <c r="G45" s="62">
-        <f>G25+G34+G42+G44</f>
-        <v>7313.7006937742008</v>
+        <f t="shared" ref="G45:Q45" si="5">G25+G34+G42+G44</f>
+        <v>7311.4273545023261</v>
       </c>
       <c r="H45" s="62">
-        <f>H25+H34+H42+H44</f>
-        <v>9227.5719145156509</v>
+        <f t="shared" si="5"/>
+        <v>10149.938389626865</v>
       </c>
       <c r="I45" s="62">
-        <f>I25+I34+I42+I44</f>
-        <v>8350.0393889662373</v>
+        <f t="shared" si="5"/>
+        <v>9438.6128507501835</v>
       </c>
       <c r="J45" s="62">
-        <f>J25+J34+J42+J44</f>
-        <v>6184.476878667665</v>
+        <f t="shared" si="5"/>
+        <v>7928.928140901382</v>
       </c>
       <c r="K45" s="62">
-        <f>K25+K34+K42+K44</f>
-        <v>2604.9972299248329</v>
+        <f t="shared" si="5"/>
+        <v>4657.9504313192192</v>
       </c>
       <c r="L45" s="62">
-        <f>L25+L34+L42+L44</f>
-        <v>-7205.2662195091543</v>
+        <f t="shared" si="5"/>
+        <v>-5238.3762456726763</v>
       </c>
       <c r="M45" s="62">
-        <f>M25+M34+M42+M44</f>
-        <v>-4611.5672208210017</v>
+        <f t="shared" si="5"/>
+        <v>-5012.5844625227292</v>
       </c>
       <c r="N45" s="62">
-        <f>N25+N34+N42+N44</f>
-        <v>-4288.4206463759401</v>
+        <f t="shared" si="5"/>
+        <v>-4645.5931669780366</v>
       </c>
       <c r="O45" s="62">
-        <f>O25+O34+O42+O44</f>
-        <v>-3866.2229605783286</v>
+        <f t="shared" si="5"/>
+        <v>-4284.462628050831</v>
       </c>
       <c r="P45" s="62">
-        <f>P25+P34+P42+P44</f>
-        <v>-3446.8275019412686</v>
+        <f t="shared" si="5"/>
+        <v>-3929.0729319386082</v>
       </c>
       <c r="Q45" s="62">
-        <f>Q25+Q34+Q42+Q44</f>
-        <v>-3029.7934109233174</v>
+        <f t="shared" si="5"/>
+        <v>-3577.077850498179</v>
       </c>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.25">
@@ -14913,43 +14939,43 @@
       </c>
       <c r="H46" s="59">
         <f>BS!G14</f>
-        <v>14581.700693774201</v>
+        <v>14579.427354502326</v>
       </c>
       <c r="I46" s="59">
         <f>BS!H14</f>
-        <v>23809.272608289852</v>
+        <v>24729.365744129191</v>
       </c>
       <c r="J46" s="59">
         <f>BS!I14</f>
-        <v>32159.311997256089</v>
+        <v>34167.978594879372</v>
       </c>
       <c r="K46" s="59">
         <f>BS!J14</f>
-        <v>38343.788875923754</v>
+        <v>42096.906735780751</v>
       </c>
       <c r="L46" s="59">
         <f>BS!K14</f>
-        <v>40948.786105848587</v>
+        <v>46754.857167099966</v>
       </c>
       <c r="M46" s="59">
         <f>BS!L14</f>
-        <v>33743.519886339433</v>
+        <v>41516.48092142729</v>
       </c>
       <c r="N46" s="59">
         <f>BS!M14</f>
-        <v>29131.952665518431</v>
+        <v>36503.896458904564</v>
       </c>
       <c r="O46" s="59">
         <f>BS!N14</f>
-        <v>24843.532019142491</v>
+        <v>31858.303291926528</v>
       </c>
       <c r="P46" s="59">
         <f>BS!O14</f>
-        <v>20977.309058564162</v>
+        <v>27573.840663875697</v>
       </c>
       <c r="Q46" s="59">
         <f>BS!P14</f>
-        <v>17530.481556622894</v>
+        <v>23644.767731937089</v>
       </c>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.25">
@@ -14969,48 +14995,48 @@
         <v>7268</v>
       </c>
       <c r="G47" s="62">
-        <f>G46+G45</f>
-        <v>14581.700693774201</v>
+        <f t="shared" ref="G47:Q47" si="6">G46+G45</f>
+        <v>14579.427354502326</v>
       </c>
       <c r="H47" s="62">
-        <f>H46+H45</f>
-        <v>23809.272608289852</v>
+        <f t="shared" si="6"/>
+        <v>24729.365744129191</v>
       </c>
       <c r="I47" s="62">
-        <f>I46+I45</f>
-        <v>32159.311997256089</v>
+        <f t="shared" si="6"/>
+        <v>34167.978594879372</v>
       </c>
       <c r="J47" s="62">
-        <f>J46+J45</f>
-        <v>38343.788875923754</v>
+        <f t="shared" si="6"/>
+        <v>42096.906735780751</v>
       </c>
       <c r="K47" s="62">
-        <f>K46+K45</f>
-        <v>40948.786105848587</v>
+        <f t="shared" si="6"/>
+        <v>46754.857167099966</v>
       </c>
       <c r="L47" s="62">
-        <f>L46+L45</f>
-        <v>33743.519886339433</v>
+        <f t="shared" si="6"/>
+        <v>41516.48092142729</v>
       </c>
       <c r="M47" s="62">
-        <f>M46+M45</f>
-        <v>29131.952665518431</v>
+        <f t="shared" si="6"/>
+        <v>36503.896458904564</v>
       </c>
       <c r="N47" s="62">
-        <f>N46+N45</f>
-        <v>24843.532019142491</v>
+        <f t="shared" si="6"/>
+        <v>31858.303291926528</v>
       </c>
       <c r="O47" s="62">
-        <f>O46+O45</f>
-        <v>20977.309058564162</v>
+        <f t="shared" si="6"/>
+        <v>27573.840663875697</v>
       </c>
       <c r="P47" s="62">
-        <f>P46+P45</f>
-        <v>17530.481556622894</v>
+        <f t="shared" si="6"/>
+        <v>23644.767731937089</v>
       </c>
       <c r="Q47" s="62">
-        <f>Q46+Q45</f>
-        <v>14500.688145699576</v>
+        <f t="shared" si="6"/>
+        <v>20067.68988143891</v>
       </c>
     </row>
   </sheetData>
@@ -15034,7 +15060,7 @@
   <sheetData>
     <row r="1" spans="2:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:17" ht="24" x14ac:dyDescent="0.4">
-      <c r="B2" s="180" t="s">
+      <c r="B2" s="176" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="70"/>
@@ -15062,7 +15088,7 @@
       <c r="E4" s="76"/>
       <c r="F4" s="76"/>
       <c r="G4" s="76"/>
-      <c r="H4" s="192">
+      <c r="H4" s="185">
         <f ca="1">TODAY()</f>
         <v>46245</v>
       </c>
@@ -15084,7 +15110,7 @@
       <c r="E5" s="76"/>
       <c r="F5" s="76"/>
       <c r="G5" s="76"/>
-      <c r="H5" s="191">
+      <c r="H5" s="184">
         <f>Main!C3</f>
         <v>1215.02</v>
       </c>
@@ -15107,7 +15133,7 @@
       <c r="E6" s="76"/>
       <c r="F6" s="76"/>
       <c r="G6" s="76"/>
-      <c r="H6" s="193">
+      <c r="H6" s="186">
         <f>Main!C4</f>
         <v>893.7</v>
       </c>
@@ -15140,7 +15166,7 @@
       <c r="Q7" s="77"/>
     </row>
     <row r="8" spans="2:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B8" s="188" t="s">
+      <c r="B8" s="181" t="s">
         <v>259</v>
       </c>
       <c r="C8" s="80"/>
@@ -15168,13 +15194,13 @@
       <c r="G9" s="81"/>
       <c r="H9" s="81"/>
       <c r="I9" s="83"/>
-      <c r="J9" s="185" t="s">
+      <c r="J9" s="200" t="s">
         <v>260</v>
       </c>
-      <c r="K9" s="186"/>
-      <c r="L9" s="186"/>
-      <c r="M9" s="186"/>
-      <c r="N9" s="187"/>
+      <c r="K9" s="201"/>
+      <c r="L9" s="201"/>
+      <c r="M9" s="201"/>
+      <c r="N9" s="202"/>
       <c r="O9" s="77"/>
       <c r="P9" s="77"/>
       <c r="Q9" s="77"/>
@@ -15182,7 +15208,7 @@
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="75"/>
       <c r="C10" s="84">
-        <f t="shared" ref="C10:G10" si="0">D10-365</f>
+        <f t="shared" ref="C10:D10" si="0">D10-365</f>
         <v>-730</v>
       </c>
       <c r="D10" s="85">
@@ -15228,41 +15254,41 @@
       <c r="C11" s="90"/>
       <c r="D11" s="91"/>
       <c r="E11" s="91"/>
-      <c r="F11" s="194">
+      <c r="F11" s="187">
         <f>IS!C42</f>
         <v>28541.400000000005</v>
       </c>
-      <c r="G11" s="194">
+      <c r="G11" s="187">
         <f>IS!D42</f>
         <v>34124.100000000006</v>
       </c>
-      <c r="H11" s="194">
+      <c r="H11" s="187">
         <f>IS!E42</f>
         <v>45042.69999999999</v>
       </c>
-      <c r="I11" s="194">
+      <c r="I11" s="187">
         <f>IS!F42</f>
         <v>65179.500000000007</v>
       </c>
       <c r="J11" s="95">
         <f>IS!G42</f>
-        <v>87634.083599999998</v>
+        <v>89937.969599999997</v>
       </c>
       <c r="K11" s="95">
         <f>IS!H42</f>
-        <v>114091.96801020001</v>
+        <v>112214.88858</v>
       </c>
       <c r="L11" s="95">
         <f>IS!I42</f>
-        <v>143221.51440561094</v>
+        <v>131632.95739494238</v>
       </c>
       <c r="M11" s="95">
         <f>IS!J42</f>
-        <v>172738.72366840087</v>
+        <v>143616.71384134586</v>
       </c>
       <c r="N11" s="95">
         <f>IS!K42</f>
-        <v>199521.23197719833</v>
+        <v>150494.34467616153</v>
       </c>
       <c r="O11" s="93"/>
       <c r="P11" s="77"/>
@@ -15293,41 +15319,41 @@
       <c r="C13" s="90"/>
       <c r="D13" s="92"/>
       <c r="E13" s="92"/>
-      <c r="F13" s="195">
+      <c r="F13" s="188">
         <f>IS!C50+IS!C49</f>
         <v>6905.2999999999993</v>
       </c>
-      <c r="G13" s="195">
+      <c r="G13" s="188">
         <f>IS!D50+IS!D49</f>
         <v>6457.9000000000005</v>
       </c>
-      <c r="H13" s="195">
+      <c r="H13" s="188">
         <f>IS!E50+IS!E49</f>
         <v>12899</v>
       </c>
-      <c r="I13" s="195">
+      <c r="I13" s="188">
         <f>IS!F50+IS!F49</f>
         <v>26302.800000000003</v>
       </c>
       <c r="J13" s="95">
         <f>IS!G50+IS!G49</f>
-        <v>26364.432724840575</v>
+        <v>27068.439340721379</v>
       </c>
       <c r="K13" s="95">
         <f>IS!H50+IS!H49</f>
-        <v>34406.856048435176</v>
+        <v>33833.270229781549</v>
       </c>
       <c r="L13" s="95">
         <f>IS!I50+IS!I49</f>
-        <v>43210.842037549621</v>
+        <v>39669.685572332761</v>
       </c>
       <c r="M13" s="95">
         <f>IS!J50+IS!J49</f>
-        <v>52307.204340792152</v>
+        <v>43408.288515099077</v>
       </c>
       <c r="N13" s="95">
         <f>IS!K50+IS!K49</f>
-        <v>60492.935370846739</v>
+        <v>45511.615541665633</v>
       </c>
       <c r="O13" s="77"/>
       <c r="P13" s="77"/>
@@ -15358,41 +15384,41 @@
       <c r="C15" s="90"/>
       <c r="D15" s="92"/>
       <c r="E15" s="92"/>
-      <c r="F15" s="195">
+      <c r="F15" s="188">
         <f>CFS!C15</f>
         <v>1522.5</v>
       </c>
-      <c r="G15" s="195">
+      <c r="G15" s="188">
         <f>CFS!D15</f>
         <v>1527</v>
       </c>
-      <c r="H15" s="195">
+      <c r="H15" s="188">
         <f>CFS!E15</f>
         <v>1767</v>
       </c>
-      <c r="I15" s="195">
+      <c r="I15" s="188">
         <f>CFS!F15</f>
         <v>1997</v>
       </c>
       <c r="J15" s="95">
         <f>CFS!G15</f>
-        <v>3679.7531309583919</v>
+        <v>3776.4932504827457</v>
       </c>
       <c r="K15" s="95">
         <f>CFS!H15</f>
-        <v>4790.719081619266</v>
+        <v>4711.9005600282435</v>
       </c>
       <c r="L15" s="95">
         <f>CFS!I15</f>
-        <v>6013.8680568646814</v>
+        <v>5527.264817673652</v>
       </c>
       <c r="M15" s="95">
         <f>CFS!J15</f>
-        <v>7253.2949868897158</v>
+        <v>6030.462471974176</v>
       </c>
       <c r="N15" s="95">
         <f>CFS!K15</f>
-        <v>8377.8918874981064</v>
+        <v>6319.2540306730216</v>
       </c>
       <c r="O15" s="77"/>
       <c r="P15" s="77"/>
@@ -15444,14 +15470,14 @@
       <c r="F18" s="81"/>
       <c r="G18" s="81"/>
       <c r="H18" s="81"/>
-      <c r="I18" s="182"/>
-      <c r="J18" s="185" t="s">
+      <c r="I18" s="178"/>
+      <c r="J18" s="200" t="s">
         <v>260</v>
       </c>
-      <c r="K18" s="186"/>
-      <c r="L18" s="186"/>
-      <c r="M18" s="186"/>
-      <c r="N18" s="187"/>
+      <c r="K18" s="201"/>
+      <c r="L18" s="201"/>
+      <c r="M18" s="201"/>
+      <c r="N18" s="202"/>
       <c r="O18" s="77"/>
       <c r="P18" s="77"/>
       <c r="Q18" s="77"/>
@@ -15459,7 +15485,7 @@
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="75"/>
       <c r="C19" s="84">
-        <f t="shared" ref="C19:G19" si="1">D19-365</f>
+        <f t="shared" ref="C19:D19" si="1">D19-365</f>
         <v>-730</v>
       </c>
       <c r="D19" s="85">
@@ -15479,19 +15505,19 @@
       <c r="I19" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="J19" s="183" t="s">
+      <c r="J19" s="179" t="s">
         <v>119</v>
       </c>
-      <c r="K19" s="183" t="s">
+      <c r="K19" s="179" t="s">
         <v>120</v>
       </c>
-      <c r="L19" s="183" t="s">
+      <c r="L19" s="179" t="s">
         <v>121</v>
       </c>
-      <c r="M19" s="183" t="s">
+      <c r="M19" s="179" t="s">
         <v>122</v>
       </c>
-      <c r="N19" s="184" t="s">
+      <c r="N19" s="180" t="s">
         <v>123</v>
       </c>
       <c r="O19" s="77"/>
@@ -15505,41 +15531,41 @@
       <c r="C20" s="97"/>
       <c r="D20" s="97"/>
       <c r="E20" s="92"/>
-      <c r="F20" s="195">
+      <c r="F20" s="188">
         <f>BS!C15</f>
         <v>6896</v>
       </c>
-      <c r="G20" s="195">
+      <c r="G20" s="188">
         <f>BS!D15</f>
         <v>9090.5</v>
       </c>
-      <c r="H20" s="195">
+      <c r="H20" s="188">
         <f>BS!E15</f>
         <v>11006</v>
       </c>
-      <c r="I20" s="195">
+      <c r="I20" s="188">
         <f>BS!F15</f>
         <v>17760</v>
       </c>
       <c r="J20" s="95">
         <f>BS!G15</f>
-        <v>23878.386988792485</v>
+        <v>24506.145952270264</v>
       </c>
       <c r="K20" s="95">
         <f>BS!H15</f>
-        <v>31087.586616361768</v>
+        <v>30576.123185676472</v>
       </c>
       <c r="L20" s="95">
         <f>BS!I15</f>
-        <v>39024.756186280196</v>
+        <v>35867.125757856018</v>
       </c>
       <c r="M20" s="95">
         <f>BS!J15</f>
-        <v>47067.555479112278</v>
+        <v>39132.439460601905</v>
       </c>
       <c r="N20" s="95">
         <f>BS!K15</f>
-        <v>54365.208077923911</v>
+        <v>41006.444686575203</v>
       </c>
       <c r="O20" s="77"/>
       <c r="P20" s="77"/>
@@ -15552,41 +15578,41 @@
       <c r="C21" s="97"/>
       <c r="D21" s="97"/>
       <c r="E21" s="92"/>
-      <c r="F21" s="195">
+      <c r="F21" s="188">
         <f>BS!C17</f>
         <v>4310</v>
       </c>
-      <c r="G21" s="195">
+      <c r="G21" s="188">
         <f>BS!D17</f>
         <v>5772.8</v>
       </c>
-      <c r="H21" s="195">
+      <c r="H21" s="188">
         <f>BS!E17</f>
         <v>7589</v>
       </c>
-      <c r="I21" s="195">
+      <c r="I21" s="188">
         <f>BS!F17</f>
         <v>13744</v>
       </c>
       <c r="J21" s="95">
         <f>BS!G17</f>
-        <v>21276.467528841309</v>
+        <v>21835.822447104551</v>
       </c>
       <c r="K21" s="95">
         <f>BS!H17</f>
-        <v>27700.113391390816</v>
+        <v>27244.381809509963</v>
       </c>
       <c r="L21" s="95">
         <f>BS!I17</f>
-        <v>34772.405615507108</v>
+        <v>31958.847844206168</v>
       </c>
       <c r="M21" s="95">
         <f>BS!J17</f>
-        <v>41938.817571023508</v>
+        <v>34868.355132138218</v>
       </c>
       <c r="N21" s="95">
         <f>BS!K17</f>
-        <v>48441.278085976075</v>
+        <v>36538.158513665374</v>
       </c>
       <c r="O21" s="77"/>
       <c r="P21" s="77"/>
@@ -15599,41 +15625,41 @@
       <c r="C22" s="97"/>
       <c r="D22" s="97"/>
       <c r="E22" s="92"/>
-      <c r="F22" s="195">
+      <c r="F22" s="188">
         <f>BS!C18</f>
         <v>2947</v>
       </c>
-      <c r="G22" s="195">
+      <c r="G22" s="188">
         <f>BS!D18</f>
         <v>5540.8</v>
       </c>
-      <c r="H22" s="195">
+      <c r="H22" s="188">
         <f>BS!E18</f>
         <v>8341</v>
       </c>
-      <c r="I22" s="195">
+      <c r="I22" s="188">
         <f>BS!F18</f>
         <v>14315</v>
       </c>
       <c r="J22" s="95">
         <f>BS!G18</f>
-        <v>19246.571494626376</v>
+        <v>19752.5607717764</v>
       </c>
       <c r="K22" s="95">
         <f>BS!H18</f>
-        <v>25057.365000744299</v>
+        <v>24645.112804220651</v>
       </c>
       <c r="L22" s="95">
         <f>BS!I18</f>
-        <v>31454.920315686995</v>
+        <v>28909.79196079442</v>
       </c>
       <c r="M22" s="95">
         <f>BS!J18</f>
-        <v>37937.615804250694</v>
+        <v>31541.715702619163</v>
       </c>
       <c r="N22" s="95">
         <f>BS!K18</f>
-        <v>43819.70459659239</v>
+        <v>33052.210342811042</v>
       </c>
       <c r="O22" s="77"/>
       <c r="P22" s="77"/>
@@ -15664,41 +15690,41 @@
       <c r="C24" s="99"/>
       <c r="D24" s="99"/>
       <c r="E24" s="99"/>
-      <c r="F24" s="196">
+      <c r="F24" s="189">
         <f>BS!C30</f>
         <v>1930.6</v>
       </c>
-      <c r="G24" s="196">
+      <c r="G24" s="189">
         <f>BS!D30</f>
         <v>2598.8000000000002</v>
       </c>
-      <c r="H24" s="196">
+      <c r="H24" s="189">
         <f>BS!E30</f>
         <v>3229</v>
       </c>
-      <c r="I24" s="196">
+      <c r="I24" s="189">
         <f>BS!F30</f>
         <v>5379</v>
       </c>
       <c r="J24" s="95">
         <f>BS!G30</f>
-        <v>8326.9876919119179</v>
+        <v>8545.9028625564151</v>
       </c>
       <c r="K24" s="95">
         <f>BS!H30</f>
-        <v>10841.014983432129</v>
+        <v>10662.654958771398</v>
       </c>
       <c r="L24" s="95">
         <f>BS!I30</f>
-        <v>13608.903507407793</v>
+        <v>12507.759207944191</v>
       </c>
       <c r="M24" s="95">
         <f>BS!J30</f>
-        <v>16413.627744072717</v>
+        <v>13646.4553445701</v>
       </c>
       <c r="N24" s="95">
         <f>BS!K30</f>
-        <v>18958.500787577508</v>
+        <v>14299.967596406143</v>
       </c>
       <c r="O24" s="77"/>
       <c r="P24" s="77"/>
@@ -15711,41 +15737,41 @@
       <c r="C25" s="97"/>
       <c r="D25" s="97"/>
       <c r="E25" s="99"/>
-      <c r="F25" s="196">
+      <c r="F25" s="189">
         <f>BS!C31</f>
         <v>1059.8</v>
       </c>
-      <c r="G25" s="196">
+      <c r="G25" s="189">
         <f>BS!D31</f>
         <v>1650.4</v>
       </c>
-      <c r="H25" s="196">
+      <c r="H25" s="189">
         <f>BS!E31</f>
         <v>2094</v>
       </c>
-      <c r="I25" s="196">
+      <c r="I25" s="189">
         <f>BS!F31</f>
         <v>2375</v>
       </c>
       <c r="J25" s="95">
         <f>BS!G31</f>
-        <v>3193.1964582422379</v>
+        <v>3277.1450808919976</v>
       </c>
       <c r="K25" s="95">
         <f>BS!H31</f>
-        <v>4157.2645390686484</v>
+        <v>4088.8678246611271</v>
       </c>
       <c r="L25" s="95">
         <f>BS!I31</f>
-        <v>5218.6822039648341</v>
+        <v>4796.4202519655428</v>
       </c>
       <c r="M25" s="95">
         <f>BS!J31</f>
-        <v>6294.2254652529091</v>
+        <v>5233.0824166063921</v>
       </c>
       <c r="N25" s="95">
         <f>BS!K31</f>
-        <v>7270.1221387989463</v>
+        <v>5483.6884082554116</v>
       </c>
       <c r="O25" s="77"/>
       <c r="P25" s="77"/>
@@ -15776,41 +15802,41 @@
       <c r="C27" s="97"/>
       <c r="D27" s="97"/>
       <c r="E27" s="99"/>
-      <c r="F27" s="196">
+      <c r="F27" s="189">
         <f>BS!C29+BS!C35</f>
         <v>16238.6</v>
       </c>
-      <c r="G27" s="196">
+      <c r="G27" s="189">
         <f>BS!D29+BS!D35</f>
         <v>25225.3</v>
       </c>
-      <c r="H27" s="196">
+      <c r="H27" s="189">
         <f>BS!E29+BS!E35</f>
         <v>33644</v>
       </c>
-      <c r="I27" s="196">
+      <c r="I27" s="189">
         <f>BS!F29+BS!F35</f>
         <v>42503</v>
       </c>
       <c r="J27" s="95">
         <f>BS!G29+BS!G35</f>
-        <v>57031.156542290868</v>
+        <v>57410.895832895738</v>
       </c>
       <c r="K27" s="95">
         <f>BS!H29+BS!H35</f>
-        <v>72619.293653197587</v>
+        <v>72783.438990441442</v>
       </c>
       <c r="L27" s="95">
         <f>BS!I29+BS!I35</f>
-        <v>87374.330833218672</v>
+        <v>86343.968607722534</v>
       </c>
       <c r="M27" s="95">
         <f>BS!J29+BS!J35</f>
-        <v>99365.675705604313</v>
+        <v>96288.871659736455</v>
       </c>
       <c r="N27" s="95">
         <f>BS!K29+BS!K35</f>
-        <v>106494.37670305475</v>
+        <v>101575.35369989932</v>
       </c>
       <c r="O27" s="77"/>
       <c r="P27" s="77"/>
@@ -15841,41 +15867,41 @@
       <c r="C29" s="97"/>
       <c r="D29" s="97"/>
       <c r="E29" s="97"/>
-      <c r="F29" s="197">
+      <c r="F29" s="190">
         <f>CFS!C27</f>
         <v>-1854.3</v>
       </c>
-      <c r="G29" s="197">
+      <c r="G29" s="190">
         <f>CFS!D27</f>
         <v>-3448</v>
       </c>
-      <c r="H29" s="197">
+      <c r="H29" s="190">
         <f>CFS!E27</f>
         <v>-5058</v>
       </c>
-      <c r="I29" s="197">
+      <c r="I29" s="190">
         <f>CFS!F27</f>
         <v>-7841</v>
       </c>
       <c r="J29" s="95">
         <f>CFS!G27</f>
-        <v>-8732.818505021467</v>
+        <v>-8962.4029026411608</v>
       </c>
       <c r="K29" s="95">
         <f>CFS!H27</f>
-        <v>-11369.371465804794</v>
+        <v>-11182.318742594189</v>
       </c>
       <c r="L29" s="95">
         <f>CFS!I27</f>
-        <v>-14272.158045577118</v>
+        <v>-13117.347486124167</v>
       </c>
       <c r="M29" s="95">
         <f>CFS!J27</f>
-        <v>-17213.575593151985</v>
+        <v>-14311.54003947475</v>
       </c>
       <c r="N29" s="95">
         <f>CFS!K27</f>
-        <v>-19882.477629459212</v>
+        <v>-14996.902393454848</v>
       </c>
       <c r="O29" s="77"/>
       <c r="P29" s="77"/>
@@ -15930,13 +15956,13 @@
       <c r="G32" s="81"/>
       <c r="H32" s="81"/>
       <c r="I32" s="103"/>
-      <c r="J32" s="185" t="s">
+      <c r="J32" s="200" t="s">
         <v>260</v>
       </c>
-      <c r="K32" s="186"/>
-      <c r="L32" s="186"/>
-      <c r="M32" s="186"/>
-      <c r="N32" s="187"/>
+      <c r="K32" s="201"/>
+      <c r="L32" s="201"/>
+      <c r="M32" s="201"/>
+      <c r="N32" s="202"/>
       <c r="O32" s="100"/>
       <c r="P32" s="100"/>
       <c r="Q32" s="100"/>
@@ -15944,7 +15970,7 @@
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="104"/>
       <c r="C33" s="84">
-        <f t="shared" ref="C33:G33" si="2">D33-365</f>
+        <f t="shared" ref="C33:D33" si="2">D33-365</f>
         <v>-730</v>
       </c>
       <c r="D33" s="85">
@@ -16022,52 +16048,52 @@
         <v>273</v>
       </c>
       <c r="C35" s="108">
-        <f>C11</f>
+        <f t="shared" ref="C35:N35" si="4">C11</f>
         <v>0</v>
       </c>
       <c r="D35" s="109">
-        <f>D11</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E35" s="109">
-        <f>E11</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F35" s="109">
-        <f>F11</f>
+        <f t="shared" si="4"/>
         <v>28541.400000000005</v>
       </c>
       <c r="G35" s="109">
-        <f>G11</f>
+        <f t="shared" si="4"/>
         <v>34124.100000000006</v>
       </c>
       <c r="H35" s="109">
-        <f>H11</f>
+        <f t="shared" si="4"/>
         <v>45042.69999999999</v>
       </c>
       <c r="I35" s="110">
-        <f>I11</f>
+        <f t="shared" si="4"/>
         <v>65179.500000000007</v>
       </c>
       <c r="J35" s="110">
-        <f>J11</f>
-        <v>87634.083599999998</v>
+        <f t="shared" si="4"/>
+        <v>89937.969599999997</v>
       </c>
       <c r="K35" s="110">
-        <f>K11</f>
-        <v>114091.96801020001</v>
+        <f t="shared" si="4"/>
+        <v>112214.88858</v>
       </c>
       <c r="L35" s="110">
-        <f>L11</f>
-        <v>143221.51440561094</v>
+        <f t="shared" si="4"/>
+        <v>131632.95739494238</v>
       </c>
       <c r="M35" s="110">
-        <f>M11</f>
-        <v>172738.72366840087</v>
+        <f t="shared" si="4"/>
+        <v>143616.71384134586</v>
       </c>
       <c r="N35" s="110">
-        <f>N11</f>
-        <v>199521.23197719833</v>
+        <f t="shared" si="4"/>
+        <v>150494.34467616153</v>
       </c>
       <c r="O35" s="100"/>
       <c r="P35" s="100"/>
@@ -16078,52 +16104,52 @@
         <v>262</v>
       </c>
       <c r="C36" s="108">
-        <f>C13</f>
+        <f t="shared" ref="C36:N36" si="5">C13</f>
         <v>0</v>
       </c>
       <c r="D36" s="110">
-        <f>D13</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E36" s="110">
-        <f>E13</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F36" s="110">
-        <f>F13</f>
+        <f t="shared" si="5"/>
         <v>6905.2999999999993</v>
       </c>
       <c r="G36" s="110">
-        <f>G13</f>
+        <f t="shared" si="5"/>
         <v>6457.9000000000005</v>
       </c>
       <c r="H36" s="110">
-        <f>H13</f>
+        <f t="shared" si="5"/>
         <v>12899</v>
       </c>
       <c r="I36" s="110">
-        <f>I13</f>
+        <f t="shared" si="5"/>
         <v>26302.800000000003</v>
       </c>
       <c r="J36" s="110">
-        <f>J13</f>
-        <v>26364.432724840575</v>
+        <f t="shared" si="5"/>
+        <v>27068.439340721379</v>
       </c>
       <c r="K36" s="110">
-        <f>K13</f>
-        <v>34406.856048435176</v>
+        <f t="shared" si="5"/>
+        <v>33833.270229781549</v>
       </c>
       <c r="L36" s="110">
-        <f>L13</f>
-        <v>43210.842037549621</v>
+        <f t="shared" si="5"/>
+        <v>39669.685572332761</v>
       </c>
       <c r="M36" s="110">
-        <f>M13</f>
-        <v>52307.204340792152</v>
+        <f t="shared" si="5"/>
+        <v>43408.288515099077</v>
       </c>
       <c r="N36" s="110">
-        <f>N13</f>
-        <v>60492.935370846739</v>
+        <f t="shared" si="5"/>
+        <v>45511.615541665633</v>
       </c>
       <c r="O36" s="100"/>
       <c r="P36" s="100"/>
@@ -16136,41 +16162,41 @@
       <c r="C37" s="111"/>
       <c r="D37" s="111"/>
       <c r="E37" s="111"/>
-      <c r="F37" s="198">
+      <c r="F37" s="191">
         <f>IS!C12</f>
         <v>8.2510578279266583E-2</v>
       </c>
-      <c r="G37" s="198">
+      <c r="G37" s="191">
         <f>IS!D12</f>
         <v>0.20818680100117226</v>
       </c>
-      <c r="H37" s="198">
+      <c r="H37" s="191">
         <f>IS!E12</f>
         <v>0.16485414382940469</v>
       </c>
-      <c r="I37" s="198">
+      <c r="I37" s="191">
         <f>IS!F12</f>
         <v>0.19786023519536136</v>
       </c>
-      <c r="J37" s="198">
+      <c r="J37" s="191">
         <f>IS!G12</f>
-        <v>0.2</v>
-      </c>
-      <c r="K37" s="198">
+        <v>0.19</v>
+      </c>
+      <c r="K37" s="191">
         <f>IS!H12</f>
-        <v>0.2</v>
-      </c>
-      <c r="L37" s="198">
+        <v>0.19</v>
+      </c>
+      <c r="L37" s="191">
         <f>IS!I12</f>
-        <v>0.2</v>
-      </c>
-      <c r="M37" s="198">
+        <v>0.19</v>
+      </c>
+      <c r="M37" s="191">
         <f>IS!J12</f>
-        <v>0.2</v>
-      </c>
-      <c r="N37" s="198">
+        <v>0.19</v>
+      </c>
+      <c r="N37" s="191">
         <f>IS!K12</f>
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="O37" s="100"/>
       <c r="P37" s="89"/>
@@ -16181,52 +16207,52 @@
         <v>275</v>
       </c>
       <c r="C38" s="112">
-        <f t="shared" ref="C38:N38" si="4">C36*(1-C37)</f>
+        <f t="shared" ref="C38:N38" si="6">C36*(1-C37)</f>
         <v>0</v>
       </c>
       <c r="D38" s="112">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E38" s="112">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F38" s="112">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6335.5397038081801</v>
       </c>
       <c r="G38" s="112">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5113.4504578145297</v>
       </c>
       <c r="H38" s="112">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>10772.546398744509</v>
       </c>
       <c r="I38" s="112">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21098.521805703451</v>
       </c>
       <c r="J38" s="113">
-        <f t="shared" si="4"/>
-        <v>21091.546179872461</v>
+        <f t="shared" si="6"/>
+        <v>21925.43586598432</v>
       </c>
       <c r="K38" s="113">
-        <f t="shared" si="4"/>
-        <v>27525.484838748143</v>
+        <f t="shared" si="6"/>
+        <v>27404.948886123057</v>
       </c>
       <c r="L38" s="113">
-        <f t="shared" si="4"/>
-        <v>34568.673630039695</v>
+        <f t="shared" si="6"/>
+        <v>32132.445313589538</v>
       </c>
       <c r="M38" s="113">
-        <f t="shared" si="4"/>
-        <v>41845.763472633727</v>
+        <f t="shared" si="6"/>
+        <v>35160.713697230254</v>
       </c>
       <c r="N38" s="113">
-        <f t="shared" si="4"/>
-        <v>48394.348296677395</v>
+        <f t="shared" si="6"/>
+        <v>36864.408588749167</v>
       </c>
       <c r="O38" s="100"/>
       <c r="P38" s="100"/>
@@ -16237,52 +16263,52 @@
         <v>276</v>
       </c>
       <c r="C39" s="115">
-        <f>C15</f>
+        <f t="shared" ref="C39:N39" si="7">C15</f>
         <v>0</v>
       </c>
       <c r="D39" s="115">
-        <f>D15</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E39" s="115">
-        <f>E15</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F39" s="115">
-        <f>F15</f>
+        <f t="shared" si="7"/>
         <v>1522.5</v>
       </c>
       <c r="G39" s="115">
-        <f>G15</f>
+        <f t="shared" si="7"/>
         <v>1527</v>
       </c>
       <c r="H39" s="115">
-        <f>H15</f>
+        <f t="shared" si="7"/>
         <v>1767</v>
       </c>
       <c r="I39" s="115">
-        <f>I15</f>
+        <f t="shared" si="7"/>
         <v>1997</v>
       </c>
       <c r="J39" s="115">
-        <f>J15</f>
-        <v>3679.7531309583919</v>
+        <f t="shared" si="7"/>
+        <v>3776.4932504827457</v>
       </c>
       <c r="K39" s="115">
-        <f>K15</f>
-        <v>4790.719081619266</v>
+        <f t="shared" si="7"/>
+        <v>4711.9005600282435</v>
       </c>
       <c r="L39" s="115">
-        <f>L15</f>
-        <v>6013.8680568646814</v>
+        <f t="shared" si="7"/>
+        <v>5527.264817673652</v>
       </c>
       <c r="M39" s="115">
-        <f>M15</f>
-        <v>7253.2949868897158</v>
+        <f t="shared" si="7"/>
+        <v>6030.462471974176</v>
       </c>
       <c r="N39" s="115">
-        <f>N15</f>
-        <v>8377.8918874981064</v>
+        <f t="shared" si="7"/>
+        <v>6319.2540306730216</v>
       </c>
       <c r="O39" s="100"/>
       <c r="P39" s="100"/>
@@ -16294,48 +16320,48 @@
       </c>
       <c r="C40" s="96"/>
       <c r="D40" s="116">
-        <f>(D20-C20)*-1</f>
+        <f t="shared" ref="D40:N40" si="8">(D20-C20)*-1</f>
         <v>0</v>
       </c>
       <c r="E40" s="116">
-        <f>(E20-D20)*-1</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F40" s="116">
-        <f>(F20-E20)*-1</f>
+        <f t="shared" si="8"/>
         <v>-6896</v>
       </c>
       <c r="G40" s="116">
-        <f>(G20-F20)*-1</f>
+        <f t="shared" si="8"/>
         <v>-2194.5</v>
       </c>
       <c r="H40" s="116">
-        <f>(H20-G20)*-1</f>
+        <f t="shared" si="8"/>
         <v>-1915.5</v>
       </c>
       <c r="I40" s="116">
-        <f>(I20-H20)*-1</f>
+        <f t="shared" si="8"/>
         <v>-6754</v>
       </c>
       <c r="J40" s="116">
-        <f>(J20-I20)*-1</f>
-        <v>-6118.3869887924848</v>
+        <f t="shared" si="8"/>
+        <v>-6746.1459522702644</v>
       </c>
       <c r="K40" s="116">
-        <f>(K20-J20)*-1</f>
-        <v>-7209.1996275692836</v>
+        <f t="shared" si="8"/>
+        <v>-6069.9772334062072</v>
       </c>
       <c r="L40" s="116">
-        <f>(L20-K20)*-1</f>
-        <v>-7937.1695699184274</v>
+        <f t="shared" si="8"/>
+        <v>-5291.0025721795464</v>
       </c>
       <c r="M40" s="116">
-        <f>(M20-L20)*-1</f>
-        <v>-8042.7992928320818</v>
+        <f t="shared" si="8"/>
+        <v>-3265.313702745887</v>
       </c>
       <c r="N40" s="116">
-        <f>(N20-M20)*-1</f>
-        <v>-7297.6525988116337</v>
+        <f t="shared" si="8"/>
+        <v>-1874.0052259732984</v>
       </c>
       <c r="O40" s="100"/>
       <c r="P40" s="100"/>
@@ -16347,48 +16373,48 @@
       </c>
       <c r="C41" s="96"/>
       <c r="D41" s="116">
-        <f>(D21-C21)*-1</f>
+        <f t="shared" ref="D41:N41" si="9">(D21-C21)*-1</f>
         <v>0</v>
       </c>
       <c r="E41" s="116">
-        <f>(E21-D21)*-1</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F41" s="116">
-        <f>(F21-E21)*-1</f>
+        <f t="shared" si="9"/>
         <v>-4310</v>
       </c>
       <c r="G41" s="116">
-        <f>(G21-F21)*-1</f>
+        <f t="shared" si="9"/>
         <v>-1462.8000000000002</v>
       </c>
       <c r="H41" s="116">
-        <f>(H21-G21)*-1</f>
+        <f t="shared" si="9"/>
         <v>-1816.1999999999998</v>
       </c>
       <c r="I41" s="116">
-        <f>(I21-H21)*-1</f>
+        <f t="shared" si="9"/>
         <v>-6155</v>
       </c>
       <c r="J41" s="116">
-        <f>(J21-I21)*-1</f>
-        <v>-7532.4675288413091</v>
+        <f t="shared" si="9"/>
+        <v>-8091.8224471045505</v>
       </c>
       <c r="K41" s="116">
-        <f>(K21-J21)*-1</f>
-        <v>-6423.645862549507</v>
+        <f t="shared" si="9"/>
+        <v>-5408.5593624054127</v>
       </c>
       <c r="L41" s="116">
-        <f>(L21-K21)*-1</f>
-        <v>-7072.2922241162923</v>
+        <f t="shared" si="9"/>
+        <v>-4714.4660346962046</v>
       </c>
       <c r="M41" s="116">
-        <f>(M21-L21)*-1</f>
-        <v>-7166.4119555163998</v>
+        <f t="shared" si="9"/>
+        <v>-2909.5072879320505</v>
       </c>
       <c r="N41" s="116">
-        <f>(N21-M21)*-1</f>
-        <v>-6502.4605149525669</v>
+        <f t="shared" si="9"/>
+        <v>-1669.8033815271556</v>
       </c>
       <c r="O41" s="100"/>
       <c r="P41" s="100"/>
@@ -16400,48 +16426,48 @@
       </c>
       <c r="C42" s="96"/>
       <c r="D42" s="116">
-        <f>(D22-C22)*-1</f>
+        <f t="shared" ref="D42:N42" si="10">(D22-C22)*-1</f>
         <v>0</v>
       </c>
       <c r="E42" s="116">
-        <f>(E22-D22)*-1</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F42" s="116">
-        <f>(F22-E22)*-1</f>
+        <f t="shared" si="10"/>
         <v>-2947</v>
       </c>
       <c r="G42" s="116">
-        <f>(G22-F22)*-1</f>
+        <f t="shared" si="10"/>
         <v>-2593.8000000000002</v>
       </c>
       <c r="H42" s="116">
-        <f>(H22-G22)*-1</f>
+        <f t="shared" si="10"/>
         <v>-2800.2</v>
       </c>
       <c r="I42" s="116">
-        <f>(I22-H22)*-1</f>
+        <f t="shared" si="10"/>
         <v>-5974</v>
       </c>
       <c r="J42" s="116">
-        <f>(J22-I22)*-1</f>
-        <v>-4931.5714946263761</v>
+        <f t="shared" si="10"/>
+        <v>-5437.5607717763996</v>
       </c>
       <c r="K42" s="116">
-        <f>(K22-J22)*-1</f>
-        <v>-5810.7935061179232</v>
+        <f t="shared" si="10"/>
+        <v>-4892.5520324442514</v>
       </c>
       <c r="L42" s="116">
-        <f>(L22-K22)*-1</f>
-        <v>-6397.555314942696</v>
+        <f t="shared" si="10"/>
+        <v>-4264.6791565737694</v>
       </c>
       <c r="M42" s="116">
-        <f>(M22-L22)*-1</f>
-        <v>-6482.6954885636987</v>
+        <f t="shared" si="10"/>
+        <v>-2631.923741824743</v>
       </c>
       <c r="N42" s="116">
-        <f>(N22-M22)*-1</f>
-        <v>-5882.0887923416958</v>
+        <f t="shared" si="10"/>
+        <v>-1510.4946401918787</v>
       </c>
       <c r="O42" s="100"/>
       <c r="P42" s="100"/>
@@ -16453,48 +16479,48 @@
       </c>
       <c r="C43" s="96"/>
       <c r="D43" s="116">
-        <f>(D24-C24)</f>
+        <f t="shared" ref="D43:N43" si="11">(D24-C24)</f>
         <v>0</v>
       </c>
       <c r="E43" s="116">
-        <f>(E24-D24)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F43" s="116">
-        <f>(F24-E24)</f>
+        <f t="shared" si="11"/>
         <v>1930.6</v>
       </c>
       <c r="G43" s="116">
-        <f>(G24-F24)</f>
+        <f t="shared" si="11"/>
         <v>668.20000000000027</v>
       </c>
       <c r="H43" s="116">
-        <f>(H24-G24)</f>
+        <f t="shared" si="11"/>
         <v>630.19999999999982</v>
       </c>
       <c r="I43" s="116">
-        <f>(I24-H24)</f>
+        <f t="shared" si="11"/>
         <v>2150</v>
       </c>
       <c r="J43" s="116">
-        <f>(J24-I24)</f>
-        <v>2947.9876919119179</v>
+        <f t="shared" si="11"/>
+        <v>3166.9028625564151</v>
       </c>
       <c r="K43" s="116">
-        <f>(K24-J24)</f>
-        <v>2514.0272915202113</v>
+        <f t="shared" si="11"/>
+        <v>2116.7520962149829</v>
       </c>
       <c r="L43" s="116">
-        <f>(L24-K24)</f>
-        <v>2767.8885239756637</v>
+        <f t="shared" si="11"/>
+        <v>1845.1042491727931</v>
       </c>
       <c r="M43" s="116">
-        <f>(M24-L24)</f>
-        <v>2804.7242366649243</v>
+        <f t="shared" si="11"/>
+        <v>1138.6961366259093</v>
       </c>
       <c r="N43" s="116">
-        <f>(N24-M24)</f>
-        <v>2544.873043504791</v>
+        <f t="shared" si="11"/>
+        <v>653.5122518360422</v>
       </c>
       <c r="O43" s="100"/>
       <c r="P43" s="100"/>
@@ -16506,48 +16532,48 @@
       </c>
       <c r="C44" s="96"/>
       <c r="D44" s="116">
-        <f>(D25-C25)</f>
+        <f t="shared" ref="D44:N44" si="12">(D25-C25)</f>
         <v>0</v>
       </c>
       <c r="E44" s="116">
-        <f>(E25-D25)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F44" s="116">
-        <f>(F25-E25)</f>
+        <f t="shared" si="12"/>
         <v>1059.8</v>
       </c>
       <c r="G44" s="116">
-        <f>(G25-F25)</f>
+        <f t="shared" si="12"/>
         <v>590.60000000000014</v>
       </c>
       <c r="H44" s="116">
-        <f>(H25-G25)</f>
+        <f t="shared" si="12"/>
         <v>443.59999999999991</v>
       </c>
       <c r="I44" s="116">
-        <f>(I25-H25)</f>
+        <f t="shared" si="12"/>
         <v>281</v>
       </c>
       <c r="J44" s="116">
-        <f>(J25-I25)</f>
-        <v>818.1964582422379</v>
+        <f t="shared" si="12"/>
+        <v>902.14508089199762</v>
       </c>
       <c r="K44" s="116">
-        <f>(K25-J25)</f>
-        <v>964.06808082641055</v>
+        <f t="shared" si="12"/>
+        <v>811.72274376912947</v>
       </c>
       <c r="L44" s="116">
-        <f>(L25-K25)</f>
-        <v>1061.4176648961857</v>
+        <f t="shared" si="12"/>
+        <v>707.55242730441569</v>
       </c>
       <c r="M44" s="116">
-        <f>(M25-L25)</f>
-        <v>1075.543261288075</v>
+        <f t="shared" si="12"/>
+        <v>436.66216464084937</v>
       </c>
       <c r="N44" s="116">
-        <f>(N25-M25)</f>
-        <v>975.89667354603716</v>
+        <f t="shared" si="12"/>
+        <v>250.60599164901942</v>
       </c>
       <c r="O44" s="100"/>
       <c r="P44" s="100"/>
@@ -16559,48 +16585,48 @@
       </c>
       <c r="C45" s="117"/>
       <c r="D45" s="118">
-        <f>D29*-1</f>
+        <f t="shared" ref="D45:N45" si="13">D29*-1</f>
         <v>0</v>
       </c>
       <c r="E45" s="118">
-        <f>E29*-1</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F45" s="118">
-        <f>F29*-1</f>
+        <f t="shared" si="13"/>
         <v>1854.3</v>
       </c>
       <c r="G45" s="118">
-        <f>G29*-1</f>
+        <f t="shared" si="13"/>
         <v>3448</v>
       </c>
       <c r="H45" s="118">
-        <f>H29*-1</f>
+        <f t="shared" si="13"/>
         <v>5058</v>
       </c>
       <c r="I45" s="118">
-        <f>I29*-1</f>
+        <f t="shared" si="13"/>
         <v>7841</v>
       </c>
       <c r="J45" s="118">
-        <f>J29*-1</f>
-        <v>8732.818505021467</v>
+        <f t="shared" si="13"/>
+        <v>8962.4029026411608</v>
       </c>
       <c r="K45" s="118">
-        <f>K29*-1</f>
-        <v>11369.371465804794</v>
+        <f t="shared" si="13"/>
+        <v>11182.318742594189</v>
       </c>
       <c r="L45" s="118">
-        <f>L29*-1</f>
-        <v>14272.158045577118</v>
+        <f t="shared" si="13"/>
+        <v>13117.347486124167</v>
       </c>
       <c r="M45" s="118">
-        <f>M29*-1</f>
-        <v>17213.575593151985</v>
+        <f t="shared" si="13"/>
+        <v>14311.54003947475</v>
       </c>
       <c r="N45" s="118">
-        <f>N29*-1</f>
-        <v>19882.477629459212</v>
+        <f t="shared" si="13"/>
+        <v>14996.902393454848</v>
       </c>
       <c r="O45" s="100"/>
       <c r="P45" s="100"/>
@@ -16612,48 +16638,48 @@
       </c>
       <c r="C46" s="104"/>
       <c r="D46" s="119">
-        <f t="shared" ref="D46:N46" si="5">SUM(D38:D45)</f>
+        <f t="shared" ref="D46:N46" si="14">SUM(D38:D45)</f>
         <v>0</v>
       </c>
       <c r="E46" s="119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F46" s="119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>-1450.2602961918203</v>
       </c>
       <c r="G46" s="119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>5096.1504578145295</v>
       </c>
       <c r="H46" s="119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>12139.446398744511</v>
       </c>
       <c r="I46" s="119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>14484.521805703451</v>
       </c>
       <c r="J46" s="119">
-        <f t="shared" si="5"/>
-        <v>18687.875953746305</v>
+        <f t="shared" si="14"/>
+        <v>18457.850791405424</v>
       </c>
       <c r="K46" s="119">
-        <f t="shared" si="5"/>
-        <v>27720.031762282113</v>
+        <f t="shared" si="14"/>
+        <v>29856.554400473731</v>
       </c>
       <c r="L46" s="119">
-        <f t="shared" si="5"/>
-        <v>37276.98881237593</v>
+        <f t="shared" si="14"/>
+        <v>39059.566530415046</v>
       </c>
       <c r="M46" s="119">
-        <f t="shared" si="5"/>
-        <v>48500.994813716243</v>
+        <f t="shared" si="14"/>
+        <v>48271.32977744325</v>
       </c>
       <c r="N46" s="119">
-        <f t="shared" si="5"/>
-        <v>60493.285624579643</v>
+        <f t="shared" si="14"/>
+        <v>54030.380008669767</v>
       </c>
       <c r="O46" s="100"/>
       <c r="P46" s="120"/>
@@ -16672,23 +16698,23 @@
       <c r="I47" s="123"/>
       <c r="J47" s="124">
         <f>$H$74</f>
-        <v>6.7102096605434286E-2</v>
+        <v>6.7125681453908931E-2</v>
       </c>
       <c r="K47" s="124">
-        <f t="shared" ref="K47:N47" si="6">$H$74</f>
-        <v>6.7102096605434286E-2</v>
+        <f t="shared" ref="K47:N47" si="15">$H$74</f>
+        <v>6.7125681453908931E-2</v>
       </c>
       <c r="L47" s="124">
-        <f t="shared" si="6"/>
-        <v>6.7102096605434286E-2</v>
+        <f t="shared" si="15"/>
+        <v>6.7125681453908931E-2</v>
       </c>
       <c r="M47" s="124">
-        <f t="shared" si="6"/>
-        <v>6.7102096605434286E-2</v>
+        <f t="shared" si="15"/>
+        <v>6.7125681453908931E-2</v>
       </c>
       <c r="N47" s="124">
-        <f t="shared" si="6"/>
-        <v>6.7102096605434286E-2</v>
+        <f t="shared" si="15"/>
+        <v>6.7125681453908931E-2</v>
       </c>
       <c r="O47" s="100"/>
       <c r="P47" s="120"/>
@@ -16706,23 +16732,23 @@
       <c r="I48" s="110"/>
       <c r="J48" s="125">
         <f>J46/(1+J47)^J34</f>
-        <v>17512.734735686896</v>
+        <v>17296.791851412912</v>
       </c>
       <c r="K48" s="125">
-        <f t="shared" ref="K48:M48" si="7">K46/(1+K47)^K34</f>
-        <v>24343.4303749848</v>
+        <f t="shared" ref="K48:M48" si="16">K46/(1+K47)^K34</f>
+        <v>26218.542350923126</v>
       </c>
       <c r="L48" s="125">
-        <f t="shared" si="7"/>
-        <v>30677.707603406416</v>
+        <f t="shared" si="16"/>
+        <v>32142.577819296312</v>
       </c>
       <c r="M48" s="125">
-        <f t="shared" si="7"/>
-        <v>37404.749776359706</v>
+        <f t="shared" si="16"/>
+        <v>37224.337390134337</v>
       </c>
       <c r="N48" s="125">
         <f>N46/(1+N47)^N34</f>
-        <v>43719.713508953508</v>
+        <v>39044.526751031823</v>
       </c>
       <c r="O48" s="100"/>
       <c r="P48" s="100"/>
@@ -16736,30 +16762,30 @@
       <c r="D49" s="119"/>
       <c r="F49" s="113">
         <f>SUM(J48:N48)</f>
-        <v>153658.33599939133</v>
+        <v>151926.77616279852</v>
       </c>
       <c r="G49" s="119"/>
       <c r="H49" s="100"/>
       <c r="I49" s="100"/>
       <c r="J49" s="124">
-        <f t="shared" ref="J49:N49" si="8">J46/I46-1</f>
-        <v>0.29019626636122253</v>
+        <f t="shared" ref="J49:N49" si="17">J46/I46-1</f>
+        <v>0.27431550996301635</v>
       </c>
       <c r="K49" s="124">
-        <f t="shared" si="8"/>
-        <v>0.48331634001054891</v>
+        <f t="shared" si="17"/>
+        <v>0.61755313432135406</v>
       </c>
       <c r="L49" s="124">
-        <f t="shared" si="8"/>
-        <v>0.34476717530669299</v>
+        <f t="shared" si="17"/>
+        <v>0.3082409311703862</v>
       </c>
       <c r="M49" s="124">
-        <f t="shared" si="8"/>
-        <v>0.30109744265647209</v>
+        <f t="shared" si="17"/>
+        <v>0.23583884987190418</v>
       </c>
       <c r="N49" s="124">
-        <f t="shared" si="8"/>
-        <v>0.24725865638269218</v>
+        <f t="shared" si="17"/>
+        <v>0.11930581274182472</v>
       </c>
       <c r="O49" s="100"/>
       <c r="P49" s="100"/>
@@ -16829,17 +16855,17 @@
       </c>
       <c r="C53" s="100"/>
       <c r="D53" s="130"/>
-      <c r="F53" s="199">
+      <c r="F53" s="192">
         <v>0.01</v>
       </c>
       <c r="G53" s="131"/>
-      <c r="H53" s="132" t="s">
+      <c r="H53" s="203" t="s">
         <v>290</v>
       </c>
-      <c r="I53" s="133"/>
-      <c r="J53" s="133"/>
-      <c r="K53" s="133"/>
-      <c r="L53" s="133"/>
+      <c r="I53" s="204"/>
+      <c r="J53" s="204"/>
+      <c r="K53" s="204"/>
+      <c r="L53" s="204"/>
       <c r="M53" s="100"/>
       <c r="N53" s="100"/>
       <c r="O53" s="100"/>
@@ -16851,28 +16877,28 @@
         <v>291</v>
       </c>
       <c r="C54" s="100"/>
-      <c r="D54" s="134"/>
-      <c r="F54" s="134">
+      <c r="D54" s="132"/>
+      <c r="F54" s="132">
         <f>H74</f>
-        <v>6.7102096605434286E-2</v>
-      </c>
-      <c r="G54" s="135"/>
-      <c r="H54" s="136">
+        <v>6.7125681453908931E-2</v>
+      </c>
+      <c r="G54" s="133"/>
+      <c r="H54" s="134">
         <v>2021</v>
       </c>
-      <c r="I54" s="137" t="str">
+      <c r="I54" s="135" t="str">
         <f>J33</f>
         <v>FY'26</v>
       </c>
-      <c r="J54" s="137" t="str">
+      <c r="J54" s="135" t="str">
         <f>K33</f>
         <v>FY'27</v>
       </c>
-      <c r="K54" s="137" t="str">
+      <c r="K54" s="135" t="str">
         <f>L33</f>
         <v>FY'28</v>
       </c>
-      <c r="L54" s="137" t="str">
+      <c r="L54" s="135" t="str">
         <f>M33</f>
         <v>FY'29</v>
       </c>
@@ -16890,25 +16916,25 @@
       <c r="D55" s="115"/>
       <c r="F55" s="115">
         <f>N46*(1+F53)</f>
-        <v>61098.218480825439</v>
+        <v>54570.683808756461</v>
       </c>
       <c r="G55" s="128"/>
       <c r="H55" s="129"/>
-      <c r="I55" s="138">
-        <f t="shared" ref="I55:L55" si="9">K46/J46-1</f>
-        <v>0.48331634001054891</v>
-      </c>
-      <c r="J55" s="138">
-        <f t="shared" si="9"/>
-        <v>0.34476717530669299</v>
-      </c>
-      <c r="K55" s="139">
-        <f t="shared" si="9"/>
-        <v>0.30109744265647209</v>
-      </c>
-      <c r="L55" s="138">
-        <f t="shared" si="9"/>
-        <v>0.24725865638269218</v>
+      <c r="I55" s="136">
+        <f t="shared" ref="I55:L55" si="18">K46/J46-1</f>
+        <v>0.61755313432135406</v>
+      </c>
+      <c r="J55" s="136">
+        <f t="shared" si="18"/>
+        <v>0.3082409311703862</v>
+      </c>
+      <c r="K55" s="137">
+        <f t="shared" si="18"/>
+        <v>0.23583884987190418</v>
+      </c>
+      <c r="L55" s="136">
+        <f t="shared" si="18"/>
+        <v>0.11930581274182472</v>
       </c>
       <c r="M55" s="100"/>
       <c r="N55" s="100"/>
@@ -16924,7 +16950,7 @@
       <c r="D56" s="115"/>
       <c r="F56" s="115">
         <f>F55/(F54-F53)</f>
-        <v>1069982.0516749793</v>
+        <v>955274.09774159221</v>
       </c>
       <c r="G56" s="128"/>
       <c r="H56" s="129"/>
@@ -16943,16 +16969,16 @@
         <v>293</v>
       </c>
       <c r="C57" s="104"/>
-      <c r="D57" s="140"/>
-      <c r="F57" s="141">
+      <c r="D57" s="138"/>
+      <c r="F57" s="139">
         <f>F56/(1+F54)^N34</f>
-        <v>773297.53667645063</v>
-      </c>
-      <c r="G57" s="142"/>
+        <v>690319.50280295045</v>
+      </c>
+      <c r="G57" s="140"/>
       <c r="H57" s="129"/>
       <c r="I57" s="129"/>
       <c r="J57" s="129"/>
-      <c r="K57" s="142"/>
+      <c r="K57" s="140"/>
       <c r="L57" s="129"/>
       <c r="M57" s="100"/>
       <c r="N57" s="100"/>
@@ -16963,9 +16989,9 @@
     <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B58" s="100"/>
       <c r="C58" s="100"/>
-      <c r="D58" s="143"/>
-      <c r="E58" s="143"/>
-      <c r="F58" s="143"/>
+      <c r="D58" s="141"/>
+      <c r="E58" s="141"/>
+      <c r="F58" s="141"/>
       <c r="G58" s="129"/>
       <c r="H58" s="129"/>
       <c r="I58" s="129"/>
@@ -17007,7 +17033,7 @@
       <c r="E60" s="100"/>
       <c r="F60" s="100"/>
       <c r="G60" s="100"/>
-      <c r="H60" s="144">
+      <c r="H60" s="142">
         <f>H5</f>
         <v>1215.02</v>
       </c>
@@ -17030,7 +17056,7 @@
       <c r="E61" s="100"/>
       <c r="F61" s="100"/>
       <c r="G61" s="100"/>
-      <c r="H61" s="145">
+      <c r="H61" s="143">
         <f>H6</f>
         <v>893.7</v>
       </c>
@@ -17053,20 +17079,20 @@
       <c r="E62" s="100"/>
       <c r="F62" s="100"/>
       <c r="G62" s="100"/>
-      <c r="H62" s="199">
+      <c r="H62" s="192">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="I62" s="100"/>
       <c r="J62" s="100"/>
       <c r="K62" s="100"/>
       <c r="L62" s="100" t="s">
-        <v>323</v>
-      </c>
-      <c r="M62" s="202">
+        <v>322</v>
+      </c>
+      <c r="M62" s="195">
         <v>4.2299999999999997E-2</v>
       </c>
       <c r="N62" s="100" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O62" s="100"/>
       <c r="P62" s="100"/>
@@ -17081,9 +17107,9 @@
       <c r="E63" s="100"/>
       <c r="F63" s="100"/>
       <c r="G63" s="100"/>
-      <c r="H63" s="200">
+      <c r="H63" s="193">
         <f>J37</f>
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="I63" s="100"/>
       <c r="J63" s="100"/>
@@ -17091,11 +17117,11 @@
       <c r="L63" s="100" t="s">
         <v>297</v>
       </c>
-      <c r="M63" s="202">
+      <c r="M63" s="195">
         <v>4.6940000000000003E-2</v>
       </c>
       <c r="N63" s="100" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O63" s="100"/>
       <c r="P63" s="100"/>
@@ -17110,9 +17136,9 @@
       <c r="E64" s="100"/>
       <c r="F64" s="100"/>
       <c r="G64" s="100"/>
-      <c r="H64" s="146">
+      <c r="H64" s="144">
         <f>H62*(1-H63)</f>
-        <v>3.9200000000000006E-2</v>
+        <v>3.9690000000000003E-2</v>
       </c>
       <c r="I64" s="100"/>
       <c r="J64" s="100"/>
@@ -17120,7 +17146,7 @@
       <c r="L64" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="M64" s="203">
+      <c r="M64" s="196">
         <v>0.51</v>
       </c>
       <c r="N64" s="100" t="s">
@@ -17139,7 +17165,7 @@
       <c r="E65" s="100"/>
       <c r="F65" s="100"/>
       <c r="G65" s="100"/>
-      <c r="H65" s="199">
+      <c r="H65" s="192">
         <f>M66</f>
         <v>6.8513000000000004E-2</v>
       </c>
@@ -17156,10 +17182,10 @@
     <row r="66" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B66" s="100"/>
       <c r="C66" s="100"/>
-      <c r="D66" s="143"/>
-      <c r="E66" s="143"/>
+      <c r="D66" s="141"/>
+      <c r="E66" s="141"/>
       <c r="F66" s="100"/>
-      <c r="G66" s="143"/>
+      <c r="G66" s="141"/>
       <c r="H66" s="100"/>
       <c r="I66" s="100"/>
       <c r="J66" s="100"/>
@@ -17185,14 +17211,14 @@
       <c r="E67" s="100"/>
       <c r="F67" s="100"/>
       <c r="G67" s="100"/>
-      <c r="H67" s="201">
+      <c r="H67" s="194">
         <f>Main!C7</f>
         <v>54908</v>
       </c>
       <c r="I67" s="100"/>
       <c r="J67" s="100"/>
       <c r="K67" s="100"/>
-      <c r="L67" s="147" t="s">
+      <c r="L67" s="145" t="s">
         <v>304</v>
       </c>
       <c r="M67" s="100"/>
@@ -17210,7 +17236,7 @@
       <c r="E68" s="100"/>
       <c r="F68" s="100"/>
       <c r="G68" s="100"/>
-      <c r="H68" s="201">
+      <c r="H68" s="194">
         <f>Main!C5</f>
         <v>1085863.3740000001</v>
       </c>
@@ -17225,10 +17251,10 @@
       <c r="Q68" s="100"/>
     </row>
     <row r="69" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B69" s="148" t="s">
+      <c r="B69" s="146" t="s">
         <v>306</v>
       </c>
-      <c r="C69" s="148"/>
+      <c r="C69" s="146"/>
       <c r="D69" s="100"/>
       <c r="E69" s="100"/>
       <c r="F69" s="100"/>
@@ -17248,13 +17274,13 @@
       <c r="Q69" s="100"/>
     </row>
     <row r="70" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B70" s="148"/>
-      <c r="C70" s="148"/>
+      <c r="B70" s="146"/>
+      <c r="C70" s="146"/>
       <c r="D70" s="100"/>
       <c r="E70" s="100"/>
       <c r="F70" s="100"/>
       <c r="G70" s="100"/>
-      <c r="H70" s="149"/>
+      <c r="H70" s="147"/>
       <c r="I70" s="100"/>
       <c r="J70" s="100"/>
       <c r="K70" s="100"/>
@@ -17274,7 +17300,7 @@
       <c r="E71" s="100"/>
       <c r="F71" s="100"/>
       <c r="G71" s="100"/>
-      <c r="H71" s="150">
+      <c r="H71" s="148">
         <f>H67/H69</f>
         <v>4.8132343825801505E-2</v>
       </c>
@@ -17297,7 +17323,7 @@
       <c r="E72" s="100"/>
       <c r="F72" s="100"/>
       <c r="G72" s="100"/>
-      <c r="H72" s="150">
+      <c r="H72" s="148">
         <f>H68/H69</f>
         <v>0.95186765617419855</v>
       </c>
@@ -17312,13 +17338,13 @@
       <c r="Q72" s="100"/>
     </row>
     <row r="73" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B73" s="148"/>
-      <c r="C73" s="148"/>
+      <c r="B73" s="146"/>
+      <c r="C73" s="146"/>
       <c r="D73" s="100"/>
       <c r="E73" s="100"/>
       <c r="F73" s="100"/>
       <c r="G73" s="100"/>
-      <c r="H73" s="149"/>
+      <c r="H73" s="147"/>
       <c r="I73" s="100"/>
       <c r="J73" s="100"/>
       <c r="K73" s="100"/>
@@ -17338,9 +17364,9 @@
       <c r="E74" s="104"/>
       <c r="F74" s="104"/>
       <c r="G74" s="104"/>
-      <c r="H74" s="151">
+      <c r="H74" s="149">
         <f>H71*H64+H72*H65</f>
-        <v>6.7102096605434286E-2</v>
+        <v>6.7125681453908931E-2</v>
       </c>
       <c r="I74" s="100"/>
       <c r="J74" s="100"/>
@@ -17355,10 +17381,10 @@
     <row r="75" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B75" s="100"/>
       <c r="C75" s="100"/>
-      <c r="D75" s="143"/>
-      <c r="E75" s="143"/>
-      <c r="F75" s="143"/>
-      <c r="G75" s="143"/>
+      <c r="D75" s="141"/>
+      <c r="E75" s="141"/>
+      <c r="F75" s="141"/>
+      <c r="G75" s="141"/>
       <c r="H75" s="100"/>
       <c r="I75" s="100"/>
       <c r="J75" s="100"/>
@@ -17395,13 +17421,13 @@
         <v>311</v>
       </c>
       <c r="C77" s="100"/>
-      <c r="D77" s="152"/>
-      <c r="E77" s="152"/>
-      <c r="F77" s="152"/>
-      <c r="G77" s="152"/>
+      <c r="D77" s="150"/>
+      <c r="E77" s="150"/>
+      <c r="F77" s="150"/>
+      <c r="G77" s="150"/>
       <c r="H77" s="110">
         <f>F57+F49</f>
-        <v>926955.87267584191</v>
+        <v>842246.27896574896</v>
       </c>
       <c r="I77" s="100"/>
       <c r="J77" s="100"/>
@@ -17418,23 +17444,23 @@
         <v>312</v>
       </c>
       <c r="C78" s="100"/>
-      <c r="D78" s="153"/>
-      <c r="E78" s="153"/>
-      <c r="F78" s="153"/>
-      <c r="G78" s="153"/>
-      <c r="H78" s="154">
+      <c r="D78" s="151"/>
+      <c r="E78" s="151"/>
+      <c r="F78" s="151"/>
+      <c r="G78" s="151"/>
+      <c r="H78" s="152">
         <f>(M78+M79)-M80</f>
         <v>35235</v>
       </c>
       <c r="I78" s="96" t="s">
         <v>313</v>
       </c>
-      <c r="J78" s="152"/>
+      <c r="J78" s="150"/>
       <c r="K78" s="100"/>
       <c r="L78" s="100" t="s">
         <v>314</v>
       </c>
-      <c r="M78" s="204">
+      <c r="M78" s="197">
         <f>BS!F29</f>
         <v>1635</v>
       </c>
@@ -17454,15 +17480,15 @@
       <c r="G79" s="100"/>
       <c r="H79" s="113">
         <f>H77-H78</f>
-        <v>891720.87267584191</v>
+        <v>807011.27896574896</v>
       </c>
       <c r="I79" s="96"/>
-      <c r="J79" s="153"/>
+      <c r="J79" s="151"/>
       <c r="K79" s="100"/>
       <c r="L79" s="100" t="s">
         <v>316</v>
       </c>
-      <c r="M79" s="204">
+      <c r="M79" s="197">
         <f>BS!F35</f>
         <v>40868</v>
       </c>
@@ -17480,19 +17506,17 @@
       <c r="E80" s="100"/>
       <c r="F80" s="100"/>
       <c r="G80" s="100"/>
-      <c r="H80" s="155">
+      <c r="H80" s="153">
         <f>H6</f>
         <v>893.7</v>
       </c>
-      <c r="I80" s="148" t="s">
-        <v>317</v>
-      </c>
-      <c r="J80" s="140"/>
+      <c r="I80" s="146"/>
+      <c r="J80" s="138"/>
       <c r="K80" s="100"/>
       <c r="L80" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="M80" s="204">
+      <c r="M80" s="197">
         <f>BS!F14</f>
         <v>7268</v>
       </c>
@@ -17502,20 +17526,20 @@
       <c r="Q80" s="100"/>
     </row>
     <row r="81" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B81" s="156" t="s">
-        <v>318</v>
+      <c r="B81" s="154" t="s">
+        <v>317</v>
       </c>
       <c r="C81" s="107"/>
       <c r="D81" s="107"/>
       <c r="E81" s="107"/>
       <c r="F81" s="107"/>
       <c r="G81" s="107"/>
-      <c r="H81" s="157">
+      <c r="H81" s="155">
         <f>H79/H80</f>
-        <v>997.78546791523092</v>
-      </c>
-      <c r="I81" s="158"/>
-      <c r="J81" s="159"/>
+        <v>903.00020025260039</v>
+      </c>
+      <c r="I81" s="156"/>
+      <c r="J81" s="157"/>
       <c r="K81" s="100"/>
       <c r="L81" s="100"/>
       <c r="M81" s="100"/>
@@ -17531,63 +17555,63 @@
       <c r="E82" s="100"/>
       <c r="F82" s="100"/>
       <c r="G82" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="H82" s="158">
+        <f>H81/H5-1</f>
+        <v>-0.25680219234860302</v>
+      </c>
+      <c r="I82" s="146"/>
+      <c r="J82" s="159"/>
+      <c r="K82" s="205" t="s">
         <v>319</v>
       </c>
-      <c r="H82" s="160">
-        <f>H81/H5-1</f>
-        <v>-0.17879091050745588</v>
-      </c>
-      <c r="I82" s="148"/>
-      <c r="J82" s="161"/>
-      <c r="K82" s="162" t="s">
-        <v>320</v>
-      </c>
-      <c r="L82" s="133"/>
-      <c r="M82" s="133"/>
-      <c r="N82" s="133"/>
-      <c r="O82" s="133"/>
-      <c r="P82" s="133"/>
+      <c r="L82" s="204"/>
+      <c r="M82" s="204"/>
+      <c r="N82" s="204"/>
+      <c r="O82" s="204"/>
+      <c r="P82" s="204"/>
       <c r="Q82" s="100"/>
     </row>
     <row r="83" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B83" s="100"/>
       <c r="C83" s="100"/>
-      <c r="D83" s="143"/>
-      <c r="E83" s="143"/>
-      <c r="F83" s="143"/>
-      <c r="G83" s="143"/>
-      <c r="H83" s="143"/>
-      <c r="I83" s="143"/>
-      <c r="N83" s="163" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q83" s="143"/>
+      <c r="D83" s="141"/>
+      <c r="E83" s="141"/>
+      <c r="F83" s="141"/>
+      <c r="G83" s="141"/>
+      <c r="H83" s="141"/>
+      <c r="I83" s="141"/>
+      <c r="N83" s="160" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q83" s="141"/>
     </row>
     <row r="84" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B84" s="100"/>
       <c r="C84" s="100"/>
-      <c r="D84" s="164"/>
-      <c r="E84" s="164"/>
-      <c r="K84" s="165">
+      <c r="D84" s="161"/>
+      <c r="E84" s="161"/>
+      <c r="K84" s="162">
         <f>+H90</f>
         <v>0</v>
       </c>
-      <c r="L84" s="166">
+      <c r="L84" s="163">
         <f>M84-0.005</f>
         <v>2.9381787991493945E-2</v>
       </c>
-      <c r="M84" s="166">
+      <c r="M84" s="163">
         <f>+N84-0.005</f>
         <v>3.4381787991493946E-2</v>
       </c>
-      <c r="N84" s="167">
+      <c r="N84" s="164">
         <v>3.9381787991493944E-2</v>
       </c>
-      <c r="O84" s="166">
+      <c r="O84" s="163">
         <f>N84+0.005</f>
         <v>4.4381787991493941E-2</v>
       </c>
-      <c r="P84" s="166">
+      <c r="P84" s="163">
         <f>O84+0.005</f>
         <v>4.9381787991493939E-2</v>
       </c>
@@ -17595,220 +17619,220 @@
     <row r="85" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B85" s="100"/>
       <c r="C85" s="100"/>
-      <c r="D85" s="164"/>
-      <c r="E85" s="164"/>
-      <c r="G85" s="164"/>
-      <c r="J85" s="168" t="s">
+      <c r="D85" s="161"/>
+      <c r="E85" s="161"/>
+      <c r="G85" s="161"/>
+      <c r="J85" s="206" t="s">
         <v>291</v>
       </c>
-      <c r="K85" s="169">
+      <c r="K85" s="165">
         <f>K86-0.005</f>
         <v>6.9572637372920895E-2</v>
       </c>
-      <c r="L85" s="170">
+      <c r="L85" s="166">
         <v>56.643249001930386</v>
       </c>
-      <c r="M85" s="170">
+      <c r="M85" s="166">
         <v>54.949116865059182</v>
       </c>
-      <c r="N85" s="170">
+      <c r="N85" s="166">
         <v>53.176855024220643</v>
       </c>
-      <c r="O85" s="170">
+      <c r="O85" s="166">
         <v>51.324676923240347</v>
       </c>
-      <c r="P85" s="170">
+      <c r="P85" s="166">
         <v>49.390772518693161</v>
       </c>
     </row>
     <row r="86" spans="2:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="171"/>
-      <c r="C86" s="171"/>
-      <c r="D86" s="164"/>
-      <c r="E86" s="164"/>
-      <c r="J86" s="168"/>
-      <c r="K86" s="169">
+      <c r="B86" s="167"/>
+      <c r="C86" s="167"/>
+      <c r="D86" s="161"/>
+      <c r="E86" s="161"/>
+      <c r="J86" s="206"/>
+      <c r="K86" s="165">
         <f>K87-0.005</f>
         <v>7.45726373729209E-2</v>
       </c>
-      <c r="L86" s="170">
+      <c r="L86" s="166">
         <v>52.242182968071361</v>
       </c>
-      <c r="M86" s="170">
+      <c r="M86" s="166">
         <v>50.665433022385216</v>
       </c>
-      <c r="N86" s="170">
+      <c r="N86" s="166">
         <v>49.017222516967315</v>
       </c>
-      <c r="O86" s="170">
+      <c r="O86" s="166">
         <v>47.295925553029477</v>
       </c>
-      <c r="P86" s="170">
+      <c r="P86" s="166">
         <v>45.49989490840796</v>
       </c>
     </row>
     <row r="87" spans="2:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="171"/>
-      <c r="C87" s="171"/>
+      <c r="B87" s="167"/>
+      <c r="C87" s="167"/>
       <c r="D87" s="100"/>
       <c r="E87" s="100"/>
-      <c r="J87" s="168"/>
-      <c r="K87" s="172">
+      <c r="J87" s="206"/>
+      <c r="K87" s="168">
         <v>7.9572637372920904E-2</v>
       </c>
-      <c r="L87" s="170">
+      <c r="L87" s="166">
         <v>48.497933549323271</v>
       </c>
-      <c r="M87" s="170">
+      <c r="M87" s="166">
         <v>47.021047636063528</v>
       </c>
-      <c r="N87" s="173">
+      <c r="N87" s="169">
         <v>45.478375001918224</v>
       </c>
-      <c r="O87" s="170">
+      <c r="O87" s="166">
         <v>43.86842642892163</v>
       </c>
-      <c r="P87" s="170">
+      <c r="P87" s="166">
         <v>42.189693216670065</v>
       </c>
     </row>
     <row r="88" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B88" s="171"/>
-      <c r="C88" s="171"/>
-      <c r="J88" s="168"/>
-      <c r="K88" s="169">
+      <c r="B88" s="167"/>
+      <c r="C88" s="167"/>
+      <c r="J88" s="206"/>
+      <c r="K88" s="165">
         <f>K87+0.005</f>
         <v>8.4572637372920909E-2</v>
       </c>
-      <c r="L88" s="170">
+      <c r="L88" s="166">
         <v>45.27766178883676</v>
       </c>
-      <c r="M88" s="170">
+      <c r="M88" s="166">
         <v>43.886664738081947</v>
       </c>
-      <c r="N88" s="170">
+      <c r="N88" s="166">
         <v>42.434760797074262</v>
       </c>
-      <c r="O88" s="170">
+      <c r="O88" s="166">
         <v>40.92057830128617</v>
       </c>
-      <c r="P88" s="170">
+      <c r="P88" s="166">
         <v>39.342727687065377</v>
       </c>
     </row>
     <row r="89" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B89" s="171"/>
-      <c r="C89" s="174"/>
-      <c r="J89" s="168"/>
-      <c r="K89" s="169">
+      <c r="B89" s="167"/>
+      <c r="C89" s="170"/>
+      <c r="J89" s="206"/>
+      <c r="K89" s="165">
         <f>K88+0.005</f>
         <v>8.9572637372920913E-2</v>
       </c>
-      <c r="L89" s="170">
+      <c r="L89" s="166">
         <v>42.481941469872744</v>
       </c>
-      <c r="M89" s="170">
+      <c r="M89" s="166">
         <v>41.165509939029654</v>
       </c>
-      <c r="N89" s="170">
+      <c r="N89" s="166">
         <v>39.79240800561783</v>
       </c>
-      <c r="O89" s="170">
+      <c r="O89" s="166">
         <v>38.361366060638048</v>
       </c>
-      <c r="P89" s="170">
+      <c r="P89" s="166">
         <v>36.871097970539985</v>
       </c>
     </row>
     <row r="90" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B90" s="171"/>
-      <c r="C90" s="171"/>
+      <c r="B90" s="167"/>
+      <c r="C90" s="167"/>
       <c r="Q90" s="74" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="91" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B91" s="171"/>
-      <c r="C91" s="174"/>
+      <c r="B91" s="167"/>
+      <c r="C91" s="170"/>
     </row>
     <row r="92" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B92" s="171"/>
-      <c r="C92" s="175"/>
+      <c r="B92" s="167"/>
+      <c r="C92" s="171"/>
     </row>
     <row r="93" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B93" s="171"/>
-      <c r="C93" s="174"/>
+      <c r="B93" s="167"/>
+      <c r="C93" s="170"/>
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C102" s="171"/>
-      <c r="D102" s="171"/>
-      <c r="E102" s="171"/>
-      <c r="F102" s="171"/>
-      <c r="G102" s="171"/>
-      <c r="H102" s="171"/>
-      <c r="I102" s="171"/>
+      <c r="C102" s="167"/>
+      <c r="D102" s="167"/>
+      <c r="E102" s="167"/>
+      <c r="F102" s="167"/>
+      <c r="G102" s="167"/>
+      <c r="H102" s="167"/>
+      <c r="I102" s="167"/>
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B103" s="171"/>
-      <c r="C103" s="171"/>
-      <c r="D103" s="171"/>
-      <c r="E103" s="171"/>
-      <c r="F103" s="171"/>
-      <c r="G103" s="171"/>
-      <c r="H103" s="171"/>
-      <c r="I103" s="171"/>
+      <c r="B103" s="167"/>
+      <c r="C103" s="167"/>
+      <c r="D103" s="167"/>
+      <c r="E103" s="167"/>
+      <c r="F103" s="167"/>
+      <c r="G103" s="167"/>
+      <c r="H103" s="167"/>
+      <c r="I103" s="167"/>
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D104" s="176"/>
-      <c r="E104" s="176"/>
-      <c r="F104" s="176"/>
-      <c r="G104" s="176"/>
-      <c r="H104" s="176"/>
-      <c r="I104" s="176"/>
+      <c r="D104" s="172"/>
+      <c r="E104" s="172"/>
+      <c r="F104" s="172"/>
+      <c r="G104" s="172"/>
+      <c r="H104" s="172"/>
+      <c r="I104" s="172"/>
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D106" s="171"/>
+      <c r="D106" s="167"/>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D107" s="176"/>
+      <c r="D107" s="172"/>
     </row>
     <row r="115" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C115" s="171"/>
-      <c r="D115" s="171"/>
-      <c r="E115" s="171"/>
-      <c r="F115" s="171"/>
-      <c r="G115" s="171"/>
-      <c r="H115" s="171"/>
-      <c r="I115" s="171"/>
-      <c r="J115" s="171"/>
-      <c r="K115" s="171"/>
-      <c r="L115" s="171"/>
-      <c r="M115" s="171"/>
-      <c r="N115" s="171"/>
+      <c r="C115" s="167"/>
+      <c r="D115" s="167"/>
+      <c r="E115" s="167"/>
+      <c r="F115" s="167"/>
+      <c r="G115" s="167"/>
+      <c r="H115" s="167"/>
+      <c r="I115" s="167"/>
+      <c r="J115" s="167"/>
+      <c r="K115" s="167"/>
+      <c r="L115" s="167"/>
+      <c r="M115" s="167"/>
+      <c r="N115" s="167"/>
     </row>
     <row r="116" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B116" s="171"/>
-      <c r="C116" s="177"/>
-      <c r="D116" s="178"/>
-      <c r="E116" s="178"/>
-      <c r="F116" s="178"/>
-      <c r="G116" s="178"/>
-      <c r="H116" s="178"/>
-      <c r="I116" s="178"/>
-      <c r="J116" s="179"/>
-      <c r="K116" s="179"/>
-      <c r="L116" s="179"/>
-      <c r="M116" s="179"/>
-      <c r="N116" s="179"/>
+      <c r="B116" s="167"/>
+      <c r="C116" s="173"/>
+      <c r="D116" s="174"/>
+      <c r="E116" s="174"/>
+      <c r="F116" s="174"/>
+      <c r="G116" s="174"/>
+      <c r="H116" s="174"/>
+      <c r="I116" s="174"/>
+      <c r="J116" s="175"/>
+      <c r="K116" s="175"/>
+      <c r="L116" s="175"/>
+      <c r="M116" s="175"/>
+      <c r="N116" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="J85:J89"/>
     <mergeCell ref="J9:N9"/>
     <mergeCell ref="J18:N18"/>
     <mergeCell ref="J32:N32"/>
     <mergeCell ref="H53:L53"/>
     <mergeCell ref="K82:P82"/>
-    <mergeCell ref="J85:J89"/>
   </mergeCells>
   <conditionalFormatting sqref="L85:P89">
     <cfRule type="colorScale" priority="1">

--- a/LLY Financial Model.xlsx
+++ b/LLY Financial Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF9A9CC-9371-40AD-B7D9-A511CAE0ADA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DDCDADC-A077-4B7F-8BC8-F1E1AE6EB352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="344">
   <si>
     <t>LLY</t>
   </si>
@@ -878,21 +878,18 @@
     <t>ST and LT debt minus cash</t>
   </si>
   <si>
-    <t>ST Debt</t>
-  </si>
-  <si>
     <t>Equity Value</t>
   </si>
   <si>
-    <t>LT Debt</t>
-  </si>
-  <si>
     <t>Equity Value Per Share</t>
   </si>
   <si>
     <t>Upside</t>
   </si>
   <si>
+    <t>WACC \ g</t>
+  </si>
+  <si>
     <t>.</t>
   </si>
   <si>
@@ -1089,13 +1086,22 @@
   </si>
   <si>
     <t>amyloid beta-directed antibody</t>
+  </si>
+  <si>
+    <t>FY26 remaining</t>
+  </si>
+  <si>
+    <t>Sensitivity Analysis</t>
+  </si>
+  <si>
+    <t>Current Price</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="21">
+  <numFmts count="22">
     <numFmt numFmtId="164" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-??_);_(@_)"/>
@@ -1116,9 +1122,10 @@
     <numFmt numFmtId="181" formatCode="0.0%_);\(0.0%\);@_)"/>
     <numFmt numFmtId="182" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* \-?_);_(@_)"/>
     <numFmt numFmtId="183" formatCode="\$#,##0.00_);[Red]&quot;($&quot;#,##0.00\)"/>
-    <numFmt numFmtId="184" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="184" formatCode="\$#,##0"/>
+    <numFmt numFmtId="185" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1311,11 +1318,22 @@
       <charset val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1324,15 +1342,8 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1348,13 +1359,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor rgb="FFC0C0C0"/>
+        <bgColor rgb="FF999999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79979857783745845"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1369,8 +1380,20 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFC1E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1543,14 +1566,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1558,8 +1593,8 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1572,21 +1607,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1599,87 +1634,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
@@ -1692,7 +1727,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" readingOrder="1"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1701,7 +1736,7 @@
     <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1711,19 +1746,19 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
     <xf numFmtId="171" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="172" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="173" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="1"/>
     </xf>
@@ -1736,21 +1771,21 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="1"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="174" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="174" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="174" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1781,10 +1816,10 @@
     <xf numFmtId="10" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="1"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1799,102 +1834,102 @@
     <xf numFmtId="10" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="174" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="174" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="174" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="174" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="174" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="167" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="174" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="183" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1904,22 +1939,31 @@
     <xf numFmtId="175" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="184" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="28" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="26" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="175" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="185" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="171" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="174" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="173" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1939,16 +1983,16 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFA6A6A6"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFC1E5F5"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFC1E5F5"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1972,7 +2016,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FFA6A6A6"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -2720,15 +2764,15 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>14</v>
@@ -2739,15 +2783,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -2767,7 +2811,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>17</v>
@@ -2775,10 +2819,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2786,15 +2830,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -2814,7 +2858,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>19</v>
@@ -2822,10 +2866,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2833,15 +2877,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -2861,7 +2905,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>20</v>
@@ -2869,10 +2913,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2880,15 +2924,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -2908,7 +2952,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>23</v>
@@ -2916,10 +2960,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2927,15 +2971,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -2955,7 +2999,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
@@ -2963,10 +3007,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2974,15 +3018,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3005,7 +3049,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>27</v>
@@ -3013,10 +3057,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3024,15 +3068,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3055,7 +3099,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>28</v>
@@ -3063,10 +3107,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3074,15 +3118,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3102,7 +3146,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>29</v>
@@ -3110,10 +3154,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3121,15 +3165,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3149,7 +3193,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>31</v>
@@ -3157,10 +3201,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3168,15 +3212,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -6965,7 +7009,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>32</v>
@@ -6973,10 +7017,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6984,15 +7028,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -7012,7 +7056,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>34</v>
@@ -7020,10 +7064,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7031,15 +7075,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -7059,7 +7103,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>35</v>
@@ -7067,10 +7111,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7078,15 +7122,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -7105,7 +7149,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>36</v>
@@ -7113,10 +7157,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7124,15 +7168,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -7151,7 +7195,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>37</v>
@@ -7159,10 +7203,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7170,15 +7214,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -7197,7 +7241,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>38</v>
@@ -7205,10 +7249,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7216,15 +7260,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -7243,7 +7287,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>39</v>
@@ -7251,10 +7295,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7262,15 +7306,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -7289,7 +7333,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>40</v>
@@ -7297,10 +7341,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7308,15 +7352,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -7335,7 +7379,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>41</v>
@@ -7343,10 +7387,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7354,15 +7398,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -7423,7 +7467,7 @@
         <v>FY'30</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="40" t="s">
         <v>92</v>
       </c>
@@ -7456,7 +7500,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="40" t="s">
         <v>93</v>
       </c>
@@ -7489,7 +7533,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="40" t="s">
         <v>94</v>
       </c>
@@ -7522,7 +7566,7 @@
         <v>8.3299999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="40" t="s">
         <v>95</v>
       </c>
@@ -7555,7 +7599,7 @@
         <v>0.15329999999999999</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="40" t="s">
         <v>96</v>
       </c>
@@ -7588,7 +7632,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="40" t="s">
         <v>97</v>
       </c>
@@ -7624,7 +7668,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="40" t="s">
         <v>98</v>
       </c>
@@ -7665,7 +7709,7 @@
         <v>0.2370471541542023</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="40" t="s">
         <v>99</v>
       </c>
@@ -7706,7 +7750,7 @@
         <v>0.19695710863991797</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="40" t="s">
         <v>100</v>
       </c>
@@ -7746,7 +7790,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="40" t="s">
         <v>101</v>
       </c>
@@ -7786,7 +7830,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" s="51"/>
     </row>
     <row r="14" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7821,7 +7865,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="53" t="s">
         <v>62</v>
       </c>
@@ -7862,7 +7906,7 @@
         <v>129488.78943000002</v>
       </c>
     </row>
-    <row r="16" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
@@ -7888,7 +7932,7 @@
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
     </row>
-    <row r="17" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
@@ -7914,7 +7958,7 @@
       <c r="J17" s="30"/>
       <c r="K17" s="30"/>
     </row>
-    <row r="18" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
@@ -7940,7 +7984,7 @@
       <c r="J18" s="30"/>
       <c r="K18" s="30"/>
     </row>
-    <row r="19" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
         <v>14</v>
       </c>
@@ -7966,7 +8010,7 @@
       <c r="J19" s="30"/>
       <c r="K19" s="30"/>
     </row>
-    <row r="20" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
         <v>17</v>
       </c>
@@ -7992,7 +8036,7 @@
       <c r="J20" s="30"/>
       <c r="K20" s="30"/>
     </row>
-    <row r="21" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
@@ -8018,7 +8062,7 @@
       <c r="J21" s="30"/>
       <c r="K21" s="30"/>
     </row>
-    <row r="22" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
@@ -8044,7 +8088,7 @@
       <c r="J22" s="30"/>
       <c r="K22" s="30"/>
     </row>
-    <row r="23" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>63</v>
       </c>
@@ -8070,7 +8114,7 @@
       <c r="J23" s="30"/>
       <c r="K23" s="30"/>
     </row>
-    <row r="24" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>25</v>
       </c>
@@ -8096,7 +8140,7 @@
       <c r="J24" s="30"/>
       <c r="K24" s="30"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="57" t="s">
         <v>64</v>
       </c>
@@ -8137,7 +8181,7 @@
         <v>6937.2556170624994</v>
       </c>
     </row>
-    <row r="26" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>27</v>
       </c>
@@ -8163,7 +8207,7 @@
       <c r="J26" s="30"/>
       <c r="K26" s="30"/>
     </row>
-    <row r="27" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>28</v>
       </c>
@@ -8189,7 +8233,7 @@
       <c r="J27" s="30"/>
       <c r="K27" s="30"/>
     </row>
-    <row r="28" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
@@ -8215,7 +8259,7 @@
       <c r="J28" s="30"/>
       <c r="K28" s="30"/>
     </row>
-    <row r="29" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
@@ -8241,7 +8285,7 @@
       <c r="J29" s="30"/>
       <c r="K29" s="30"/>
     </row>
-    <row r="30" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>32</v>
       </c>
@@ -8267,7 +8311,7 @@
       <c r="J30" s="30"/>
       <c r="K30" s="30"/>
     </row>
-    <row r="31" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>34</v>
       </c>
@@ -8293,7 +8337,7 @@
       <c r="J31" s="30"/>
       <c r="K31" s="30"/>
     </row>
-    <row r="32" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>35</v>
       </c>
@@ -8319,7 +8363,7 @@
       <c r="J32" s="30"/>
       <c r="K32" s="30"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="57" t="s">
         <v>65</v>
       </c>
@@ -8360,7 +8404,7 @@
         <v>9090.4325617814829</v>
       </c>
     </row>
-    <row r="34" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
         <v>36</v>
       </c>
@@ -8386,7 +8430,7 @@
       <c r="J34" s="30"/>
       <c r="K34" s="30"/>
     </row>
-    <row r="35" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>37</v>
       </c>
@@ -8412,7 +8456,7 @@
       <c r="J35" s="30"/>
       <c r="K35" s="30"/>
     </row>
-    <row r="36" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
         <v>38</v>
       </c>
@@ -8438,7 +8482,7 @@
       <c r="J36" s="30"/>
       <c r="K36" s="30"/>
     </row>
-    <row r="37" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>39</v>
       </c>
@@ -8464,7 +8508,7 @@
       <c r="J37" s="30"/>
       <c r="K37" s="30"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="57" t="s">
         <v>66</v>
       </c>
@@ -8505,7 +8549,7 @@
         <v>3125.2633158599992</v>
       </c>
     </row>
-    <row r="39" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
         <v>40</v>
       </c>
@@ -8531,7 +8575,7 @@
       <c r="J39" s="30"/>
       <c r="K39" s="30"/>
     </row>
-    <row r="40" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
         <v>41</v>
       </c>
@@ -8557,7 +8601,7 @@
       <c r="J40" s="30"/>
       <c r="K40" s="30"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
         <v>112</v>
       </c>
@@ -8598,7 +8642,7 @@
         <v>1852.6037514575346</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="34" t="s">
         <v>68</v>
       </c>
@@ -8639,7 +8683,7 @@
         <v>150494.34467616153</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
         <v>69</v>
       </c>
@@ -8680,7 +8724,7 @@
         <v>22574.151701424234</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="34" t="s">
         <v>70</v>
       </c>
@@ -8721,7 +8765,7 @@
         <v>127920.19297473731</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
         <v>71</v>
       </c>
@@ -8762,7 +8806,7 @@
         <v>35674.256121785715</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
         <v>72</v>
       </c>
@@ -8803,7 +8847,7 @@
         <v>29640.930994076007</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
         <v>73</v>
       </c>
@@ -8844,7 +8888,7 @@
         <v>6019.7737870464616</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
         <v>74</v>
       </c>
@@ -8885,7 +8929,7 @@
         <v>475.47509765625</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
         <v>75</v>
       </c>
@@ -8926,7 +8970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
         <v>76</v>
       </c>
@@ -8967,7 +9011,7 @@
         <v>56109.75697417288</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
         <v>77</v>
       </c>
@@ -9008,7 +9052,7 @@
         <v>10660.853825092847</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="34" t="s">
         <v>78</v>
       </c>
@@ -9049,7 +9093,7 @@
         <v>45448.903149080033</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
         <v>79</v>
       </c>
@@ -9090,7 +9134,7 @@
         <v>50.614068878089014</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
         <v>9</v>
       </c>
@@ -9408,7 +9452,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="70" t="s">
         <v>124</v>
       </c>
@@ -9429,7 +9473,7 @@
         <v>15589.807793445721</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="70" t="s">
         <v>125</v>
       </c>
@@ -9450,7 +9494,7 @@
         <v>24283.251791999999</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="70" t="s">
         <v>126</v>
       </c>
@@ -9471,7 +9515,7 @@
         <v>3304.7420920995091</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="70" t="s">
         <v>127</v>
       </c>
@@ -9492,7 +9536,7 @@
         <v>18886.973615999999</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="70" t="s">
         <v>128</v>
       </c>
@@ -9513,7 +9557,7 @@
         <v>22484.492399999999</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="70" t="s">
         <v>129</v>
       </c>
@@ -9534,7 +9578,7 @@
         <v>202.83803237520996</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="73" t="s">
         <v>130</v>
       </c>
@@ -9555,7 +9599,7 @@
         <v>84752.105725920439</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="70" t="s">
         <v>131</v>
       </c>
@@ -9576,7 +9620,7 @@
         <v>2918.25</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="70" t="s">
         <v>132</v>
       </c>
@@ -9597,7 +9641,7 @@
         <v>6643.05</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="70" t="s">
         <v>133</v>
       </c>
@@ -9618,7 +9662,7 @@
         <v>6521</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="70" t="s">
         <v>134</v>
       </c>
@@ -9639,7 +9683,7 @@
         <v>12202.666666666666</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="70" t="s">
         <v>135</v>
       </c>
@@ -9660,7 +9704,7 @@
         <v>31388.953662641157</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="70" t="s">
         <v>136</v>
       </c>
@@ -9681,7 +9725,7 @@
         <v>7522.0250000000005</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="73" t="s">
         <v>137</v>
       </c>
@@ -9702,10 +9746,10 @@
         <v>151948.05105522828</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="51"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="70" t="s">
         <v>138</v>
       </c>
@@ -9726,7 +9770,7 @@
         <v>1718.82</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="70" t="s">
         <v>139</v>
       </c>
@@ -9747,7 +9791,7 @@
         <v>8499.1381272000017</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="70" t="s">
         <v>140</v>
       </c>
@@ -9768,7 +9812,7 @@
         <v>3277.1450808919976</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="70" t="s">
         <v>141</v>
       </c>
@@ -9789,7 +9833,7 @@
         <v>23984.562440448299</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="70" t="s">
         <v>142</v>
       </c>
@@ -9810,7 +9854,7 @@
         <v>11669.396189096264</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="73" t="s">
         <v>143</v>
       </c>
@@ -9831,7 +9875,7 @@
         <v>49149.06183763656</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="70" t="s">
         <v>144</v>
       </c>
@@ -9852,7 +9896,7 @@
         <v>52610.561686641158</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="70" t="s">
         <v>145</v>
       </c>
@@ -9873,7 +9917,7 @@
         <v>5875</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="70" t="s">
         <v>146</v>
       </c>
@@ -9894,7 +9938,7 @@
         <v>3970</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="73" t="s">
         <v>147</v>
       </c>
@@ -9915,7 +9959,7 @@
         <v>62455.561686641158</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="73" t="s">
         <v>148</v>
       </c>
@@ -9936,7 +9980,7 @@
         <v>40343.427530950532</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="73" t="s">
         <v>149</v>
       </c>
@@ -9957,7 +10001,7 @@
         <v>151948.05105522825</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="46" t="s">
         <v>150</v>
       </c>
@@ -10225,7 +10269,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="70" t="s">
         <v>162</v>
       </c>
@@ -10246,7 +10290,7 @@
         <v>26593.165227867124</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="70" t="s">
         <v>163</v>
       </c>
@@ -10267,7 +10311,7 @@
         <v>2248.4492399999999</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="70" t="s">
         <v>164</v>
       </c>
@@ -10288,7 +10332,7 @@
         <v>-2243.6666666666665</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="70" t="s">
         <v>165</v>
       </c>
@@ -10315,7 +10359,7 @@
       <c r="P17" s="71"/>
       <c r="Q17" s="71"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="70" t="s">
         <v>166</v>
       </c>
@@ -10342,7 +10386,7 @@
       <c r="P18" s="71"/>
       <c r="Q18" s="71"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="70" t="s">
         <v>167</v>
       </c>
@@ -10369,7 +10413,7 @@
       <c r="P19" s="71"/>
       <c r="Q19" s="71"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="70" t="s">
         <v>168</v>
       </c>
@@ -10396,7 +10440,7 @@
       <c r="P20" s="71"/>
       <c r="Q20" s="71"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="70" t="s">
         <v>169</v>
       </c>
@@ -10423,7 +10467,7 @@
       <c r="P21" s="71"/>
       <c r="Q21" s="71"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="70" t="s">
         <v>170</v>
       </c>
@@ -10450,7 +10494,7 @@
       <c r="P22" s="71"/>
       <c r="Q22" s="71"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="70" t="s">
         <v>171</v>
       </c>
@@ -10477,7 +10521,7 @@
       <c r="P23" s="71"/>
       <c r="Q23" s="71"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="70" t="s">
         <v>172</v>
       </c>
@@ -10504,7 +10548,7 @@
       <c r="P24" s="71"/>
       <c r="Q24" s="71"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="73" t="s">
         <v>173</v>
       </c>
@@ -10531,10 +10575,10 @@
       <c r="P25" s="74"/>
       <c r="Q25" s="74"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F26" s="51"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="70" t="s">
         <v>174</v>
       </c>
@@ -10561,7 +10605,7 @@
       <c r="P27" s="71"/>
       <c r="Q27" s="71"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="70" t="s">
         <v>175</v>
       </c>
@@ -10588,7 +10632,7 @@
       <c r="P28" s="71"/>
       <c r="Q28" s="71"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="70" t="s">
         <v>176</v>
       </c>
@@ -10615,7 +10659,7 @@
       <c r="P29" s="71"/>
       <c r="Q29" s="71"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="70" t="s">
         <v>177</v>
       </c>
@@ -10641,7 +10685,7 @@
       <c r="P30" s="71"/>
       <c r="Q30" s="71"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="70" t="s">
         <v>178</v>
       </c>
@@ -10668,7 +10712,7 @@
       <c r="P31" s="71"/>
       <c r="Q31" s="71"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="70" t="s">
         <v>179</v>
       </c>
@@ -10695,7 +10739,7 @@
       <c r="P32" s="71"/>
       <c r="Q32" s="71"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="70" t="s">
         <v>180</v>
       </c>
@@ -10721,7 +10765,7 @@
       <c r="P33" s="71"/>
       <c r="Q33" s="71"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="73" t="s">
         <v>181</v>
       </c>
@@ -10748,10 +10792,10 @@
       <c r="P34" s="74"/>
       <c r="Q34" s="74"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F35" s="51"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="70" t="s">
         <v>182</v>
       </c>
@@ -10778,7 +10822,7 @@
       <c r="P36" s="71"/>
       <c r="Q36" s="71"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="70" t="s">
         <v>183</v>
       </c>
@@ -10805,7 +10849,7 @@
       <c r="P37" s="71"/>
       <c r="Q37" s="71"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="70" t="s">
         <v>184</v>
       </c>
@@ -10832,7 +10876,7 @@
       <c r="P38" s="71"/>
       <c r="Q38" s="71"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="70" t="s">
         <v>185</v>
       </c>
@@ -10859,7 +10903,7 @@
       <c r="P39" s="71"/>
       <c r="Q39" s="71"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="70" t="s">
         <v>186</v>
       </c>
@@ -10886,7 +10930,7 @@
       <c r="P40" s="71"/>
       <c r="Q40" s="71"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="70" t="s">
         <v>187</v>
       </c>
@@ -10913,7 +10957,7 @@
       <c r="P41" s="71"/>
       <c r="Q41" s="71"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="73" t="s">
         <v>188</v>
       </c>
@@ -10940,10 +10984,10 @@
       <c r="P42" s="74"/>
       <c r="Q42" s="74"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F43" s="51"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="70" t="s">
         <v>189</v>
       </c>
@@ -10969,7 +11013,7 @@
       <c r="P44" s="71"/>
       <c r="Q44" s="71"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="73" t="s">
         <v>190</v>
       </c>
@@ -10996,7 +11040,7 @@
       <c r="P45" s="74"/>
       <c r="Q45" s="74"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="70" t="s">
         <v>191</v>
       </c>
@@ -11023,7 +11067,7 @@
       <c r="P46" s="71"/>
       <c r="Q46" s="71"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="73" t="s">
         <v>192</v>
       </c>
@@ -11091,7 +11135,7 @@
       <c r="P2" s="82"/>
       <c r="Q2" s="82"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>193</v>
       </c>
@@ -11113,7 +11157,7 @@
       <c r="P4" s="86"/>
       <c r="Q4" s="86"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>194</v>
       </c>
@@ -11136,7 +11180,7 @@
       <c r="P5" s="86"/>
       <c r="Q5" s="86"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>195</v>
       </c>
@@ -11159,7 +11203,7 @@
       <c r="P6" s="86"/>
       <c r="Q6" s="86"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="83"/>
       <c r="C7" s="83"/>
       <c r="D7" s="84"/>
@@ -11197,7 +11241,7 @@
       <c r="P8" s="86"/>
       <c r="Q8" s="86"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="83"/>
       <c r="C9" s="83"/>
       <c r="D9" s="91"/>
@@ -11217,7 +11261,7 @@
       <c r="P9" s="86"/>
       <c r="Q9" s="86"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="83"/>
       <c r="C10" s="94">
         <f>D10-365</f>
@@ -11259,7 +11303,7 @@
       <c r="P10" s="99"/>
       <c r="Q10" s="99"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="83" t="s">
         <v>198</v>
       </c>
@@ -11306,7 +11350,7 @@
       <c r="P11" s="86"/>
       <c r="Q11" s="86"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="83"/>
       <c r="C12" s="105"/>
       <c r="D12" s="84"/>
@@ -11324,7 +11368,7 @@
       <c r="P12" s="86"/>
       <c r="Q12" s="86"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="83" t="s">
         <v>199</v>
       </c>
@@ -11371,7 +11415,7 @@
       <c r="P13" s="86"/>
       <c r="Q13" s="86"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="83"/>
       <c r="C14" s="105"/>
       <c r="D14" s="84"/>
@@ -11389,7 +11433,7 @@
       <c r="P14" s="86"/>
       <c r="Q14" s="86"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="83" t="s">
         <v>200</v>
       </c>
@@ -11442,7 +11486,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="83"/>
       <c r="C16" s="100"/>
       <c r="D16" s="107"/>
@@ -11491,7 +11535,7 @@
         <v>4.1156151630137194E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="83"/>
       <c r="C17" s="83"/>
       <c r="D17" s="84"/>
@@ -11529,7 +11573,7 @@
       <c r="P18" s="86"/>
       <c r="Q18" s="86"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="83"/>
       <c r="C19" s="83"/>
       <c r="D19" s="91"/>
@@ -11549,7 +11593,7 @@
       <c r="P19" s="86"/>
       <c r="Q19" s="86"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="83"/>
       <c r="C20" s="94">
         <f>D20-365</f>
@@ -11591,7 +11635,7 @@
       <c r="P20" s="86"/>
       <c r="Q20" s="86"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="116" t="s">
         <v>205</v>
       </c>
@@ -11638,7 +11682,7 @@
       <c r="P21" s="86"/>
       <c r="Q21" s="86"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="116" t="s">
         <v>127</v>
       </c>
@@ -11685,7 +11729,7 @@
       <c r="P22" s="86"/>
       <c r="Q22" s="86"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="116" t="s">
         <v>206</v>
       </c>
@@ -11732,7 +11776,7 @@
       <c r="P23" s="86"/>
       <c r="Q23" s="86"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="83"/>
       <c r="C24" s="119"/>
       <c r="D24" s="119"/>
@@ -11750,7 +11794,7 @@
       <c r="P24" s="86"/>
       <c r="Q24" s="86"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="116" t="s">
         <v>207</v>
       </c>
@@ -11797,7 +11841,7 @@
       <c r="P25" s="86"/>
       <c r="Q25" s="86"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="116" t="s">
         <v>208</v>
       </c>
@@ -11844,7 +11888,7 @@
       <c r="P26" s="86"/>
       <c r="Q26" s="86"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="83"/>
       <c r="C27" s="119"/>
       <c r="D27" s="119"/>
@@ -11862,7 +11906,7 @@
       <c r="P27" s="86"/>
       <c r="Q27" s="86"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="83" t="s">
         <v>16</v>
       </c>
@@ -11894,7 +11938,7 @@
       <c r="P28" s="86"/>
       <c r="Q28" s="86"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="83"/>
       <c r="C29" s="119"/>
       <c r="D29" s="119"/>
@@ -11912,7 +11956,7 @@
       <c r="P29" s="86"/>
       <c r="Q29" s="86"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="83" t="s">
         <v>209</v>
       </c>
@@ -11959,7 +12003,7 @@
       <c r="P30" s="86"/>
       <c r="Q30" s="86"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="83"/>
       <c r="C31" s="117"/>
       <c r="D31" s="117"/>
@@ -11983,7 +12027,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="124" t="s">
         <v>212</v>
       </c>
@@ -12045,7 +12089,7 @@
         <v>0.25585646421278629</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="124" t="s">
         <v>213</v>
       </c>
@@ -12109,7 +12153,7 @@
         <v>0.17356909165949161</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="124" t="s">
         <v>214</v>
       </c>
@@ -12173,7 +12217,7 @@
         <v>0.16159299909069005</v>
       </c>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="124" t="s">
         <v>215</v>
       </c>
@@ -12237,7 +12281,7 @@
         <v>7.4300324025935297E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="124" t="s">
         <v>216</v>
       </c>
@@ -12299,7 +12343,7 @@
         <v>4.1763354611314793E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="128" t="s">
         <v>217</v>
       </c>
@@ -12361,7 +12405,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="130" t="s">
         <v>218</v>
       </c>
@@ -12396,7 +12440,7 @@
       <c r="P38" s="99"/>
       <c r="Q38" s="99"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="130" t="s">
         <v>219</v>
       </c>
@@ -12431,7 +12475,7 @@
       <c r="P39" s="86"/>
       <c r="Q39" s="86"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="130" t="s">
         <v>220</v>
       </c>
@@ -12466,7 +12510,7 @@
       <c r="P40" s="86"/>
       <c r="Q40" s="86"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="130" t="s">
         <v>221</v>
       </c>
@@ -12501,7 +12545,7 @@
       <c r="P41" s="86"/>
       <c r="Q41" s="86"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="130" t="s">
         <v>222</v>
       </c>
@@ -12536,7 +12580,7 @@
       <c r="P42" s="86"/>
       <c r="Q42" s="86"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="130" t="s">
         <v>223</v>
       </c>
@@ -12571,7 +12615,7 @@
       <c r="P43" s="86"/>
       <c r="Q43" s="86"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="83"/>
       <c r="C44" s="83"/>
       <c r="D44" s="84"/>
@@ -12609,7 +12653,7 @@
       <c r="P45" s="132"/>
       <c r="Q45" s="132"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="133" t="s">
         <v>225</v>
       </c>
@@ -12631,7 +12675,7 @@
       <c r="P46" s="132"/>
       <c r="Q46" s="132"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="136"/>
       <c r="C47" s="94">
         <f>D47-365</f>
@@ -12670,10 +12714,12 @@
         <v>111</v>
       </c>
       <c r="O47" s="132"/>
-      <c r="P47" s="132"/>
+      <c r="P47" s="132" t="s">
+        <v>341</v>
+      </c>
       <c r="Q47" s="132"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="137" t="s">
         <v>226</v>
       </c>
@@ -12685,29 +12731,33 @@
       <c r="H48" s="139"/>
       <c r="I48" s="139"/>
       <c r="J48" s="138">
-        <v>1</v>
+        <f ca="1">$P$48</f>
+        <v>0.38082191780821917</v>
       </c>
       <c r="K48" s="138">
-        <f>J48+1</f>
-        <v>2</v>
+        <f ca="1">J48+1</f>
+        <v>1.3808219178082193</v>
       </c>
       <c r="L48" s="138">
-        <f>K48+1</f>
-        <v>3</v>
+        <f ca="1">K48+1</f>
+        <v>2.3808219178082193</v>
       </c>
       <c r="M48" s="138">
-        <f>L48+1</f>
-        <v>4</v>
+        <f ca="1">L48+1</f>
+        <v>3.3808219178082193</v>
       </c>
       <c r="N48" s="138">
-        <f>M48+1</f>
-        <v>5</v>
+        <f ca="1">M48+1</f>
+        <v>4.3808219178082197</v>
       </c>
       <c r="O48" s="132"/>
-      <c r="P48" s="132"/>
+      <c r="P48" s="132">
+        <f ca="1">(DATE(YEAR($H$4),12,31)-$H$4)/365</f>
+        <v>0.38082191780821917</v>
+      </c>
       <c r="Q48" s="132"/>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="132" t="s">
         <v>227</v>
       </c>
@@ -12763,7 +12813,7 @@
       <c r="P49" s="132"/>
       <c r="Q49" s="132"/>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="132" t="s">
         <v>199</v>
       </c>
@@ -12819,7 +12869,7 @@
       <c r="P50" s="132"/>
       <c r="Q50" s="132"/>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="132" t="s">
         <v>228</v>
       </c>
@@ -12866,7 +12916,7 @@
       <c r="P51" s="99"/>
       <c r="Q51" s="99"/>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="136" t="s">
         <v>229</v>
       </c>
@@ -12922,7 +12972,7 @@
       <c r="P52" s="132"/>
       <c r="Q52" s="132"/>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="147" t="s">
         <v>230</v>
       </c>
@@ -12978,7 +13028,7 @@
       <c r="P53" s="132"/>
       <c r="Q53" s="132"/>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="116" t="s">
         <v>231</v>
       </c>
@@ -13031,7 +13081,7 @@
       <c r="P54" s="132"/>
       <c r="Q54" s="132"/>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="116" t="s">
         <v>232</v>
       </c>
@@ -13084,7 +13134,7 @@
       <c r="P55" s="132"/>
       <c r="Q55" s="132"/>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="116" t="s">
         <v>233</v>
       </c>
@@ -13137,7 +13187,7 @@
       <c r="P56" s="132"/>
       <c r="Q56" s="132"/>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="116" t="s">
         <v>234</v>
       </c>
@@ -13190,7 +13240,7 @@
       <c r="P57" s="132"/>
       <c r="Q57" s="132"/>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="116" t="s">
         <v>235</v>
       </c>
@@ -13243,7 +13293,7 @@
       <c r="P58" s="132"/>
       <c r="Q58" s="132"/>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="147" t="s">
         <v>236</v>
       </c>
@@ -13296,7 +13346,7 @@
       <c r="P59" s="132"/>
       <c r="Q59" s="132"/>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="136" t="s">
         <v>237</v>
       </c>
@@ -13349,7 +13399,7 @@
       <c r="P60" s="153"/>
       <c r="Q60" s="132"/>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="116" t="s">
         <v>238</v>
       </c>
@@ -13384,7 +13434,7 @@
       <c r="P61" s="153"/>
       <c r="Q61" s="132"/>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="116" t="s">
         <v>239</v>
       </c>
@@ -13395,38 +13445,38 @@
       <c r="H62" s="142"/>
       <c r="I62" s="142"/>
       <c r="J62" s="158">
-        <f>J60/(1+J61)^J48</f>
-        <v>30719.828498262901</v>
+        <f ca="1">(J60*$P$48)/(1+J61)^J48</f>
+        <v>12178.987541527766</v>
       </c>
       <c r="K62" s="158">
-        <f>K60/(1+K61)^K48</f>
-        <v>31927.007593858321</v>
+        <f ca="1">K60/(1+K61)^K48</f>
+        <v>33237.52516579994</v>
       </c>
       <c r="L62" s="158">
-        <f>L60/(1+L61)^L48</f>
-        <v>37490.386480989648</v>
+        <f ca="1">L60/(1+L61)^L48</f>
+        <v>39029.265754839005</v>
       </c>
       <c r="M62" s="158">
-        <f>M60/(1+M61)^M48</f>
-        <v>41720.854523066693</v>
+        <f ca="1">M60/(1+M61)^M48</f>
+        <v>43433.383102770378</v>
       </c>
       <c r="N62" s="158">
-        <f>N60/(1+N61)^N48</f>
-        <v>42925.27961418077</v>
+        <f ca="1">N60/(1+N61)^N48</f>
+        <v>44687.246596194862</v>
       </c>
       <c r="O62" s="132"/>
       <c r="P62" s="132"/>
       <c r="Q62" s="132"/>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="136" t="s">
         <v>240</v>
       </c>
       <c r="C63" s="136"/>
       <c r="D63" s="152"/>
       <c r="F63" s="146">
-        <f>SUM(J62:N62)</f>
-        <v>184783.35671035832</v>
+        <f ca="1">SUM(J62:N62)</f>
+        <v>172566.40816113196</v>
       </c>
       <c r="G63" s="152"/>
       <c r="H63" s="132"/>
@@ -13455,7 +13505,7 @@
       <c r="P63" s="132"/>
       <c r="Q63" s="132"/>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="132"/>
       <c r="C64" s="132"/>
       <c r="D64" s="132"/>
@@ -13493,7 +13543,7 @@
       <c r="P65" s="132"/>
       <c r="Q65" s="132"/>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="159" t="s">
         <v>242</v>
       </c>
@@ -13513,7 +13563,7 @@
       <c r="P66" s="132"/>
       <c r="Q66" s="132"/>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="132" t="s">
         <v>243</v>
       </c>
@@ -13536,7 +13586,7 @@
       <c r="P67" s="132"/>
       <c r="Q67" s="132"/>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="132" t="s">
         <v>245</v>
       </c>
@@ -13572,7 +13622,7 @@
       <c r="P68" s="132"/>
       <c r="Q68" s="132"/>
     </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="132" t="s">
         <v>246</v>
       </c>
@@ -13606,7 +13656,7 @@
       <c r="P69" s="132"/>
       <c r="Q69" s="132"/>
     </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="132" t="s">
         <v>241</v>
       </c>
@@ -13628,15 +13678,15 @@
       <c r="P70" s="132"/>
       <c r="Q70" s="132"/>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="136" t="s">
         <v>247</v>
       </c>
       <c r="C71" s="136"/>
       <c r="D71" s="172"/>
       <c r="F71" s="173">
-        <f>F70/(1+F68)^N48</f>
-        <v>758932.43296016683</v>
+        <f ca="1">F70/(1+F68)^N48</f>
+        <v>790084.562904911</v>
       </c>
       <c r="G71" s="174"/>
       <c r="H71" s="162"/>
@@ -13650,7 +13700,7 @@
       <c r="P71" s="132"/>
       <c r="Q71" s="132"/>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="132"/>
       <c r="C72" s="132"/>
       <c r="D72" s="175"/>
@@ -13688,7 +13738,7 @@
       <c r="P73" s="132"/>
       <c r="Q73" s="132"/>
     </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="132" t="s">
         <v>248</v>
       </c>
@@ -13711,7 +13761,7 @@
       <c r="P74" s="132"/>
       <c r="Q74" s="132"/>
     </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="132" t="s">
         <v>195</v>
       </c>
@@ -13734,7 +13784,7 @@
       <c r="P75" s="132"/>
       <c r="Q75" s="132"/>
     </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="132" t="s">
         <v>249</v>
       </c>
@@ -13762,7 +13812,7 @@
       <c r="P76" s="132"/>
       <c r="Q76" s="132"/>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="132" t="s">
         <v>252</v>
       </c>
@@ -13791,7 +13841,7 @@
       <c r="P77" s="132"/>
       <c r="Q77" s="132"/>
     </row>
-    <row r="78" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="132" t="s">
         <v>255</v>
       </c>
@@ -13820,7 +13870,7 @@
       <c r="P78" s="132"/>
       <c r="Q78" s="132"/>
     </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="132" t="s">
         <v>258</v>
       </c>
@@ -13843,7 +13893,7 @@
       <c r="P79" s="132"/>
       <c r="Q79" s="132"/>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="132"/>
       <c r="C80" s="132"/>
       <c r="D80" s="175"/>
@@ -13866,7 +13916,7 @@
       <c r="P80" s="132"/>
       <c r="Q80" s="132"/>
     </row>
-    <row r="81" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="132" t="s">
         <v>260</v>
       </c>
@@ -13891,7 +13941,7 @@
       <c r="P81" s="132"/>
       <c r="Q81" s="132"/>
     </row>
-    <row r="82" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="132" t="s">
         <v>262</v>
       </c>
@@ -13914,7 +13964,7 @@
       <c r="P82" s="132"/>
       <c r="Q82" s="132"/>
     </row>
-    <row r="83" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="184" t="s">
         <v>263</v>
       </c>
@@ -13937,7 +13987,7 @@
       <c r="P83" s="132"/>
       <c r="Q83" s="132"/>
     </row>
-    <row r="84" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="184"/>
       <c r="C84" s="184"/>
       <c r="D84" s="132"/>
@@ -13955,7 +14005,7 @@
       <c r="P84" s="132"/>
       <c r="Q84" s="132"/>
     </row>
-    <row r="85" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="132" t="s">
         <v>264</v>
       </c>
@@ -13978,7 +14028,7 @@
       <c r="P85" s="132"/>
       <c r="Q85" s="132"/>
     </row>
-    <row r="86" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="132" t="s">
         <v>265</v>
       </c>
@@ -14001,7 +14051,7 @@
       <c r="P86" s="132"/>
       <c r="Q86" s="132"/>
     </row>
-    <row r="87" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="184"/>
       <c r="C87" s="184"/>
       <c r="D87" s="132"/>
@@ -14019,7 +14069,7 @@
       <c r="P87" s="132"/>
       <c r="Q87" s="132"/>
     </row>
-    <row r="88" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="136" t="s">
         <v>266</v>
       </c>
@@ -14042,7 +14092,7 @@
       <c r="P88" s="132"/>
       <c r="Q88" s="132"/>
     </row>
-    <row r="89" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="132"/>
       <c r="C89" s="132"/>
       <c r="D89" s="175"/>
@@ -14080,7 +14130,7 @@
       <c r="P90" s="132"/>
       <c r="Q90" s="132"/>
     </row>
-    <row r="91" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="132" t="s">
         <v>268</v>
       </c>
@@ -14090,8 +14140,8 @@
       <c r="F91" s="188"/>
       <c r="G91" s="188"/>
       <c r="H91" s="142">
-        <f>F71+F63</f>
-        <v>943715.78967052512</v>
+        <f ca="1">F71+F63</f>
+        <v>962650.97106604301</v>
       </c>
       <c r="I91" s="132"/>
       <c r="J91" s="132"/>
@@ -14103,7 +14153,7 @@
       <c r="P91" s="132"/>
       <c r="Q91" s="132"/>
     </row>
-    <row r="92" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="132" t="s">
         <v>269</v>
       </c>
@@ -14114,28 +14164,23 @@
       <c r="G92" s="189"/>
       <c r="H92" s="190">
         <f>(M92+M93)-M94</f>
-        <v>35235</v>
+        <v>45958</v>
       </c>
       <c r="I92" s="116" t="s">
         <v>270</v>
       </c>
       <c r="J92" s="188"/>
       <c r="K92" s="132"/>
-      <c r="L92" s="132" t="s">
-        <v>271</v>
-      </c>
-      <c r="M92" s="191">
-        <f>BS!F29</f>
-        <v>1635</v>
-      </c>
+      <c r="L92"/>
+      <c r="M92"/>
       <c r="N92" s="132"/>
       <c r="O92" s="132"/>
       <c r="P92" s="132"/>
       <c r="Q92" s="132"/>
     </row>
-    <row r="93" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="136" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C93" s="136"/>
       <c r="D93" s="132"/>
@@ -14143,25 +14188,25 @@
       <c r="F93" s="132"/>
       <c r="G93" s="132"/>
       <c r="H93" s="146">
-        <f>H91-H92</f>
-        <v>908480.78967052512</v>
+        <f ca="1">H91-H92</f>
+        <v>916692.97106604301</v>
       </c>
       <c r="I93" s="116"/>
       <c r="J93" s="189"/>
       <c r="K93" s="132"/>
       <c r="L93" s="132" t="s">
-        <v>273</v>
+        <v>16</v>
       </c>
       <c r="M93" s="191">
-        <f>BS!F35</f>
-        <v>40868</v>
+        <f>Main!C7</f>
+        <v>54908</v>
       </c>
       <c r="N93" s="132"/>
       <c r="O93" s="132"/>
       <c r="P93" s="132"/>
       <c r="Q93" s="132"/>
     </row>
-    <row r="94" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="132" t="s">
         <v>195</v>
       </c>
@@ -14181,17 +14226,17 @@
         <v>13</v>
       </c>
       <c r="M94" s="191">
-        <f>BS!F14</f>
-        <v>7268</v>
+        <f>Main!C6</f>
+        <v>8950</v>
       </c>
       <c r="N94" s="132"/>
       <c r="O94" s="132"/>
       <c r="P94" s="132"/>
       <c r="Q94" s="132"/>
     </row>
-    <row r="95" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="193" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C95" s="139"/>
       <c r="D95" s="139"/>
@@ -14199,8 +14244,8 @@
       <c r="F95" s="139"/>
       <c r="G95" s="139"/>
       <c r="H95" s="194">
-        <f>H93/H94</f>
-        <v>1016.5388717360693</v>
+        <f ca="1">H93/H94</f>
+        <v>1025.7278405125244</v>
       </c>
       <c r="I95" s="195"/>
       <c r="J95" s="196"/>
@@ -14212,23 +14257,23 @@
       <c r="P95" s="132"/>
       <c r="Q95" s="132"/>
     </row>
-    <row r="96" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="132"/>
       <c r="C96" s="132"/>
       <c r="D96" s="132"/>
       <c r="E96" s="132"/>
       <c r="F96" s="132"/>
       <c r="G96" s="132" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H96" s="197">
-        <f>H95/H5-1</f>
-        <v>-0.16335626431164152</v>
+        <f ca="1">H95/H5-1</f>
+        <v>-0.15579345153781465</v>
       </c>
       <c r="I96" s="184"/>
       <c r="Q96" s="132"/>
     </row>
-    <row r="97" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="132"/>
       <c r="C97" s="132"/>
       <c r="D97" s="175"/>
@@ -14239,119 +14284,262 @@
       <c r="I97" s="175"/>
       <c r="Q97" s="175"/>
     </row>
-    <row r="98" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B98" s="132"/>
-      <c r="C98" s="132"/>
-      <c r="D98" s="198"/>
-      <c r="E98" s="198"/>
-    </row>
-    <row r="99" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B99" s="132"/>
-      <c r="C99" s="132"/>
-      <c r="D99" s="198"/>
-      <c r="E99" s="198"/>
-      <c r="G99" s="198"/>
-    </row>
-    <row r="100" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B100" s="199"/>
-      <c r="C100" s="199"/>
-      <c r="D100" s="198"/>
-      <c r="E100" s="198"/>
-    </row>
-    <row r="101" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B101" s="199"/>
-      <c r="C101" s="199"/>
-      <c r="D101" s="132"/>
-      <c r="E101" s="132"/>
-    </row>
-    <row r="102" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B102" s="199"/>
-      <c r="C102" s="199"/>
-    </row>
-    <row r="103" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B103" s="199"/>
-      <c r="C103" s="200"/>
-    </row>
-    <row r="104" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B104" s="199"/>
-      <c r="C104" s="199"/>
-      <c r="Q104" s="201" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="105" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B105" s="199"/>
-      <c r="C105" s="200"/>
-    </row>
-    <row r="106" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B106" s="199"/>
-      <c r="C106" s="202"/>
-    </row>
-    <row r="107" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B107" s="199"/>
-      <c r="C107" s="200"/>
-    </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C116" s="199"/>
-      <c r="D116" s="199"/>
-      <c r="E116" s="199"/>
-      <c r="F116" s="199"/>
-      <c r="G116" s="199"/>
-      <c r="H116" s="199"/>
-      <c r="I116" s="199"/>
-    </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B117" s="199"/>
-      <c r="C117" s="199"/>
-      <c r="D117" s="199"/>
-      <c r="E117" s="199"/>
-      <c r="F117" s="199"/>
-      <c r="G117" s="199"/>
-      <c r="H117" s="199"/>
-      <c r="I117" s="199"/>
-    </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D118" s="203"/>
-      <c r="E118" s="203"/>
-      <c r="F118" s="203"/>
-      <c r="G118" s="203"/>
-      <c r="H118" s="203"/>
-      <c r="I118" s="203"/>
-    </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D120" s="199"/>
-    </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D121" s="203"/>
-    </row>
-    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C129" s="199"/>
-      <c r="D129" s="199"/>
-      <c r="E129" s="199"/>
-      <c r="F129" s="199"/>
-      <c r="G129" s="199"/>
-      <c r="H129" s="199"/>
-      <c r="I129" s="199"/>
-      <c r="J129" s="199"/>
-      <c r="K129" s="199"/>
-      <c r="L129" s="199"/>
-      <c r="M129" s="199"/>
-      <c r="N129" s="199"/>
-    </row>
-    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B130" s="199"/>
-      <c r="C130" s="204"/>
-      <c r="D130" s="205"/>
-      <c r="E130" s="205"/>
-      <c r="F130" s="205"/>
-      <c r="G130" s="205"/>
-      <c r="H130" s="205"/>
-      <c r="I130" s="205"/>
-      <c r="J130" s="206"/>
-      <c r="K130" s="206"/>
-      <c r="L130" s="206"/>
-      <c r="M130" s="206"/>
-      <c r="N130" s="206"/>
+    <row r="98" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J98" s="132"/>
+      <c r="K98" s="198"/>
+      <c r="L98" s="198"/>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I99" s="184" t="s">
+        <v>342</v>
+      </c>
+      <c r="J99" s="132"/>
+      <c r="K99" s="198"/>
+      <c r="L99" s="198"/>
+      <c r="N99" s="198"/>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I100" s="199" t="s">
+        <v>274</v>
+      </c>
+      <c r="J100" s="200">
+        <f>$F$67-0.01</f>
+        <v>0</v>
+      </c>
+      <c r="K100" s="200">
+        <f>$F$67-0.005</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="L100" s="200">
+        <f>$F$67</f>
+        <v>0.01</v>
+      </c>
+      <c r="M100" s="200">
+        <f>$F$67+0.005</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N100" s="200">
+        <f>$F$67+0.01</f>
+        <v>0.02</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I101" s="200">
+        <f>$H$88-0.01</f>
+        <v>5.7125681453908929E-2</v>
+      </c>
+      <c r="J101" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I101)^J$48+K$60/(1+$I101)^K$48+L$60/(1+$I101)^L$48+M$60/(1+$I101)^M$48+N$60/(1+$I101)^N$48+(N$60*(1+J$100)/($I101-J$100))/(1+$I101)^N$48-$H$92)/$H$94</f>
+        <v>1059.0356553766926</v>
+      </c>
+      <c r="K101" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I101)^J$48+K$60/(1+$I101)^K$48+L$60/(1+$I101)^L$48+M$60/(1+$I101)^M$48+N$60/(1+$I101)^N$48+(N$60*(1+K$100)/($I101-K$100))/(1+$I101)^N$48-$H$92)/$H$94</f>
+        <v>1151.5306605098965</v>
+      </c>
+      <c r="L101" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I101)^J$48+K$60/(1+$I101)^K$48+L$60/(1+$I101)^L$48+M$60/(1+$I101)^M$48+N$60/(1+$I101)^N$48+(N$60*(1+L$100)/($I101-L$100))/(1+$I101)^N$48-$H$92)/$H$94</f>
+        <v>1263.6529691174644</v>
+      </c>
+      <c r="M101" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I101)^J$48+K$60/(1+$I101)^K$48+L$60/(1+$I101)^L$48+M$60/(1+$I101)^M$48+N$60/(1+$I101)^N$48+(N$60*(1+M$100)/($I101-M$100))/(1+$I101)^N$48-$H$92)/$H$94</f>
+        <v>1402.3914189333927</v>
+      </c>
+      <c r="N101" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I101)^J$48+K$60/(1+$I101)^K$48+L$60/(1+$I101)^L$48+M$60/(1+$I101)^M$48+N$60/(1+$I101)^N$48+(N$60*(1+N$100)/($I101-N$100))/(1+$I101)^N$48-$H$92)/$H$94</f>
+        <v>1578.4998090124168</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I102" s="200">
+        <f>$H$88-0.005</f>
+        <v>6.2125681453908933E-2</v>
+      </c>
+      <c r="J102" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I102)^J$48+K$60/(1+$I102)^K$48+L$60/(1+$I102)^L$48+M$60/(1+$I102)^M$48+N$60/(1+$I102)^N$48+(N$60*(1+J$100)/($I102-J$100))/(1+$I102)^N$48-$H$92)/$H$94</f>
+        <v>965.83410366892554</v>
+      </c>
+      <c r="K102" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I102)^J$48+K$60/(1+$I102)^K$48+L$60/(1+$I102)^L$48+M$60/(1+$I102)^M$48+N$60/(1+$I102)^N$48+(N$60*(1+K$100)/($I102-K$100))/(1+$I102)^N$48-$H$92)/$H$94</f>
+        <v>1042.2125093676839</v>
+      </c>
+      <c r="L102" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I102)^J$48+K$60/(1+$I102)^K$48+L$60/(1+$I102)^L$48+M$60/(1+$I102)^M$48+N$60/(1+$I102)^N$48+(N$60*(1+L$100)/($I102-L$100))/(1+$I102)^N$48-$H$92)/$H$94</f>
+        <v>1133.2436550534096</v>
+      </c>
+      <c r="M102" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I102)^J$48+K$60/(1+$I102)^K$48+L$60/(1+$I102)^L$48+M$60/(1+$I102)^M$48+N$60/(1+$I102)^N$48+(N$60*(1+M$100)/($I102-M$100))/(1+$I102)^N$48-$H$92)/$H$94</f>
+        <v>1243.5914754008597</v>
+      </c>
+      <c r="N102" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I102)^J$48+K$60/(1+$I102)^K$48+L$60/(1+$I102)^L$48+M$60/(1+$I102)^M$48+N$60/(1+$I102)^N$48+(N$60*(1+N$100)/($I102-N$100))/(1+$I102)^N$48-$H$92)/$H$94</f>
+        <v>1380.1342002671095</v>
+      </c>
+      <c r="O102" s="3"/>
+    </row>
+    <row r="103" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I103" s="200">
+        <f>$H$88</f>
+        <v>6.7125681453908931E-2</v>
+      </c>
+      <c r="J103" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I103)^J$48+K$60/(1+$I103)^K$48+L$60/(1+$I103)^L$48+M$60/(1+$I103)^M$48+N$60/(1+$I103)^N$48+(N$60*(1+J$100)/($I103-J$100))/(1+$I103)^N$48-$H$92)/$H$94</f>
+        <v>886.57652744604525</v>
+      </c>
+      <c r="K103" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I103)^J$48+K$60/(1+$I103)^K$48+L$60/(1+$I103)^L$48+M$60/(1+$I103)^M$48+N$60/(1+$I103)^N$48+(N$60*(1+K$100)/($I103-K$100))/(1+$I103)^N$48-$H$92)/$H$94</f>
+        <v>950.55259497639713</v>
+      </c>
+      <c r="L103" s="202">
+        <f ca="1">((J$60*$P$48)/(1+$I103)^J$48+K$60/(1+$I103)^K$48+L$60/(1+$I103)^L$48+M$60/(1+$I103)^M$48+N$60/(1+$I103)^N$48+(N$60*(1+L$100)/($I103-L$100))/(1+$I103)^N$48-$H$92)/$H$94</f>
+        <v>1025.7278405125244</v>
+      </c>
+      <c r="M103" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I103)^J$48+K$60/(1+$I103)^K$48+L$60/(1+$I103)^L$48+M$60/(1+$I103)^M$48+N$60/(1+$I103)^N$48+(N$60*(1+M$100)/($I103-M$100))/(1+$I103)^N$48-$H$92)/$H$94</f>
+        <v>1115.3250069596704</v>
+      </c>
+      <c r="N103" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I103)^J$48+K$60/(1+$I103)^K$48+L$60/(1+$I103)^L$48+M$60/(1+$I103)^M$48+N$60/(1+$I103)^N$48+(N$60*(1+N$100)/($I103-N$100))/(1+$I103)^N$48-$H$92)/$H$94</f>
+        <v>1223.9345597920997</v>
+      </c>
+      <c r="O103" s="3"/>
+    </row>
+    <row r="104" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I104" s="200">
+        <f>$H$88+0.005</f>
+        <v>7.2125681453908935E-2</v>
+      </c>
+      <c r="J104" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I104)^J$48+K$60/(1+$I104)^K$48+L$60/(1+$I104)^L$48+M$60/(1+$I104)^M$48+N$60/(1+$I104)^N$48+(N$60*(1+J$100)/($I104-J$100))/(1+$I104)^N$48-$H$92)/$H$94</f>
+        <v>818.36183668066622</v>
+      </c>
+      <c r="K104" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I104)^J$48+K$60/(1+$I104)^K$48+L$60/(1+$I104)^L$48+M$60/(1+$I104)^M$48+N$60/(1+$I104)^N$48+(N$60*(1+K$100)/($I104-K$100))/(1+$I104)^N$48-$H$92)/$H$94</f>
+        <v>872.60378472869832</v>
+      </c>
+      <c r="L104" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I104)^J$48+K$60/(1+$I104)^K$48+L$60/(1+$I104)^L$48+M$60/(1+$I104)^M$48+N$60/(1+$I104)^N$48+(N$60*(1+L$100)/($I104-L$100))/(1+$I104)^N$48-$H$92)/$H$94</f>
+        <v>935.57673528304065</v>
+      </c>
+      <c r="M104" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I104)^J$48+K$60/(1+$I104)^K$48+L$60/(1+$I104)^L$48+M$60/(1+$I104)^M$48+N$60/(1+$I104)^N$48+(N$60*(1+M$100)/($I104-M$100))/(1+$I104)^N$48-$H$92)/$H$94</f>
+        <v>1009.57326559199</v>
+      </c>
+      <c r="N104" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I104)^J$48+K$60/(1+$I104)^K$48+L$60/(1+$I104)^L$48+M$60/(1+$I104)^M$48+N$60/(1+$I104)^N$48+(N$60*(1+N$100)/($I104-N$100))/(1+$I104)^N$48-$H$92)/$H$94</f>
+        <v>1097.7655873505682</v>
+      </c>
+      <c r="O104" s="3"/>
+      <c r="Q104" s="203" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="105" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I105" s="200">
+        <f>$H$88+0.01</f>
+        <v>7.7125681453908926E-2</v>
+      </c>
+      <c r="J105" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I105)^J$48+K$60/(1+$I105)^K$48+L$60/(1+$I105)^L$48+M$60/(1+$I105)^M$48+N$60/(1+$I105)^N$48+(N$60*(1+J$100)/($I105-J$100))/(1+$I105)^N$48-$H$92)/$H$94</f>
+        <v>759.04127161905876</v>
+      </c>
+      <c r="K105" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I105)^J$48+K$60/(1+$I105)^K$48+L$60/(1+$I105)^L$48+M$60/(1+$I105)^M$48+N$60/(1+$I105)^N$48+(N$60*(1+K$100)/($I105-K$100))/(1+$I105)^N$48-$H$92)/$H$94</f>
+        <v>805.5134903043546</v>
+      </c>
+      <c r="L105" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I105)^J$48+K$60/(1+$I105)^K$48+L$60/(1+$I105)^L$48+M$60/(1+$I105)^M$48+N$60/(1+$I105)^N$48+(N$60*(1+L$100)/($I105-L$100))/(1+$I105)^N$48-$H$92)/$H$94</f>
+        <v>858.90887426391362</v>
+      </c>
+      <c r="M105" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I105)^J$48+K$60/(1+$I105)^K$48+L$60/(1+$I105)^L$48+M$60/(1+$I105)^M$48+N$60/(1+$I105)^N$48+(N$60*(1+M$100)/($I105-M$100))/(1+$I105)^N$48-$H$92)/$H$94</f>
+        <v>920.89899436317603</v>
+      </c>
+      <c r="N105" s="201">
+        <f ca="1">((J$60*$P$48)/(1+$I105)^J$48+K$60/(1+$I105)^K$48+L$60/(1+$I105)^L$48+M$60/(1+$I105)^M$48+N$60/(1+$I105)^N$48+(N$60*(1+N$100)/($I105-N$100))/(1+$I105)^N$48-$H$92)/$H$94</f>
+        <v>993.74064717444253</v>
+      </c>
+      <c r="O105" s="3"/>
+    </row>
+    <row r="106" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I106" s="204"/>
+      <c r="J106" s="205"/>
+      <c r="O106" s="3"/>
+    </row>
+    <row r="107" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I107" s="132" t="s">
+        <v>343</v>
+      </c>
+      <c r="J107" s="206">
+        <f>H5</f>
+        <v>1215.02</v>
+      </c>
+      <c r="O107" s="3"/>
+    </row>
+    <row r="116" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C116" s="204"/>
+      <c r="D116" s="204"/>
+      <c r="E116" s="204"/>
+      <c r="F116" s="204"/>
+      <c r="G116" s="204"/>
+      <c r="H116" s="204"/>
+      <c r="I116" s="204"/>
+    </row>
+    <row r="117" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="204"/>
+      <c r="C117" s="204"/>
+      <c r="D117" s="204"/>
+      <c r="E117" s="204"/>
+      <c r="F117" s="204"/>
+      <c r="G117" s="204"/>
+      <c r="H117" s="204"/>
+      <c r="I117" s="204"/>
+    </row>
+    <row r="118" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D118" s="207"/>
+      <c r="E118" s="207"/>
+      <c r="F118" s="207"/>
+      <c r="G118" s="207"/>
+      <c r="H118" s="207"/>
+      <c r="I118" s="207"/>
+    </row>
+    <row r="120" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D120" s="204"/>
+    </row>
+    <row r="121" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D121" s="207"/>
+    </row>
+    <row r="129" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C129" s="204"/>
+      <c r="D129" s="204"/>
+      <c r="E129" s="204"/>
+      <c r="F129" s="204"/>
+      <c r="G129" s="204"/>
+      <c r="H129" s="204"/>
+      <c r="I129" s="204"/>
+      <c r="J129" s="204"/>
+      <c r="K129" s="204"/>
+      <c r="L129" s="204"/>
+      <c r="M129" s="204"/>
+      <c r="N129" s="204"/>
+    </row>
+    <row r="130" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="204"/>
+      <c r="C130" s="208"/>
+      <c r="D130" s="209"/>
+      <c r="E130" s="209"/>
+      <c r="F130" s="209"/>
+      <c r="G130" s="209"/>
+      <c r="H130" s="209"/>
+      <c r="I130" s="209"/>
+      <c r="J130" s="210"/>
+      <c r="K130" s="210"/>
+      <c r="L130" s="210"/>
+      <c r="M130" s="210"/>
+      <c r="N130" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -14376,7 +14564,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -14384,10 +14572,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14395,15 +14583,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14426,7 +14614,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
@@ -14434,10 +14622,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14445,15 +14633,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14476,7 +14664,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -14484,10 +14672,10 @@
     </row>
     <row r="3" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14495,15 +14683,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
